--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4622,7 +4622,7 @@
         <v>2.5</v>
       </c>
       <c r="J55" t="n">
-        <v>280.58</v>
+        <v>280.59</v>
       </c>
       <c r="K55" t="n">
         <v>268.78</v>
@@ -8562,7 +8562,7 @@
         <v>2.5</v>
       </c>
       <c r="J107" t="n">
-        <v>308.88</v>
+        <v>308.89</v>
       </c>
       <c r="K107" t="n">
         <v>302.49</v>
@@ -31559,6 +31559,83 @@
         <v>154.5</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>391.89</v>
+      </c>
+      <c r="D413" t="n">
+        <v>395.89</v>
+      </c>
+      <c r="E413" t="n">
+        <v>390.96</v>
+      </c>
+      <c r="F413" t="n">
+        <v>395.05</v>
+      </c>
+      <c r="G413" t="n">
+        <v>5396103</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J413" t="n">
+        <v>409.11</v>
+      </c>
+      <c r="K413" t="n">
+        <v>388.69</v>
+      </c>
+      <c r="L413" t="n">
+        <v>404.1</v>
+      </c>
+      <c r="M413" t="n">
+        <v>416.01</v>
+      </c>
+      <c r="N413" s="3" t="n">
+        <v>29.18</v>
+      </c>
+      <c r="O413" t="n">
+        <v>31</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S413" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -4622,7 +4622,7 @@
         <v>2.5</v>
       </c>
       <c r="J55" t="n">
-        <v>280.59</v>
+        <v>280.58</v>
       </c>
       <c r="K55" t="n">
         <v>268.78</v>
@@ -8562,7 +8562,7 @@
         <v>2.5</v>
       </c>
       <c r="J107" t="n">
-        <v>308.89</v>
+        <v>308.88</v>
       </c>
       <c r="K107" t="n">
         <v>302.49</v>
@@ -11676,7 +11676,7 @@
         <v>308.13</v>
       </c>
       <c r="K148" t="n">
-        <v>308.4</v>
+        <v>308.39</v>
       </c>
       <c r="L148" t="n">
         <v>300.06</v>
@@ -31580,31 +31580,31 @@
         <v>390.96</v>
       </c>
       <c r="F413" t="n">
-        <v>395.05</v>
+        <v>392.84</v>
       </c>
       <c r="G413" t="n">
-        <v>5396103</v>
+        <v>7347570</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>-0.93</v>
+        <v>-1.49</v>
       </c>
       <c r="I413" t="n">
         <v>2.5</v>
       </c>
       <c r="J413" t="n">
-        <v>409.11</v>
+        <v>409</v>
       </c>
       <c r="K413" t="n">
-        <v>388.69</v>
+        <v>388.65</v>
       </c>
       <c r="L413" t="n">
-        <v>404.1</v>
+        <v>404.08</v>
       </c>
       <c r="M413" t="n">
-        <v>416.01</v>
+        <v>416</v>
       </c>
       <c r="N413" s="3" t="n">
-        <v>29.18</v>
+        <v>28.35</v>
       </c>
       <c r="O413" t="n">
         <v>31</v>
@@ -31625,16 +31625,18 @@
         </is>
       </c>
       <c r="S413" t="n">
-        <v>4.95</v>
+        <v>4.96</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>16.7</v>
+        <v>17.1</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>152.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31435,7 +31435,7 @@
         <v>398.77</v>
       </c>
       <c r="G411" t="n">
-        <v>10943000</v>
+        <v>10963000</v>
       </c>
       <c r="H411" s="1" t="n">
         <v>0.61</v>
@@ -31495,28 +31495,44 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="C412" t="n">
+        <v>391.89</v>
+      </c>
+      <c r="D412" t="n">
+        <v>395.9</v>
+      </c>
+      <c r="E412" t="n">
+        <v>390.96</v>
+      </c>
+      <c r="F412" t="n">
+        <v>392.84</v>
+      </c>
       <c r="G412" t="n">
-        <v>7347570</v>
-      </c>
-      <c r="H412" s="3" t="n">
-        <v>0</v>
+        <v>7424200</v>
+      </c>
+      <c r="H412" s="2" t="n">
+        <v>-1.49</v>
       </c>
       <c r="I412" t="n">
         <v>2.5</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
-      <c r="N412" s="3" t="n">
-        <v>30.68</v>
+      <c r="J412" t="n">
+        <v>409</v>
+      </c>
+      <c r="K412" t="n">
+        <v>388.65</v>
+      </c>
+      <c r="L412" t="n">
+        <v>404.08</v>
+      </c>
+      <c r="M412" t="n">
+        <v>416</v>
+      </c>
+      <c r="N412" s="1" t="n">
+        <v>28.35</v>
       </c>
       <c r="O412" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31528,16 +31544,18 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R412" t="inlineStr"/>
+      <c r="R412" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
       <c r="S412" t="n">
         <v>4.96</v>
       </c>
       <c r="T412" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="U412" s="3" t="n">
-        <v>12</v>
-      </c>
+      <c r="U412" s="3" t="inlineStr"/>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="3" t="n">
         <v>152.1</v>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31532,7 +31532,7 @@
         <v>28.35</v>
       </c>
       <c r="O412" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31561,6 +31561,83 @@
         <v>152.1</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>393.11</v>
+      </c>
+      <c r="D413" t="n">
+        <v>394.33</v>
+      </c>
+      <c r="E413" t="n">
+        <v>391.81</v>
+      </c>
+      <c r="F413" t="n">
+        <v>393.69</v>
+      </c>
+      <c r="G413" t="n">
+        <v>4734108</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J413" t="n">
+        <v>408.41</v>
+      </c>
+      <c r="K413" t="n">
+        <v>388.76</v>
+      </c>
+      <c r="L413" t="n">
+        <v>403.99</v>
+      </c>
+      <c r="M413" t="n">
+        <v>416.07</v>
+      </c>
+      <c r="N413" s="1" t="n">
+        <v>27.87</v>
+      </c>
+      <c r="O413" t="n">
+        <v>29</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S413" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="T413" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="U413" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -645,9 +645,7 @@
       <c r="T2" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="U2" s="3" t="n">
-        <v>9</v>
-      </c>
+      <c r="U2" s="3" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" s="2" t="n">
         <v>173.2</v>
@@ -720,9 +718,7 @@
       <c r="T3" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="U3" s="3" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="U3" s="3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" s="2" t="n">
         <v>168.6</v>
@@ -795,9 +791,7 @@
       <c r="T4" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U4" s="3" t="n">
-        <v>13.5</v>
-      </c>
+      <c r="U4" s="3" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" s="2" t="n">
         <v>163.6</v>
@@ -870,9 +864,7 @@
       <c r="T5" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="U5" s="3" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U5" s="3" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" s="2" t="n">
         <v>157.4</v>
@@ -945,9 +937,7 @@
       <c r="T6" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="U6" s="3" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="U6" s="3" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" s="2" t="n">
         <v>156.7</v>
@@ -1020,9 +1010,7 @@
       <c r="T7" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U7" s="3" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="U7" s="3" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" s="2" t="n">
         <v>158.5</v>
@@ -1095,9 +1083,7 @@
       <c r="T8" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="U8" s="3" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="U8" s="3" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" s="2" t="n">
         <v>155.4</v>
@@ -1170,9 +1156,7 @@
       <c r="T9" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="U9" s="3" t="n">
-        <v>15</v>
-      </c>
+      <c r="U9" s="3" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" s="2" t="n">
         <v>159.4</v>
@@ -1245,9 +1229,7 @@
       <c r="T10" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="U10" s="3" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U10" s="3" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" s="2" t="n">
         <v>162.6</v>
@@ -1320,9 +1302,7 @@
       <c r="T11" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="U11" s="3" t="n">
-        <v>15.8</v>
-      </c>
+      <c r="U11" s="3" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" s="2" t="n">
         <v>163.6</v>
@@ -1395,9 +1375,7 @@
       <c r="T12" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="U12" s="3" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U12" s="3" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" s="2" t="n">
         <v>166.5</v>
@@ -1470,9 +1448,7 @@
       <c r="T13" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="U13" s="3" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="U13" s="3" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" s="2" t="n">
         <v>166.9</v>
@@ -1545,9 +1521,7 @@
       <c r="T14" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="U14" s="3" t="n">
-        <v>14.1</v>
-      </c>
+      <c r="U14" s="3" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" s="2" t="n">
         <v>168.8</v>
@@ -1620,9 +1594,7 @@
       <c r="T15" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="U15" s="3" t="n">
-        <v>12.8</v>
-      </c>
+      <c r="U15" s="3" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" s="2" t="n">
         <v>166.1</v>
@@ -1695,9 +1667,7 @@
       <c r="T16" s="3" t="n">
         <v>15.1</v>
       </c>
-      <c r="U16" s="3" t="n">
-        <v>11</v>
-      </c>
+      <c r="U16" s="3" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" s="2" t="n">
         <v>163.4</v>
@@ -1770,9 +1740,7 @@
       <c r="T17" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="U17" s="3" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U17" s="3" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" s="2" t="n">
         <v>168</v>
@@ -1845,9 +1813,7 @@
       <c r="T18" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="U18" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
+      <c r="U18" s="3" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" s="2" t="n">
         <v>183.1</v>
@@ -1920,9 +1886,7 @@
       <c r="T19" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="U19" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
+      <c r="U19" s="3" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" s="2" t="n">
         <v>175.8</v>
@@ -1995,9 +1959,7 @@
       <c r="T20" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="U20" s="3" t="n">
-        <v>11.2</v>
-      </c>
+      <c r="U20" s="3" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" s="2" t="n">
         <v>178.6</v>
@@ -2070,9 +2032,7 @@
       <c r="T21" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="U21" s="3" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="U21" s="3" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21" s="2" t="n">
         <v>165</v>
@@ -2145,9 +2105,7 @@
       <c r="T22" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="U22" s="3" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U22" s="3" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" s="2" t="n">
         <v>156.9</v>
@@ -2220,9 +2178,7 @@
       <c r="T23" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="U23" s="3" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U23" s="3" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" s="2" t="n">
         <v>157.6</v>
@@ -2295,9 +2251,7 @@
       <c r="T24" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="U24" s="3" t="n">
-        <v>20.5</v>
-      </c>
+      <c r="U24" s="3" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" s="3" t="n">
         <v>153.4</v>
@@ -2374,9 +2328,7 @@
       <c r="T25" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="U25" s="3" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="U25" s="3" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
       <c r="W25" s="3" t="n">
         <v>149.3</v>
@@ -2449,9 +2401,7 @@
       <c r="T26" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="U26" s="3" t="n">
-        <v>18.7</v>
-      </c>
+      <c r="U26" s="3" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
       <c r="W26" s="2" t="n">
         <v>157.9</v>
@@ -2524,9 +2474,7 @@
       <c r="T27" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="U27" s="3" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="U27" s="3" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
       <c r="W27" s="3" t="n">
         <v>154.3</v>
@@ -2599,9 +2547,7 @@
       <c r="T28" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="U28" s="3" t="n">
-        <v>24.6</v>
-      </c>
+      <c r="U28" s="3" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
       <c r="W28" s="3" t="n">
         <v>151.4</v>
@@ -2674,9 +2620,7 @@
       <c r="T29" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="U29" s="3" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U29" s="3" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
       <c r="W29" s="3" t="n">
         <v>138.9</v>
@@ -2749,9 +2693,7 @@
       <c r="T30" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="U30" s="1" t="n">
-        <v>31.1</v>
-      </c>
+      <c r="U30" s="3" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
       <c r="W30" s="3" t="n">
         <v>137.6</v>
@@ -2824,9 +2766,7 @@
       <c r="T31" s="3" t="n">
         <v>23.4</v>
       </c>
-      <c r="U31" s="3" t="n">
-        <v>24.7</v>
-      </c>
+      <c r="U31" s="3" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
       <c r="W31" s="3" t="n">
         <v>139.9</v>
@@ -2903,14 +2843,8 @@
       <c r="T32" s="1" t="n">
         <v>27.9</v>
       </c>
-      <c r="U32" s="1" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="V32" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U32" s="3" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" s="3" t="n">
         <v>146</v>
       </c>
@@ -2982,14 +2916,8 @@
       <c r="T33" s="1" t="n">
         <v>26.9</v>
       </c>
-      <c r="U33" s="1" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="V33" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U33" s="3" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" s="3" t="n">
         <v>132.8</v>
       </c>
@@ -3061,9 +2989,7 @@
       <c r="T34" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="U34" s="3" t="n">
-        <v>23.2</v>
-      </c>
+      <c r="U34" s="3" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
       <c r="W34" s="3" t="n">
         <v>128.7</v>
@@ -3136,9 +3062,7 @@
       <c r="T35" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="U35" s="3" t="n">
-        <v>23.4</v>
-      </c>
+      <c r="U35" s="3" t="inlineStr"/>
       <c r="V35" t="inlineStr"/>
       <c r="W35" s="3" t="n">
         <v>128.9</v>
@@ -3211,9 +3135,7 @@
       <c r="T36" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="U36" s="3" t="n">
-        <v>21.4</v>
-      </c>
+      <c r="U36" s="3" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
       <c r="W36" s="3" t="n">
         <v>130.3</v>
@@ -3286,9 +3208,7 @@
       <c r="T37" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="U37" s="3" t="n">
-        <v>16.4</v>
-      </c>
+      <c r="U37" s="3" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" s="3" t="n">
         <v>133.9</v>
@@ -3361,9 +3281,7 @@
       <c r="T38" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="U38" s="3" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U38" s="3" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" s="3" t="n">
         <v>136.8</v>
@@ -3436,9 +3354,7 @@
       <c r="T39" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="U39" s="3" t="n">
-        <v>18.5</v>
-      </c>
+      <c r="U39" s="3" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
       <c r="W39" s="3" t="n">
         <v>136.4</v>
@@ -3511,9 +3427,7 @@
       <c r="T40" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="U40" s="3" t="n">
-        <v>18.6</v>
-      </c>
+      <c r="U40" s="3" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
       <c r="W40" s="3" t="n">
         <v>140.8</v>
@@ -3586,9 +3500,7 @@
       <c r="T41" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="U41" s="3" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U41" s="3" t="inlineStr"/>
       <c r="V41" t="inlineStr"/>
       <c r="W41" s="3" t="n">
         <v>141.7</v>
@@ -3661,9 +3573,7 @@
       <c r="T42" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="U42" s="3" t="n">
-        <v>13</v>
-      </c>
+      <c r="U42" s="3" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
       <c r="W42" s="3" t="n">
         <v>144</v>
@@ -3736,9 +3646,7 @@
       <c r="T43" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="U43" s="3" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U43" s="3" t="inlineStr"/>
       <c r="V43" t="inlineStr"/>
       <c r="W43" s="3" t="n">
         <v>148.7</v>
@@ -3811,9 +3719,7 @@
       <c r="T44" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="U44" s="3" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U44" s="3" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
       <c r="W44" s="3" t="n">
         <v>144.8</v>
@@ -3886,9 +3792,7 @@
       <c r="T45" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="U45" s="3" t="n">
-        <v>17.1</v>
-      </c>
+      <c r="U45" s="3" t="inlineStr"/>
       <c r="V45" t="inlineStr"/>
       <c r="W45" s="3" t="n">
         <v>140.9</v>
@@ -3961,9 +3865,7 @@
       <c r="T46" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="U46" s="1" t="n">
-        <v>25.4</v>
-      </c>
+      <c r="U46" s="3" t="inlineStr"/>
       <c r="V46" t="inlineStr"/>
       <c r="W46" s="3" t="n">
         <v>139</v>
@@ -4036,9 +3938,7 @@
       <c r="T47" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="U47" s="3" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="U47" s="3" t="inlineStr"/>
       <c r="V47" t="inlineStr"/>
       <c r="W47" s="3" t="n">
         <v>148.6</v>
@@ -4111,9 +4011,7 @@
       <c r="T48" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="U48" s="3" t="n">
-        <v>20.1</v>
-      </c>
+      <c r="U48" s="3" t="inlineStr"/>
       <c r="V48" t="inlineStr"/>
       <c r="W48" s="3" t="n">
         <v>143</v>
@@ -4186,9 +4084,7 @@
       <c r="T49" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="U49" s="1" t="n">
-        <v>26.7</v>
-      </c>
+      <c r="U49" s="3" t="inlineStr"/>
       <c r="V49" t="inlineStr"/>
       <c r="W49" s="3" t="n">
         <v>144.3</v>
@@ -4261,14 +4157,8 @@
       <c r="T50" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="U50" s="1" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="V50" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U50" s="3" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
       <c r="W50" s="3" t="n">
         <v>139.2</v>
       </c>
@@ -4340,14 +4230,8 @@
       <c r="T51" s="1" t="n">
         <v>45.3</v>
       </c>
-      <c r="U51" s="1" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="V51" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U51" s="3" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
       <c r="W51" s="3" t="n">
         <v>136.5</v>
       </c>
@@ -4423,14 +4307,8 @@
       <c r="T52" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="U52" s="1" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="V52" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U52" s="3" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
       <c r="W52" s="3" t="n">
         <v>133.8</v>
       </c>
@@ -4502,14 +4380,8 @@
       <c r="T53" s="1" t="n">
         <v>52.3</v>
       </c>
-      <c r="U53" s="1" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="V53" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U53" s="3" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" s="3" t="n">
         <v>135.7</v>
       </c>
@@ -4581,14 +4453,8 @@
       <c r="T54" s="1" t="n">
         <v>33.6</v>
       </c>
-      <c r="U54" s="1" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="V54" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U54" s="3" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
       <c r="W54" s="3" t="n">
         <v>142.2</v>
       </c>
@@ -4660,14 +4526,8 @@
       <c r="T55" s="1" t="n">
         <v>40.7</v>
       </c>
-      <c r="U55" s="1" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="V55" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U55" s="3" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
       <c r="W55" s="3" t="n">
         <v>127.5</v>
       </c>
@@ -4739,14 +4599,8 @@
       <c r="T56" s="1" t="n">
         <v>37.6</v>
       </c>
-      <c r="U56" s="1" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="V56" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U56" s="3" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
       <c r="W56" s="3" t="n">
         <v>128.6</v>
       </c>
@@ -4818,9 +4672,7 @@
       <c r="T57" s="1" t="n">
         <v>30.9</v>
       </c>
-      <c r="U57" s="1" t="n">
-        <v>28.5</v>
-      </c>
+      <c r="U57" s="3" t="inlineStr"/>
       <c r="V57" t="inlineStr"/>
       <c r="W57" s="3" t="n">
         <v>135.7</v>
@@ -4893,9 +4745,7 @@
       <c r="T58" s="1" t="n">
         <v>30.1</v>
       </c>
-      <c r="U58" s="1" t="n">
-        <v>26</v>
-      </c>
+      <c r="U58" s="3" t="inlineStr"/>
       <c r="V58" t="inlineStr"/>
       <c r="W58" s="3" t="n">
         <v>135.8</v>
@@ -4968,14 +4818,8 @@
       <c r="T59" s="1" t="n">
         <v>32.6</v>
       </c>
-      <c r="U59" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="V59" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U59" s="3" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
       <c r="W59" s="3" t="n">
         <v>131.3</v>
       </c>
@@ -5047,14 +4891,8 @@
       <c r="T60" s="1" t="n">
         <v>29.6</v>
       </c>
-      <c r="U60" s="1" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="V60" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U60" s="3" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
       <c r="W60" s="3" t="n">
         <v>130</v>
       </c>
@@ -5126,9 +4964,7 @@
       <c r="T61" s="1" t="n">
         <v>33.8</v>
       </c>
-      <c r="U61" s="1" t="n">
-        <v>30.6</v>
-      </c>
+      <c r="U61" s="3" t="inlineStr"/>
       <c r="V61" t="inlineStr"/>
       <c r="W61" s="1" t="n">
         <v>125.8</v>
@@ -5201,9 +5037,7 @@
       <c r="T62" s="1" t="n">
         <v>30.6</v>
       </c>
-      <c r="U62" s="1" t="n">
-        <v>29.1</v>
-      </c>
+      <c r="U62" s="3" t="inlineStr"/>
       <c r="V62" t="inlineStr"/>
       <c r="W62" s="1" t="n">
         <v>125.9</v>
@@ -5276,14 +5110,8 @@
       <c r="T63" s="1" t="n">
         <v>28.5</v>
       </c>
-      <c r="U63" s="1" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="V63" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U63" s="3" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
       <c r="W63" s="1" t="n">
         <v>126.7</v>
       </c>
@@ -5355,9 +5183,7 @@
       <c r="T64" s="1" t="n">
         <v>26.5</v>
       </c>
-      <c r="U64" s="1" t="n">
-        <v>25.7</v>
-      </c>
+      <c r="U64" s="3" t="inlineStr"/>
       <c r="V64" t="inlineStr"/>
       <c r="W64" s="3" t="n">
         <v>129</v>
@@ -5430,9 +5256,7 @@
       <c r="T65" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="U65" s="3" t="n">
-        <v>23.6</v>
-      </c>
+      <c r="U65" s="3" t="inlineStr"/>
       <c r="V65" t="inlineStr"/>
       <c r="W65" s="3" t="n">
         <v>132.4</v>
@@ -5505,9 +5329,7 @@
       <c r="T66" s="1" t="n">
         <v>25.1</v>
       </c>
-      <c r="U66" s="3" t="n">
-        <v>21.4</v>
-      </c>
+      <c r="U66" s="3" t="inlineStr"/>
       <c r="V66" t="inlineStr"/>
       <c r="W66" s="3" t="n">
         <v>131.3</v>
@@ -5580,9 +5402,7 @@
       <c r="T67" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="U67" s="3" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U67" s="3" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
       <c r="W67" s="3" t="n">
         <v>134.3</v>
@@ -5655,9 +5475,7 @@
       <c r="T68" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="U68" s="3" t="n">
-        <v>22.9</v>
-      </c>
+      <c r="U68" s="3" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
       <c r="W68" s="3" t="n">
         <v>132.7</v>
@@ -5734,9 +5552,7 @@
       <c r="T69" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="U69" s="1" t="n">
-        <v>27.5</v>
-      </c>
+      <c r="U69" s="3" t="inlineStr"/>
       <c r="V69" t="inlineStr"/>
       <c r="W69" s="3" t="n">
         <v>134.1</v>
@@ -5809,9 +5625,7 @@
       <c r="T70" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="U70" s="3" t="n">
-        <v>20</v>
-      </c>
+      <c r="U70" s="3" t="inlineStr"/>
       <c r="V70" t="inlineStr"/>
       <c r="W70" s="3" t="n">
         <v>134.8</v>
@@ -5884,9 +5698,7 @@
       <c r="T71" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="U71" s="3" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U71" s="3" t="inlineStr"/>
       <c r="V71" t="inlineStr"/>
       <c r="W71" s="3" t="n">
         <v>134.1</v>
@@ -5959,9 +5771,7 @@
       <c r="T72" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="U72" s="3" t="n">
-        <v>22.2</v>
-      </c>
+      <c r="U72" s="3" t="inlineStr"/>
       <c r="V72" t="inlineStr"/>
       <c r="W72" s="3" t="n">
         <v>133.2</v>
@@ -6034,9 +5844,7 @@
       <c r="T73" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="U73" s="3" t="n">
-        <v>19.8</v>
-      </c>
+      <c r="U73" s="3" t="inlineStr"/>
       <c r="V73" t="inlineStr"/>
       <c r="W73" s="3" t="n">
         <v>132.2</v>
@@ -6113,9 +5921,7 @@
       <c r="T74" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="U74" s="3" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U74" s="3" t="inlineStr"/>
       <c r="V74" t="inlineStr"/>
       <c r="W74" s="3" t="n">
         <v>131.5</v>
@@ -6188,9 +5994,7 @@
       <c r="T75" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="U75" s="1" t="n">
-        <v>26.9</v>
-      </c>
+      <c r="U75" s="3" t="inlineStr"/>
       <c r="V75" t="inlineStr"/>
       <c r="W75" s="3" t="n">
         <v>128.4</v>
@@ -6267,9 +6071,7 @@
       <c r="T76" s="6" t="n">
         <v>18.4</v>
       </c>
-      <c r="U76" s="6" t="n">
-        <v>18.7</v>
-      </c>
+      <c r="U76" s="6" t="inlineStr"/>
       <c r="V76" s="4" t="inlineStr"/>
       <c r="W76" s="6" t="n">
         <v>137.7</v>
@@ -6342,9 +6144,7 @@
       <c r="T77" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="U77" s="3" t="n">
-        <v>15.4</v>
-      </c>
+      <c r="U77" s="3" t="inlineStr"/>
       <c r="V77" t="inlineStr"/>
       <c r="W77" s="3" t="n">
         <v>140.5</v>
@@ -6417,9 +6217,7 @@
       <c r="T78" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="U78" s="3" t="n">
-        <v>15.2</v>
-      </c>
+      <c r="U78" s="3" t="inlineStr"/>
       <c r="V78" t="inlineStr"/>
       <c r="W78" s="3" t="n">
         <v>138.9</v>
@@ -6492,9 +6290,7 @@
       <c r="T79" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="U79" s="3" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U79" s="3" t="inlineStr"/>
       <c r="V79" t="inlineStr"/>
       <c r="W79" s="3" t="n">
         <v>140.9</v>
@@ -6567,9 +6363,7 @@
       <c r="T80" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="U80" s="3" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="U80" s="3" t="inlineStr"/>
       <c r="V80" t="inlineStr"/>
       <c r="W80" s="3" t="n">
         <v>136</v>
@@ -6642,9 +6436,7 @@
       <c r="T81" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="U81" s="3" t="n">
-        <v>13.5</v>
-      </c>
+      <c r="U81" s="3" t="inlineStr"/>
       <c r="V81" t="inlineStr"/>
       <c r="W81" s="3" t="n">
         <v>135.9</v>
@@ -6717,9 +6509,7 @@
       <c r="T82" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="U82" s="3" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U82" s="3" t="inlineStr"/>
       <c r="V82" t="inlineStr"/>
       <c r="W82" s="3" t="n">
         <v>137.3</v>
@@ -6792,9 +6582,7 @@
       <c r="T83" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="U83" s="3" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U83" s="3" t="inlineStr"/>
       <c r="V83" t="inlineStr"/>
       <c r="W83" s="3" t="n">
         <v>137.3</v>
@@ -6867,9 +6655,7 @@
       <c r="T84" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="U84" s="3" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="U84" s="3" t="inlineStr"/>
       <c r="V84" t="inlineStr"/>
       <c r="W84" s="3" t="n">
         <v>139</v>
@@ -6942,9 +6728,7 @@
       <c r="T85" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="U85" s="3" t="n">
-        <v>21.7</v>
-      </c>
+      <c r="U85" s="3" t="inlineStr"/>
       <c r="V85" t="inlineStr"/>
       <c r="W85" s="3" t="n">
         <v>139.3</v>
@@ -7017,9 +6801,7 @@
       <c r="T86" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="U86" s="3" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U86" s="3" t="inlineStr"/>
       <c r="V86" t="inlineStr"/>
       <c r="W86" s="3" t="n">
         <v>140.9</v>
@@ -7092,9 +6874,7 @@
       <c r="T87" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="U87" s="3" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="U87" s="3" t="inlineStr"/>
       <c r="V87" t="inlineStr"/>
       <c r="W87" s="3" t="n">
         <v>137.6</v>
@@ -7167,9 +6947,7 @@
       <c r="T88" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="U88" s="3" t="n">
-        <v>17.4</v>
-      </c>
+      <c r="U88" s="3" t="inlineStr"/>
       <c r="V88" t="inlineStr"/>
       <c r="W88" s="3" t="n">
         <v>137.3</v>
@@ -7242,9 +7020,7 @@
       <c r="T89" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="U89" s="3" t="n">
-        <v>17</v>
-      </c>
+      <c r="U89" s="3" t="inlineStr"/>
       <c r="V89" t="inlineStr"/>
       <c r="W89" s="3" t="n">
         <v>138.2</v>
@@ -7317,9 +7093,7 @@
       <c r="T90" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="U90" s="3" t="n">
-        <v>13.3</v>
-      </c>
+      <c r="U90" s="3" t="inlineStr"/>
       <c r="V90" t="inlineStr"/>
       <c r="W90" s="3" t="n">
         <v>141</v>
@@ -7392,9 +7166,7 @@
       <c r="T91" s="3" t="n">
         <v>17.7</v>
       </c>
-      <c r="U91" s="3" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U91" s="3" t="inlineStr"/>
       <c r="V91" t="inlineStr"/>
       <c r="W91" s="3" t="n">
         <v>141.6</v>
@@ -7467,9 +7239,7 @@
       <c r="T92" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="U92" s="3" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U92" s="3" t="inlineStr"/>
       <c r="V92" t="inlineStr"/>
       <c r="W92" s="3" t="n">
         <v>137.5</v>
@@ -7542,9 +7312,7 @@
       <c r="T93" s="3" t="n">
         <v>18.5</v>
       </c>
-      <c r="U93" s="3" t="n">
-        <v>19</v>
-      </c>
+      <c r="U93" s="3" t="inlineStr"/>
       <c r="V93" t="inlineStr"/>
       <c r="W93" s="3" t="n">
         <v>140.1</v>
@@ -7617,9 +7385,7 @@
       <c r="T94" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="U94" s="3" t="n">
-        <v>14.3</v>
-      </c>
+      <c r="U94" s="3" t="inlineStr"/>
       <c r="V94" t="inlineStr"/>
       <c r="W94" s="3" t="n">
         <v>138.9</v>
@@ -7692,9 +7458,7 @@
       <c r="T95" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="U95" s="3" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U95" s="3" t="inlineStr"/>
       <c r="V95" t="inlineStr"/>
       <c r="W95" s="3" t="n">
         <v>139.2</v>
@@ -7767,9 +7531,7 @@
       <c r="T96" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="U96" s="3" t="n">
-        <v>15.9</v>
-      </c>
+      <c r="U96" s="3" t="inlineStr"/>
       <c r="V96" t="inlineStr"/>
       <c r="W96" s="3" t="n">
         <v>141.2</v>
@@ -7842,9 +7604,7 @@
       <c r="T97" s="3" t="n">
         <v>17.3</v>
       </c>
-      <c r="U97" s="3" t="n">
-        <v>13.9</v>
-      </c>
+      <c r="U97" s="3" t="inlineStr"/>
       <c r="V97" t="inlineStr"/>
       <c r="W97" s="3" t="n">
         <v>141.4</v>
@@ -7917,9 +7677,7 @@
       <c r="T98" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="U98" s="3" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U98" s="3" t="inlineStr"/>
       <c r="V98" t="inlineStr"/>
       <c r="W98" s="3" t="n">
         <v>145.6</v>
@@ -7992,9 +7750,7 @@
       <c r="T99" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="U99" s="3" t="n">
-        <v>21.7</v>
-      </c>
+      <c r="U99" s="3" t="inlineStr"/>
       <c r="V99" t="inlineStr"/>
       <c r="W99" s="3" t="n">
         <v>149.6</v>
@@ -8067,9 +7823,7 @@
       <c r="T100" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="U100" s="3" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U100" s="3" t="inlineStr"/>
       <c r="V100" t="inlineStr"/>
       <c r="W100" s="2" t="n">
         <v>156.6</v>
@@ -8142,9 +7896,7 @@
       <c r="T101" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="U101" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="U101" s="3" t="inlineStr"/>
       <c r="V101" t="inlineStr"/>
       <c r="W101" s="3" t="n">
         <v>154.4</v>
@@ -8217,9 +7969,7 @@
       <c r="T102" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="U102" s="3" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U102" s="3" t="inlineStr"/>
       <c r="V102" t="inlineStr"/>
       <c r="W102" s="3" t="n">
         <v>148.4</v>
@@ -8292,9 +8042,7 @@
       <c r="T103" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="U103" s="3" t="n">
-        <v>18.4</v>
-      </c>
+      <c r="U103" s="3" t="inlineStr"/>
       <c r="V103" t="inlineStr"/>
       <c r="W103" s="3" t="n">
         <v>149.2</v>
@@ -8367,9 +8115,7 @@
       <c r="T104" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="U104" s="3" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="U104" s="3" t="inlineStr"/>
       <c r="V104" t="inlineStr"/>
       <c r="W104" s="3" t="n">
         <v>154.8</v>
@@ -8446,9 +8192,7 @@
       <c r="T105" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="U105" s="3" t="n">
-        <v>11.2</v>
-      </c>
+      <c r="U105" s="3" t="inlineStr"/>
       <c r="V105" t="inlineStr"/>
       <c r="W105" s="2" t="n">
         <v>155</v>
@@ -8521,9 +8265,7 @@
       <c r="T106" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="U106" s="3" t="n">
-        <v>10.4</v>
-      </c>
+      <c r="U106" s="3" t="inlineStr"/>
       <c r="V106" t="inlineStr"/>
       <c r="W106" s="3" t="n">
         <v>152.2</v>
@@ -8596,9 +8338,7 @@
       <c r="T107" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="U107" s="3" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U107" s="3" t="inlineStr"/>
       <c r="V107" t="inlineStr"/>
       <c r="W107" s="3" t="n">
         <v>147.5</v>
@@ -8675,9 +8415,7 @@
       <c r="T108" s="3" t="n">
         <v>16.3</v>
       </c>
-      <c r="U108" s="3" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U108" s="3" t="inlineStr"/>
       <c r="V108" t="inlineStr"/>
       <c r="W108" s="3" t="n">
         <v>143.4</v>
@@ -8750,9 +8488,7 @@
       <c r="T109" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="U109" s="3" t="n">
-        <v>10.2</v>
-      </c>
+      <c r="U109" s="3" t="inlineStr"/>
       <c r="V109" t="inlineStr"/>
       <c r="W109" s="3" t="n">
         <v>139.6</v>
@@ -8825,9 +8561,7 @@
       <c r="T110" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="U110" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="U110" s="3" t="inlineStr"/>
       <c r="V110" t="inlineStr"/>
       <c r="W110" s="3" t="n">
         <v>140.1</v>
@@ -8900,9 +8634,7 @@
       <c r="T111" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="U111" s="3" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U111" s="3" t="inlineStr"/>
       <c r="V111" t="inlineStr"/>
       <c r="W111" s="3" t="n">
         <v>139.3</v>
@@ -8979,9 +8711,7 @@
       <c r="T112" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U112" s="3" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U112" s="3" t="inlineStr"/>
       <c r="V112" t="inlineStr"/>
       <c r="W112" s="3" t="n">
         <v>141.4</v>
@@ -9054,9 +8784,7 @@
       <c r="T113" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="U113" s="3" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U113" s="3" t="inlineStr"/>
       <c r="V113" t="inlineStr"/>
       <c r="W113" s="3" t="n">
         <v>138</v>
@@ -9133,9 +8861,7 @@
       <c r="T114" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="U114" s="3" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="U114" s="3" t="inlineStr"/>
       <c r="V114" t="inlineStr"/>
       <c r="W114" s="3" t="n">
         <v>140.8</v>
@@ -9208,9 +8934,7 @@
       <c r="T115" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="U115" s="3" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="U115" s="3" t="inlineStr"/>
       <c r="V115" t="inlineStr"/>
       <c r="W115" s="3" t="n">
         <v>141.8</v>
@@ -9283,9 +9007,7 @@
       <c r="T116" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="U116" s="3" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U116" s="3" t="inlineStr"/>
       <c r="V116" t="inlineStr"/>
       <c r="W116" s="3" t="n">
         <v>143.3</v>
@@ -9358,9 +9080,7 @@
       <c r="T117" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U117" s="3" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="U117" s="3" t="inlineStr"/>
       <c r="V117" t="inlineStr"/>
       <c r="W117" s="3" t="n">
         <v>145</v>
@@ -9437,9 +9157,7 @@
       <c r="T118" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="U118" s="3" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U118" s="3" t="inlineStr"/>
       <c r="V118" t="inlineStr"/>
       <c r="W118" s="3" t="n">
         <v>147</v>
@@ -9512,9 +9230,7 @@
       <c r="T119" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="U119" s="3" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U119" s="3" t="inlineStr"/>
       <c r="V119" t="inlineStr"/>
       <c r="W119" s="3" t="n">
         <v>143.7</v>
@@ -9587,9 +9303,7 @@
       <c r="T120" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="U120" s="3" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U120" s="3" t="inlineStr"/>
       <c r="V120" t="inlineStr"/>
       <c r="W120" s="3" t="n">
         <v>146.7</v>
@@ -9662,9 +9376,7 @@
       <c r="T121" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="U121" s="3" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U121" s="3" t="inlineStr"/>
       <c r="V121" t="inlineStr"/>
       <c r="W121" s="3" t="n">
         <v>151.1</v>
@@ -9737,9 +9449,7 @@
       <c r="T122" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U122" s="3" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U122" s="3" t="inlineStr"/>
       <c r="V122" t="inlineStr"/>
       <c r="W122" s="3" t="n">
         <v>150.4</v>
@@ -9812,9 +9522,7 @@
       <c r="T123" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="U123" s="3" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U123" s="3" t="inlineStr"/>
       <c r="V123" t="inlineStr"/>
       <c r="W123" s="3" t="n">
         <v>154.8</v>
@@ -9887,9 +9595,7 @@
       <c r="T124" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="U124" s="3" t="n">
-        <v>8.4</v>
-      </c>
+      <c r="U124" s="3" t="inlineStr"/>
       <c r="V124" t="inlineStr"/>
       <c r="W124" s="3" t="n">
         <v>153.4</v>
@@ -9962,9 +9668,7 @@
       <c r="T125" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="U125" s="3" t="n">
-        <v>10</v>
-      </c>
+      <c r="U125" s="3" t="inlineStr"/>
       <c r="V125" t="inlineStr"/>
       <c r="W125" s="2" t="n">
         <v>159.3</v>
@@ -10037,9 +9741,7 @@
       <c r="T126" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="U126" s="3" t="n">
-        <v>10</v>
-      </c>
+      <c r="U126" s="3" t="inlineStr"/>
       <c r="V126" t="inlineStr"/>
       <c r="W126" s="2" t="n">
         <v>159.4</v>
@@ -10116,9 +9818,7 @@
       <c r="T127" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="U127" s="3" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U127" s="3" t="inlineStr"/>
       <c r="V127" t="inlineStr"/>
       <c r="W127" s="3" t="n">
         <v>145.6</v>
@@ -10195,9 +9895,7 @@
       <c r="T128" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="U128" s="3" t="n">
-        <v>7.9</v>
-      </c>
+      <c r="U128" s="3" t="inlineStr"/>
       <c r="V128" t="inlineStr"/>
       <c r="W128" s="3" t="n">
         <v>147.6</v>
@@ -10270,9 +9968,7 @@
       <c r="T129" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="U129" s="3" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U129" s="3" t="inlineStr"/>
       <c r="V129" t="inlineStr"/>
       <c r="W129" s="3" t="n">
         <v>149.1</v>
@@ -10345,9 +10041,7 @@
       <c r="T130" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="U130" s="3" t="n">
-        <v>13.8</v>
-      </c>
+      <c r="U130" s="3" t="inlineStr"/>
       <c r="V130" t="inlineStr"/>
       <c r="W130" s="3" t="n">
         <v>154.1</v>
@@ -10420,9 +10114,7 @@
       <c r="T131" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="U131" s="3" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U131" s="3" t="inlineStr"/>
       <c r="V131" t="inlineStr"/>
       <c r="W131" s="3" t="n">
         <v>152.3</v>
@@ -10495,9 +10187,7 @@
       <c r="T132" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="U132" s="3" t="n">
-        <v>20</v>
-      </c>
+      <c r="U132" s="3" t="inlineStr"/>
       <c r="V132" t="inlineStr"/>
       <c r="W132" s="2" t="n">
         <v>155.5</v>
@@ -10570,9 +10260,7 @@
       <c r="T133" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="U133" s="3" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U133" s="3" t="inlineStr"/>
       <c r="V133" t="inlineStr"/>
       <c r="W133" s="2" t="n">
         <v>159.3</v>
@@ -10645,9 +10333,7 @@
       <c r="T134" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="U134" s="3" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U134" s="3" t="inlineStr"/>
       <c r="V134" t="inlineStr"/>
       <c r="W134" s="3" t="n">
         <v>149.9</v>
@@ -10720,9 +10406,7 @@
       <c r="T135" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="U135" s="3" t="n">
-        <v>11.4</v>
-      </c>
+      <c r="U135" s="3" t="inlineStr"/>
       <c r="V135" t="inlineStr"/>
       <c r="W135" s="3" t="n">
         <v>149.7</v>
@@ -10795,9 +10479,7 @@
       <c r="T136" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="U136" s="3" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="U136" s="3" t="inlineStr"/>
       <c r="V136" t="inlineStr"/>
       <c r="W136" s="3" t="n">
         <v>147</v>
@@ -10870,9 +10552,7 @@
       <c r="T137" s="3" t="n">
         <v>15.1</v>
       </c>
-      <c r="U137" s="3" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U137" s="3" t="inlineStr"/>
       <c r="V137" t="inlineStr"/>
       <c r="W137" s="3" t="n">
         <v>147.5</v>
@@ -10949,9 +10629,7 @@
       <c r="T138" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="U138" s="3" t="n">
-        <v>15.9</v>
-      </c>
+      <c r="U138" s="3" t="inlineStr"/>
       <c r="V138" t="inlineStr"/>
       <c r="W138" s="3" t="n">
         <v>148.6</v>
@@ -11024,9 +10702,7 @@
       <c r="T139" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="U139" s="3" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U139" s="3" t="inlineStr"/>
       <c r="V139" t="inlineStr"/>
       <c r="W139" s="3" t="n">
         <v>151.4</v>
@@ -11099,9 +10775,7 @@
       <c r="T140" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="U140" s="3" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U140" s="3" t="inlineStr"/>
       <c r="V140" t="inlineStr"/>
       <c r="W140" s="3" t="n">
         <v>153.1</v>
@@ -11178,9 +10852,7 @@
       <c r="T141" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="U141" s="3" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="U141" s="3" t="inlineStr"/>
       <c r="V141" t="inlineStr"/>
       <c r="W141" s="3" t="n">
         <v>150.6</v>
@@ -11253,9 +10925,7 @@
       <c r="T142" s="3" t="n">
         <v>15.1</v>
       </c>
-      <c r="U142" s="3" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U142" s="3" t="inlineStr"/>
       <c r="V142" t="inlineStr"/>
       <c r="W142" s="3" t="n">
         <v>153.8</v>
@@ -11328,9 +10998,7 @@
       <c r="T143" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="U143" s="3" t="n">
-        <v>7.8</v>
-      </c>
+      <c r="U143" s="3" t="inlineStr"/>
       <c r="V143" t="inlineStr"/>
       <c r="W143" s="3" t="n">
         <v>153.9</v>
@@ -11403,9 +11071,7 @@
       <c r="T144" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="U144" s="3" t="n">
-        <v>10.2</v>
-      </c>
+      <c r="U144" s="3" t="inlineStr"/>
       <c r="V144" t="inlineStr"/>
       <c r="W144" s="3" t="n">
         <v>153.2</v>
@@ -11478,9 +11144,7 @@
       <c r="T145" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="U145" s="3" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U145" s="3" t="inlineStr"/>
       <c r="V145" t="inlineStr"/>
       <c r="W145" s="3" t="n">
         <v>144.6</v>
@@ -11557,9 +11221,7 @@
       <c r="T146" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="U146" s="3" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="U146" s="3" t="inlineStr"/>
       <c r="V146" t="inlineStr"/>
       <c r="W146" s="3" t="n">
         <v>144.3</v>
@@ -11601,7 +11263,7 @@
         <v>308.13</v>
       </c>
       <c r="K147" t="n">
-        <v>308.39</v>
+        <v>308.4</v>
       </c>
       <c r="L147" t="n">
         <v>300.06</v>
@@ -11632,9 +11294,7 @@
       <c r="T147" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="U147" s="3" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U147" s="3" t="inlineStr"/>
       <c r="V147" t="inlineStr"/>
       <c r="W147" s="3" t="n">
         <v>146.4</v>
@@ -11707,9 +11367,7 @@
       <c r="T148" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="U148" s="3" t="n">
-        <v>8.1</v>
-      </c>
+      <c r="U148" s="3" t="inlineStr"/>
       <c r="V148" t="inlineStr"/>
       <c r="W148" s="3" t="n">
         <v>150</v>
@@ -11782,9 +11440,7 @@
       <c r="T149" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="U149" s="3" t="n">
-        <v>7.8</v>
-      </c>
+      <c r="U149" s="3" t="inlineStr"/>
       <c r="V149" t="inlineStr"/>
       <c r="W149" s="2" t="n">
         <v>156.5</v>
@@ -11857,9 +11513,7 @@
       <c r="T150" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="U150" s="3" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U150" s="3" t="inlineStr"/>
       <c r="V150" t="inlineStr"/>
       <c r="W150" s="3" t="n">
         <v>150.9</v>
@@ -11932,9 +11586,7 @@
       <c r="T151" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="U151" s="3" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U151" s="3" t="inlineStr"/>
       <c r="V151" t="inlineStr"/>
       <c r="W151" s="3" t="n">
         <v>152.5</v>
@@ -12007,9 +11659,7 @@
       <c r="T152" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="U152" s="3" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="U152" s="3" t="inlineStr"/>
       <c r="V152" t="inlineStr"/>
       <c r="W152" s="3" t="n">
         <v>152.1</v>
@@ -12082,9 +11732,7 @@
       <c r="T153" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="U153" s="3" t="n">
-        <v>11.4</v>
-      </c>
+      <c r="U153" s="3" t="inlineStr"/>
       <c r="V153" t="inlineStr"/>
       <c r="W153" s="3" t="n">
         <v>151.5</v>
@@ -12157,9 +11805,7 @@
       <c r="T154" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U154" s="3" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U154" s="3" t="inlineStr"/>
       <c r="V154" t="inlineStr"/>
       <c r="W154" s="3" t="n">
         <v>150.2</v>
@@ -12232,9 +11878,7 @@
       <c r="T155" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="U155" s="3" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U155" s="3" t="inlineStr"/>
       <c r="V155" t="inlineStr"/>
       <c r="W155" s="3" t="n">
         <v>154</v>
@@ -12307,9 +11951,7 @@
       <c r="T156" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="U156" s="3" t="n">
-        <v>10</v>
-      </c>
+      <c r="U156" s="3" t="inlineStr"/>
       <c r="V156" t="inlineStr"/>
       <c r="W156" s="3" t="n">
         <v>148.2</v>
@@ -12382,9 +12024,7 @@
       <c r="T157" s="3" t="n">
         <v>15.1</v>
       </c>
-      <c r="U157" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
+      <c r="U157" s="3" t="inlineStr"/>
       <c r="V157" t="inlineStr"/>
       <c r="W157" s="3" t="n">
         <v>148.8</v>
@@ -12457,9 +12097,7 @@
       <c r="T158" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="U158" s="3" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U158" s="3" t="inlineStr"/>
       <c r="V158" t="inlineStr"/>
       <c r="W158" s="3" t="n">
         <v>150.9</v>
@@ -12532,9 +12170,7 @@
       <c r="T159" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="U159" s="3" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="U159" s="3" t="inlineStr"/>
       <c r="V159" t="inlineStr"/>
       <c r="W159" s="3" t="n">
         <v>151.9</v>
@@ -12607,9 +12243,7 @@
       <c r="T160" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="U160" s="3" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U160" s="3" t="inlineStr"/>
       <c r="V160" t="inlineStr"/>
       <c r="W160" s="3" t="n">
         <v>147.6</v>
@@ -12682,9 +12316,7 @@
       <c r="T161" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="U161" s="3" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U161" s="3" t="inlineStr"/>
       <c r="V161" t="inlineStr"/>
       <c r="W161" s="3" t="n">
         <v>149.5</v>
@@ -12757,9 +12389,7 @@
       <c r="T162" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="U162" s="3" t="n">
-        <v>9</v>
-      </c>
+      <c r="U162" s="3" t="inlineStr"/>
       <c r="V162" t="inlineStr"/>
       <c r="W162" s="3" t="n">
         <v>152.1</v>
@@ -12832,9 +12462,7 @@
       <c r="T163" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U163" s="3" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U163" s="3" t="inlineStr"/>
       <c r="V163" t="inlineStr"/>
       <c r="W163" s="3" t="n">
         <v>148.2</v>
@@ -12907,9 +12535,7 @@
       <c r="T164" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="U164" s="3" t="n">
-        <v>14.8</v>
-      </c>
+      <c r="U164" s="3" t="inlineStr"/>
       <c r="V164" t="inlineStr"/>
       <c r="W164" s="3" t="n">
         <v>146.4</v>
@@ -12982,9 +12608,7 @@
       <c r="T165" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="U165" s="3" t="n">
-        <v>14.4</v>
-      </c>
+      <c r="U165" s="3" t="inlineStr"/>
       <c r="V165" t="inlineStr"/>
       <c r="W165" s="3" t="n">
         <v>148.2</v>
@@ -13057,9 +12681,7 @@
       <c r="T166" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="U166" s="3" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U166" s="3" t="inlineStr"/>
       <c r="V166" t="inlineStr"/>
       <c r="W166" s="3" t="n">
         <v>147</v>
@@ -13132,9 +12754,7 @@
       <c r="T167" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="U167" s="3" t="n">
-        <v>9.1</v>
-      </c>
+      <c r="U167" s="3" t="inlineStr"/>
       <c r="V167" t="inlineStr"/>
       <c r="W167" s="3" t="n">
         <v>145.5</v>
@@ -13207,9 +12827,7 @@
       <c r="T168" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="U168" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="U168" s="3" t="inlineStr"/>
       <c r="V168" t="inlineStr"/>
       <c r="W168" s="3" t="n">
         <v>146.5</v>
@@ -13282,9 +12900,7 @@
       <c r="T169" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="U169" s="3" t="n">
-        <v>9.4</v>
-      </c>
+      <c r="U169" s="3" t="inlineStr"/>
       <c r="V169" t="inlineStr"/>
       <c r="W169" s="3" t="n">
         <v>145.9</v>
@@ -13357,9 +12973,7 @@
       <c r="T170" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="U170" s="3" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U170" s="3" t="inlineStr"/>
       <c r="V170" t="inlineStr"/>
       <c r="W170" s="3" t="n">
         <v>145.9</v>
@@ -13432,9 +13046,7 @@
       <c r="T171" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="U171" s="3" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="U171" s="3" t="inlineStr"/>
       <c r="V171" t="inlineStr"/>
       <c r="W171" s="3" t="n">
         <v>141.5</v>
@@ -13507,9 +13119,7 @@
       <c r="T172" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="U172" s="3" t="n">
-        <v>10.2</v>
-      </c>
+      <c r="U172" s="3" t="inlineStr"/>
       <c r="V172" t="inlineStr"/>
       <c r="W172" s="3" t="n">
         <v>143</v>
@@ -13582,9 +13192,7 @@
       <c r="T173" s="3" t="n">
         <v>16.3</v>
       </c>
-      <c r="U173" s="3" t="n">
-        <v>12</v>
-      </c>
+      <c r="U173" s="3" t="inlineStr"/>
       <c r="V173" t="inlineStr"/>
       <c r="W173" s="3" t="n">
         <v>143.4</v>
@@ -13657,9 +13265,7 @@
       <c r="T174" s="3" t="n">
         <v>16.3</v>
       </c>
-      <c r="U174" s="3" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="U174" s="3" t="inlineStr"/>
       <c r="V174" t="inlineStr"/>
       <c r="W174" s="3" t="n">
         <v>143.7</v>
@@ -13732,9 +13338,7 @@
       <c r="T175" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="U175" s="3" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U175" s="3" t="inlineStr"/>
       <c r="V175" t="inlineStr"/>
       <c r="W175" s="3" t="n">
         <v>145.9</v>
@@ -13807,9 +13411,7 @@
       <c r="T176" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="U176" s="3" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="U176" s="3" t="inlineStr"/>
       <c r="V176" t="inlineStr"/>
       <c r="W176" s="3" t="n">
         <v>144.6</v>
@@ -13882,9 +13484,7 @@
       <c r="T177" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U177" s="3" t="n">
-        <v>8.4</v>
-      </c>
+      <c r="U177" s="3" t="inlineStr"/>
       <c r="V177" t="inlineStr"/>
       <c r="W177" s="3" t="n">
         <v>142.5</v>
@@ -13957,9 +13557,7 @@
       <c r="T178" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="U178" s="3" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="U178" s="3" t="inlineStr"/>
       <c r="V178" t="inlineStr"/>
       <c r="W178" s="3" t="n">
         <v>145.2</v>
@@ -14032,9 +13630,7 @@
       <c r="T179" s="3" t="n">
         <v>16.3</v>
       </c>
-      <c r="U179" s="3" t="n">
-        <v>10</v>
-      </c>
+      <c r="U179" s="3" t="inlineStr"/>
       <c r="V179" t="inlineStr"/>
       <c r="W179" s="3" t="n">
         <v>145.8</v>
@@ -14107,9 +13703,7 @@
       <c r="T180" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U180" s="3" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="U180" s="3" t="inlineStr"/>
       <c r="V180" t="inlineStr"/>
       <c r="W180" s="3" t="n">
         <v>145.3</v>
@@ -14182,9 +13776,7 @@
       <c r="T181" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="U181" s="1" t="n">
-        <v>25.7</v>
-      </c>
+      <c r="U181" s="3" t="inlineStr"/>
       <c r="V181" t="inlineStr"/>
       <c r="W181" s="3" t="n">
         <v>138.9</v>
@@ -14257,9 +13849,7 @@
       <c r="T182" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="U182" s="3" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U182" s="3" t="inlineStr"/>
       <c r="V182" t="inlineStr"/>
       <c r="W182" s="3" t="n">
         <v>142.8</v>
@@ -14332,9 +13922,7 @@
       <c r="T183" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="U183" s="3" t="n">
-        <v>17.7</v>
-      </c>
+      <c r="U183" s="3" t="inlineStr"/>
       <c r="V183" t="inlineStr"/>
       <c r="W183" s="3" t="n">
         <v>146.5</v>
@@ -14407,9 +13995,7 @@
       <c r="T184" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="U184" s="3" t="n">
-        <v>17.1</v>
-      </c>
+      <c r="U184" s="3" t="inlineStr"/>
       <c r="V184" t="inlineStr"/>
       <c r="W184" s="3" t="n">
         <v>145</v>
@@ -14482,9 +14068,7 @@
       <c r="T185" s="1" t="n">
         <v>25.3</v>
       </c>
-      <c r="U185" s="3" t="n">
-        <v>23.8</v>
-      </c>
+      <c r="U185" s="3" t="inlineStr"/>
       <c r="V185" t="inlineStr"/>
       <c r="W185" s="3" t="n">
         <v>147.1</v>
@@ -14557,9 +14141,7 @@
       <c r="T186" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="U186" s="3" t="n">
-        <v>17.9</v>
-      </c>
+      <c r="U186" s="3" t="inlineStr"/>
       <c r="V186" t="inlineStr"/>
       <c r="W186" s="3" t="n">
         <v>147.6</v>
@@ -14632,9 +14214,7 @@
       <c r="T187" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="U187" s="3" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U187" s="3" t="inlineStr"/>
       <c r="V187" t="inlineStr"/>
       <c r="W187" s="3" t="n">
         <v>151.3</v>
@@ -14707,9 +14287,7 @@
       <c r="T188" s="6" t="n">
         <v>17.9</v>
       </c>
-      <c r="U188" s="6" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U188" s="6" t="inlineStr"/>
       <c r="V188" s="4" t="inlineStr"/>
       <c r="W188" s="6" t="n">
         <v>149.9</v>
@@ -14782,9 +14360,7 @@
       <c r="T189" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="U189" s="3" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U189" s="3" t="inlineStr"/>
       <c r="V189" t="inlineStr"/>
       <c r="W189" s="3" t="n">
         <v>152.9</v>
@@ -14857,9 +14433,7 @@
       <c r="T190" s="3" t="n">
         <v>17.3</v>
       </c>
-      <c r="U190" s="3" t="n">
-        <v>13.8</v>
-      </c>
+      <c r="U190" s="3" t="inlineStr"/>
       <c r="V190" t="inlineStr"/>
       <c r="W190" s="3" t="n">
         <v>154.3</v>
@@ -14932,9 +14506,7 @@
       <c r="T191" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U191" s="3" t="n">
-        <v>14.5</v>
-      </c>
+      <c r="U191" s="3" t="inlineStr"/>
       <c r="V191" t="inlineStr"/>
       <c r="W191" s="3" t="n">
         <v>153.5</v>
@@ -15011,9 +14583,7 @@
       <c r="T192" s="6" t="n">
         <v>15.8</v>
       </c>
-      <c r="U192" s="6" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U192" s="6" t="inlineStr"/>
       <c r="V192" s="4" t="inlineStr"/>
       <c r="W192" s="6" t="n">
         <v>148.5</v>
@@ -15086,9 +14656,7 @@
       <c r="T193" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U193" s="3" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U193" s="3" t="inlineStr"/>
       <c r="V193" t="inlineStr"/>
       <c r="W193" s="3" t="n">
         <v>140.4</v>
@@ -15161,9 +14729,7 @@
       <c r="T194" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="U194" s="3" t="n">
-        <v>15.2</v>
-      </c>
+      <c r="U194" s="3" t="inlineStr"/>
       <c r="V194" t="inlineStr"/>
       <c r="W194" s="3" t="n">
         <v>139.4</v>
@@ -15236,9 +14802,7 @@
       <c r="T195" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="U195" s="3" t="n">
-        <v>14.2</v>
-      </c>
+      <c r="U195" s="3" t="inlineStr"/>
       <c r="V195" t="inlineStr"/>
       <c r="W195" s="3" t="n">
         <v>141.1</v>
@@ -15311,9 +14875,7 @@
       <c r="T196" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="U196" s="3" t="n">
-        <v>13.8</v>
-      </c>
+      <c r="U196" s="3" t="inlineStr"/>
       <c r="V196" t="inlineStr"/>
       <c r="W196" s="3" t="n">
         <v>142.8</v>
@@ -15386,9 +14948,7 @@
       <c r="T197" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="U197" s="3" t="n">
-        <v>10</v>
-      </c>
+      <c r="U197" s="3" t="inlineStr"/>
       <c r="V197" t="inlineStr"/>
       <c r="W197" s="3" t="n">
         <v>142</v>
@@ -15461,9 +15021,7 @@
       <c r="T198" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="U198" s="3" t="n">
-        <v>15.2</v>
-      </c>
+      <c r="U198" s="3" t="inlineStr"/>
       <c r="V198" t="inlineStr"/>
       <c r="W198" s="3" t="n">
         <v>144</v>
@@ -15536,9 +15094,7 @@
       <c r="T199" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="U199" s="3" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U199" s="3" t="inlineStr"/>
       <c r="V199" t="inlineStr"/>
       <c r="W199" s="3" t="n">
         <v>143.6</v>
@@ -15611,9 +15167,7 @@
       <c r="T200" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="U200" s="3" t="n">
-        <v>15.9</v>
-      </c>
+      <c r="U200" s="3" t="inlineStr"/>
       <c r="V200" t="inlineStr"/>
       <c r="W200" s="3" t="n">
         <v>143.5</v>
@@ -15686,9 +15240,7 @@
       <c r="T201" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="U201" s="3" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U201" s="3" t="inlineStr"/>
       <c r="V201" t="inlineStr"/>
       <c r="W201" s="3" t="n">
         <v>141.3</v>
@@ -15761,9 +15313,7 @@
       <c r="T202" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="U202" s="3" t="n">
-        <v>11.2</v>
-      </c>
+      <c r="U202" s="3" t="inlineStr"/>
       <c r="V202" t="inlineStr"/>
       <c r="W202" s="3" t="n">
         <v>142.9</v>
@@ -15836,9 +15386,7 @@
       <c r="T203" s="3" t="n">
         <v>17.3</v>
       </c>
-      <c r="U203" s="3" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U203" s="3" t="inlineStr"/>
       <c r="V203" t="inlineStr"/>
       <c r="W203" s="3" t="n">
         <v>143.4</v>
@@ -15911,9 +15459,7 @@
       <c r="T204" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="U204" s="3" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U204" s="3" t="inlineStr"/>
       <c r="V204" t="inlineStr"/>
       <c r="W204" s="3" t="n">
         <v>138.6</v>
@@ -15986,9 +15532,7 @@
       <c r="T205" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="U205" s="3" t="n">
-        <v>17</v>
-      </c>
+      <c r="U205" s="3" t="inlineStr"/>
       <c r="V205" t="inlineStr"/>
       <c r="W205" s="3" t="n">
         <v>142.5</v>
@@ -16061,9 +15605,7 @@
       <c r="T206" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="U206" s="3" t="n">
-        <v>18.5</v>
-      </c>
+      <c r="U206" s="3" t="inlineStr"/>
       <c r="V206" t="inlineStr"/>
       <c r="W206" s="3" t="n">
         <v>137.9</v>
@@ -16140,9 +15682,7 @@
       <c r="T207" s="3" t="n">
         <v>22.4</v>
       </c>
-      <c r="U207" s="3" t="n">
-        <v>19.4</v>
-      </c>
+      <c r="U207" s="3" t="inlineStr"/>
       <c r="V207" t="inlineStr"/>
       <c r="W207" s="3" t="n">
         <v>140.9</v>
@@ -16215,9 +15755,7 @@
       <c r="T208" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="U208" s="3" t="n">
-        <v>20.9</v>
-      </c>
+      <c r="U208" s="3" t="inlineStr"/>
       <c r="V208" t="inlineStr"/>
       <c r="W208" s="3" t="n">
         <v>143</v>
@@ -16290,9 +15828,7 @@
       <c r="T209" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="U209" s="1" t="n">
-        <v>26.9</v>
-      </c>
+      <c r="U209" s="3" t="inlineStr"/>
       <c r="V209" t="inlineStr"/>
       <c r="W209" s="3" t="n">
         <v>143.1</v>
@@ -16365,14 +15901,8 @@
       <c r="T210" s="1" t="n">
         <v>26.4</v>
       </c>
-      <c r="U210" s="1" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="V210" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U210" s="3" t="inlineStr"/>
+      <c r="V210" t="inlineStr"/>
       <c r="W210" s="3" t="n">
         <v>145</v>
       </c>
@@ -16444,9 +15974,7 @@
       <c r="T211" s="3" t="n">
         <v>23.4</v>
       </c>
-      <c r="U211" s="3" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="U211" s="3" t="inlineStr"/>
       <c r="V211" t="inlineStr"/>
       <c r="W211" s="3" t="n">
         <v>148.3</v>
@@ -16519,9 +16047,7 @@
       <c r="T212" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="U212" s="3" t="n">
-        <v>14.3</v>
-      </c>
+      <c r="U212" s="3" t="inlineStr"/>
       <c r="V212" t="inlineStr"/>
       <c r="W212" s="3" t="n">
         <v>148.6</v>
@@ -16594,9 +16120,7 @@
       <c r="T213" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="U213" s="3" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U213" s="3" t="inlineStr"/>
       <c r="V213" t="inlineStr"/>
       <c r="W213" s="3" t="n">
         <v>151.7</v>
@@ -16669,9 +16193,7 @@
       <c r="T214" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="U214" s="3" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="U214" s="3" t="inlineStr"/>
       <c r="V214" t="inlineStr"/>
       <c r="W214" s="3" t="n">
         <v>145</v>
@@ -16744,9 +16266,7 @@
       <c r="T215" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U215" s="3" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U215" s="3" t="inlineStr"/>
       <c r="V215" t="inlineStr"/>
       <c r="W215" s="3" t="n">
         <v>143</v>
@@ -16819,9 +16339,7 @@
       <c r="T216" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="U216" s="3" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U216" s="3" t="inlineStr"/>
       <c r="V216" t="inlineStr"/>
       <c r="W216" s="3" t="n">
         <v>144.9</v>
@@ -16894,9 +16412,7 @@
       <c r="T217" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="U217" s="3" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="U217" s="3" t="inlineStr"/>
       <c r="V217" t="inlineStr"/>
       <c r="W217" s="3" t="n">
         <v>144.9</v>
@@ -16969,9 +16485,7 @@
       <c r="T218" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="U218" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
+      <c r="U218" s="3" t="inlineStr"/>
       <c r="V218" t="inlineStr"/>
       <c r="W218" s="3" t="n">
         <v>149.2</v>
@@ -17044,9 +16558,7 @@
       <c r="T219" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="U219" s="3" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="U219" s="3" t="inlineStr"/>
       <c r="V219" t="inlineStr"/>
       <c r="W219" s="3" t="n">
         <v>148.9</v>
@@ -17119,9 +16631,7 @@
       <c r="T220" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="U220" s="3" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U220" s="3" t="inlineStr"/>
       <c r="V220" t="inlineStr"/>
       <c r="W220" s="3" t="n">
         <v>148.8</v>
@@ -17194,9 +16704,7 @@
       <c r="T221" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="U221" s="3" t="n">
-        <v>9.4</v>
-      </c>
+      <c r="U221" s="3" t="inlineStr"/>
       <c r="V221" t="inlineStr"/>
       <c r="W221" s="3" t="n">
         <v>150.6</v>
@@ -17269,9 +16777,7 @@
       <c r="T222" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="U222" s="3" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U222" s="3" t="inlineStr"/>
       <c r="V222" t="inlineStr"/>
       <c r="W222" s="3" t="n">
         <v>150.3</v>
@@ -17344,9 +16850,7 @@
       <c r="T223" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="U223" s="3" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U223" s="3" t="inlineStr"/>
       <c r="V223" t="inlineStr"/>
       <c r="W223" s="3" t="n">
         <v>147.6</v>
@@ -17419,9 +16923,7 @@
       <c r="T224" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="U224" s="3" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="U224" s="3" t="inlineStr"/>
       <c r="V224" t="inlineStr"/>
       <c r="W224" s="3" t="n">
         <v>148.3</v>
@@ -17494,9 +16996,7 @@
       <c r="T225" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="U225" s="3" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U225" s="3" t="inlineStr"/>
       <c r="V225" t="inlineStr"/>
       <c r="W225" s="3" t="n">
         <v>153.6</v>
@@ -17569,9 +17069,7 @@
       <c r="T226" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="U226" s="3" t="n">
-        <v>12.9</v>
-      </c>
+      <c r="U226" s="3" t="inlineStr"/>
       <c r="V226" t="inlineStr"/>
       <c r="W226" s="2" t="n">
         <v>161.9</v>
@@ -17644,9 +17142,7 @@
       <c r="T227" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="U227" s="3" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="U227" s="3" t="inlineStr"/>
       <c r="V227" t="inlineStr"/>
       <c r="W227" s="2" t="n">
         <v>157</v>
@@ -17719,9 +17215,7 @@
       <c r="T228" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="U228" s="3" t="n">
-        <v>16.9</v>
-      </c>
+      <c r="U228" s="3" t="inlineStr"/>
       <c r="V228" t="inlineStr"/>
       <c r="W228" s="3" t="n">
         <v>153.5</v>
@@ -17794,9 +17288,7 @@
       <c r="T229" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="U229" s="3" t="n">
-        <v>15.8</v>
-      </c>
+      <c r="U229" s="3" t="inlineStr"/>
       <c r="V229" t="inlineStr"/>
       <c r="W229" s="2" t="n">
         <v>155.4</v>
@@ -17869,9 +17361,7 @@
       <c r="T230" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="U230" s="3" t="n">
-        <v>10.4</v>
-      </c>
+      <c r="U230" s="3" t="inlineStr"/>
       <c r="V230" t="inlineStr"/>
       <c r="W230" s="2" t="n">
         <v>155.9</v>
@@ -17944,9 +17434,7 @@
       <c r="T231" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="U231" s="3" t="n">
-        <v>7.7</v>
-      </c>
+      <c r="U231" s="3" t="inlineStr"/>
       <c r="V231" t="inlineStr"/>
       <c r="W231" s="2" t="n">
         <v>159.9</v>
@@ -18019,9 +17507,7 @@
       <c r="T232" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="U232" s="3" t="n">
-        <v>7.6</v>
-      </c>
+      <c r="U232" s="3" t="inlineStr"/>
       <c r="V232" t="inlineStr"/>
       <c r="W232" s="2" t="n">
         <v>160.5</v>
@@ -18094,9 +17580,7 @@
       <c r="T233" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="U233" s="3" t="n">
-        <v>7.4</v>
-      </c>
+      <c r="U233" s="3" t="inlineStr"/>
       <c r="V233" t="inlineStr"/>
       <c r="W233" s="2" t="n">
         <v>160.5</v>
@@ -18169,9 +17653,7 @@
       <c r="T234" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="U234" s="3" t="n">
-        <v>7.7</v>
-      </c>
+      <c r="U234" s="3" t="inlineStr"/>
       <c r="V234" t="inlineStr"/>
       <c r="W234" s="3" t="n">
         <v>151.4</v>
@@ -18244,9 +17726,7 @@
       <c r="T235" s="6" t="n">
         <v>14.2</v>
       </c>
-      <c r="U235" s="6" t="n">
-        <v>8.800000000000001</v>
-      </c>
+      <c r="U235" s="6" t="inlineStr"/>
       <c r="V235" s="4" t="inlineStr"/>
       <c r="W235" s="6" t="n">
         <v>150.5</v>
@@ -18319,9 +17799,7 @@
       <c r="T236" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="U236" s="3" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U236" s="3" t="inlineStr"/>
       <c r="V236" t="inlineStr"/>
       <c r="W236" s="3" t="n">
         <v>148.3</v>
@@ -18398,9 +17876,7 @@
       <c r="T237" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="U237" s="3" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="U237" s="3" t="inlineStr"/>
       <c r="V237" t="inlineStr"/>
       <c r="W237" s="3" t="n">
         <v>148.7</v>
@@ -18473,9 +17949,7 @@
       <c r="T238" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="U238" s="3" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U238" s="3" t="inlineStr"/>
       <c r="V238" t="inlineStr"/>
       <c r="W238" s="3" t="n">
         <v>141.9</v>
@@ -18548,9 +18022,7 @@
       <c r="T239" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="U239" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
+      <c r="U239" s="3" t="inlineStr"/>
       <c r="V239" t="inlineStr"/>
       <c r="W239" s="3" t="n">
         <v>142.4</v>
@@ -18623,9 +18095,7 @@
       <c r="T240" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="U240" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="U240" s="3" t="inlineStr"/>
       <c r="V240" t="inlineStr"/>
       <c r="W240" s="3" t="n">
         <v>146.2</v>
@@ -18698,9 +18168,7 @@
       <c r="T241" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="U241" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
+      <c r="U241" s="3" t="inlineStr"/>
       <c r="V241" t="inlineStr"/>
       <c r="W241" s="3" t="n">
         <v>143.6</v>
@@ -18773,9 +18241,7 @@
       <c r="T242" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="U242" s="3" t="n">
-        <v>13.6</v>
-      </c>
+      <c r="U242" s="3" t="inlineStr"/>
       <c r="V242" t="inlineStr"/>
       <c r="W242" s="3" t="n">
         <v>147.1</v>
@@ -18848,9 +18314,7 @@
       <c r="T243" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="U243" s="3" t="n">
-        <v>8.5</v>
-      </c>
+      <c r="U243" s="3" t="inlineStr"/>
       <c r="V243" t="inlineStr"/>
       <c r="W243" s="3" t="n">
         <v>146</v>
@@ -18923,9 +18387,7 @@
       <c r="T244" s="3" t="n">
         <v>15.1</v>
       </c>
-      <c r="U244" s="3" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="U244" s="3" t="inlineStr"/>
       <c r="V244" t="inlineStr"/>
       <c r="W244" s="3" t="n">
         <v>149.8</v>
@@ -18998,9 +18460,7 @@
       <c r="T245" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="U245" s="3" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U245" s="3" t="inlineStr"/>
       <c r="V245" t="inlineStr"/>
       <c r="W245" s="3" t="n">
         <v>151.6</v>
@@ -19073,9 +18533,7 @@
       <c r="T246" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="U246" s="3" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U246" s="3" t="inlineStr"/>
       <c r="V246" t="inlineStr"/>
       <c r="W246" s="3" t="n">
         <v>152.5</v>
@@ -19148,9 +18606,7 @@
       <c r="T247" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="U247" s="3" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U247" s="3" t="inlineStr"/>
       <c r="V247" t="inlineStr"/>
       <c r="W247" s="3" t="n">
         <v>151.6</v>
@@ -19223,9 +18679,7 @@
       <c r="T248" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="U248" s="3" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U248" s="3" t="inlineStr"/>
       <c r="V248" t="inlineStr"/>
       <c r="W248" s="3" t="n">
         <v>153.6</v>
@@ -19298,9 +18752,7 @@
       <c r="T249" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="U249" s="3" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U249" s="3" t="inlineStr"/>
       <c r="V249" t="inlineStr"/>
       <c r="W249" s="2" t="n">
         <v>155</v>
@@ -19373,9 +18825,7 @@
       <c r="T250" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="U250" s="3" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U250" s="3" t="inlineStr"/>
       <c r="V250" t="inlineStr"/>
       <c r="W250" s="3" t="n">
         <v>144.4</v>
@@ -19448,9 +18898,7 @@
       <c r="T251" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="U251" s="3" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U251" s="3" t="inlineStr"/>
       <c r="V251" t="inlineStr"/>
       <c r="W251" s="3" t="n">
         <v>141.3</v>
@@ -19523,9 +18971,7 @@
       <c r="T252" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="U252" s="3" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U252" s="3" t="inlineStr"/>
       <c r="V252" t="inlineStr"/>
       <c r="W252" s="3" t="n">
         <v>144</v>
@@ -19598,9 +19044,7 @@
       <c r="T253" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="U253" s="3" t="n">
-        <v>9</v>
-      </c>
+      <c r="U253" s="3" t="inlineStr"/>
       <c r="V253" t="inlineStr"/>
       <c r="W253" s="3" t="n">
         <v>148.1</v>
@@ -19673,9 +19117,7 @@
       <c r="T254" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U254" s="3" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U254" s="3" t="inlineStr"/>
       <c r="V254" t="inlineStr"/>
       <c r="W254" s="3" t="n">
         <v>147.2</v>
@@ -19748,9 +19190,7 @@
       <c r="T255" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U255" s="3" t="n">
-        <v>13.2</v>
-      </c>
+      <c r="U255" s="3" t="inlineStr"/>
       <c r="V255" t="inlineStr"/>
       <c r="W255" s="3" t="n">
         <v>145</v>
@@ -19823,9 +19263,7 @@
       <c r="T256" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="U256" s="3" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U256" s="3" t="inlineStr"/>
       <c r="V256" t="inlineStr"/>
       <c r="W256" s="3" t="n">
         <v>143.7</v>
@@ -19898,9 +19336,7 @@
       <c r="T257" s="6" t="n">
         <v>17.4</v>
       </c>
-      <c r="U257" s="6" t="n">
-        <v>16.4</v>
-      </c>
+      <c r="U257" s="6" t="inlineStr"/>
       <c r="V257" s="4" t="inlineStr"/>
       <c r="W257" s="6" t="n">
         <v>143.6</v>
@@ -19977,9 +19413,7 @@
       <c r="T258" s="6" t="n">
         <v>16.3</v>
       </c>
-      <c r="U258" s="6" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U258" s="6" t="inlineStr"/>
       <c r="V258" s="4" t="inlineStr"/>
       <c r="W258" s="6" t="n">
         <v>146.6</v>
@@ -20052,9 +19486,7 @@
       <c r="T259" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="U259" s="3" t="n">
-        <v>14.5</v>
-      </c>
+      <c r="U259" s="3" t="inlineStr"/>
       <c r="V259" t="inlineStr"/>
       <c r="W259" s="3" t="n">
         <v>143.9</v>
@@ -20127,9 +19559,7 @@
       <c r="T260" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="U260" s="3" t="n">
-        <v>17.5</v>
-      </c>
+      <c r="U260" s="3" t="inlineStr"/>
       <c r="V260" t="inlineStr"/>
       <c r="W260" s="3" t="n">
         <v>143.2</v>
@@ -20206,9 +19636,7 @@
       <c r="T261" s="6" t="n">
         <v>21.8</v>
       </c>
-      <c r="U261" s="6" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U261" s="6" t="inlineStr"/>
       <c r="V261" s="4" t="inlineStr"/>
       <c r="W261" s="6" t="n">
         <v>137.2</v>
@@ -20281,9 +19709,7 @@
       <c r="T262" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="U262" s="3" t="n">
-        <v>15</v>
-      </c>
+      <c r="U262" s="3" t="inlineStr"/>
       <c r="V262" t="inlineStr"/>
       <c r="W262" s="3" t="n">
         <v>140.3</v>
@@ -20356,9 +19782,7 @@
       <c r="T263" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="U263" s="3" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U263" s="3" t="inlineStr"/>
       <c r="V263" t="inlineStr"/>
       <c r="W263" s="3" t="n">
         <v>145.2</v>
@@ -20431,9 +19855,7 @@
       <c r="T264" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="U264" s="3" t="n">
-        <v>13.6</v>
-      </c>
+      <c r="U264" s="3" t="inlineStr"/>
       <c r="V264" t="inlineStr"/>
       <c r="W264" s="3" t="n">
         <v>145.7</v>
@@ -20506,9 +19928,7 @@
       <c r="T265" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="U265" s="3" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U265" s="3" t="inlineStr"/>
       <c r="V265" t="inlineStr"/>
       <c r="W265" s="3" t="n">
         <v>143.8</v>
@@ -20585,9 +20005,7 @@
       <c r="T266" s="6" t="n">
         <v>20.8</v>
       </c>
-      <c r="U266" s="6" t="n">
-        <v>21.5</v>
-      </c>
+      <c r="U266" s="6" t="inlineStr"/>
       <c r="V266" s="4" t="inlineStr"/>
       <c r="W266" s="6" t="n">
         <v>142.5</v>
@@ -20660,9 +20078,7 @@
       <c r="T267" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="U267" s="3" t="n">
-        <v>22.4</v>
-      </c>
+      <c r="U267" s="3" t="inlineStr"/>
       <c r="V267" t="inlineStr"/>
       <c r="W267" s="3" t="n">
         <v>139.4</v>
@@ -20739,9 +20155,7 @@
       <c r="T268" s="6" t="n">
         <v>20.3</v>
       </c>
-      <c r="U268" s="6" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U268" s="6" t="inlineStr"/>
       <c r="V268" s="4" t="inlineStr"/>
       <c r="W268" s="6" t="n">
         <v>140.3</v>
@@ -20814,9 +20228,7 @@
       <c r="T269" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="U269" s="3" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U269" s="3" t="inlineStr"/>
       <c r="V269" t="inlineStr"/>
       <c r="W269" s="3" t="n">
         <v>139.2</v>
@@ -20889,9 +20301,7 @@
       <c r="T270" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="U270" s="3" t="n">
-        <v>16.6</v>
-      </c>
+      <c r="U270" s="3" t="inlineStr"/>
       <c r="V270" t="inlineStr"/>
       <c r="W270" s="3" t="n">
         <v>141.2</v>
@@ -20964,9 +20374,7 @@
       <c r="T271" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="U271" s="3" t="n">
-        <v>17.8</v>
-      </c>
+      <c r="U271" s="3" t="inlineStr"/>
       <c r="V271" t="inlineStr"/>
       <c r="W271" s="3" t="n">
         <v>145.5</v>
@@ -21039,9 +20447,7 @@
       <c r="T272" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="U272" s="3" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U272" s="3" t="inlineStr"/>
       <c r="V272" t="inlineStr"/>
       <c r="W272" s="3" t="n">
         <v>141.4</v>
@@ -21114,9 +20520,7 @@
       <c r="T273" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="U273" s="3" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U273" s="3" t="inlineStr"/>
       <c r="V273" t="inlineStr"/>
       <c r="W273" s="3" t="n">
         <v>141.9</v>
@@ -21189,9 +20593,7 @@
       <c r="T274" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="U274" s="3" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U274" s="3" t="inlineStr"/>
       <c r="V274" t="inlineStr"/>
       <c r="W274" s="3" t="n">
         <v>146.1</v>
@@ -21264,9 +20666,7 @@
       <c r="T275" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="U275" s="3" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U275" s="3" t="inlineStr"/>
       <c r="V275" t="inlineStr"/>
       <c r="W275" s="3" t="n">
         <v>146.6</v>
@@ -21339,9 +20739,7 @@
       <c r="T276" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="U276" s="3" t="n">
-        <v>19</v>
-      </c>
+      <c r="U276" s="3" t="inlineStr"/>
       <c r="V276" t="inlineStr"/>
       <c r="W276" s="3" t="n">
         <v>146.7</v>
@@ -21414,9 +20812,7 @@
       <c r="T277" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="U277" s="3" t="n">
-        <v>16.3</v>
-      </c>
+      <c r="U277" s="3" t="inlineStr"/>
       <c r="V277" t="inlineStr"/>
       <c r="W277" s="3" t="n">
         <v>151.8</v>
@@ -21489,9 +20885,7 @@
       <c r="T278" s="6" t="n">
         <v>23.6</v>
       </c>
-      <c r="U278" s="6" t="n">
-        <v>20.3</v>
-      </c>
+      <c r="U278" s="6" t="inlineStr"/>
       <c r="V278" s="4" t="inlineStr"/>
       <c r="W278" s="6" t="n">
         <v>152.8</v>
@@ -21564,9 +20958,7 @@
       <c r="T279" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="U279" s="3" t="n">
-        <v>17.8</v>
-      </c>
+      <c r="U279" s="3" t="inlineStr"/>
       <c r="V279" t="inlineStr"/>
       <c r="W279" s="3" t="n">
         <v>152.9</v>
@@ -21643,9 +21035,7 @@
       <c r="T280" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="U280" s="3" t="n">
-        <v>21.9</v>
-      </c>
+      <c r="U280" s="3" t="inlineStr"/>
       <c r="V280" t="inlineStr"/>
       <c r="W280" s="3" t="n">
         <v>153.9</v>
@@ -21718,14 +21108,8 @@
       <c r="T281" s="1" t="n">
         <v>29.5</v>
       </c>
-      <c r="U281" s="1" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="V281" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U281" s="3" t="inlineStr"/>
+      <c r="V281" t="inlineStr"/>
       <c r="W281" s="3" t="n">
         <v>151.8</v>
       </c>
@@ -21797,9 +21181,7 @@
       <c r="T282" s="1" t="n">
         <v>25.5</v>
       </c>
-      <c r="U282" s="3" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="U282" s="3" t="inlineStr"/>
       <c r="V282" t="inlineStr"/>
       <c r="W282" s="2" t="n">
         <v>158</v>
@@ -21872,9 +21254,7 @@
       <c r="T283" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="U283" s="3" t="n">
-        <v>21.3</v>
-      </c>
+      <c r="U283" s="3" t="inlineStr"/>
       <c r="V283" t="inlineStr"/>
       <c r="W283" s="3" t="n">
         <v>154.5</v>
@@ -21947,9 +21327,7 @@
       <c r="T284" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="U284" s="3" t="n">
-        <v>19</v>
-      </c>
+      <c r="U284" s="3" t="inlineStr"/>
       <c r="V284" t="inlineStr"/>
       <c r="W284" s="3" t="n">
         <v>152.4</v>
@@ -22020,9 +21398,7 @@
       <c r="T285" s="1" t="n">
         <v>27.3</v>
       </c>
-      <c r="U285" s="3" t="n">
-        <v>24.2</v>
-      </c>
+      <c r="U285" s="3" t="inlineStr"/>
       <c r="V285" t="inlineStr"/>
       <c r="W285" s="3" t="n">
         <v>139.9</v>
@@ -22095,14 +21471,8 @@
       <c r="T286" s="1" t="n">
         <v>27.2</v>
       </c>
-      <c r="U286" s="1" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="V286" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U286" s="3" t="inlineStr"/>
+      <c r="V286" t="inlineStr"/>
       <c r="W286" s="3" t="n">
         <v>137.8</v>
       </c>
@@ -22174,9 +21544,7 @@
       <c r="T287" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="U287" s="3" t="n">
-        <v>17.4</v>
-      </c>
+      <c r="U287" s="3" t="inlineStr"/>
       <c r="V287" t="inlineStr"/>
       <c r="W287" s="3" t="n">
         <v>141.5</v>
@@ -22249,9 +21617,7 @@
       <c r="T288" s="3" t="n">
         <v>22.4</v>
       </c>
-      <c r="U288" s="3" t="n">
-        <v>17.5</v>
-      </c>
+      <c r="U288" s="3" t="inlineStr"/>
       <c r="V288" t="inlineStr"/>
       <c r="W288" s="3" t="n">
         <v>145</v>
@@ -22328,9 +21694,7 @@
       <c r="T289" s="7" t="n">
         <v>25.1</v>
       </c>
-      <c r="U289" s="6" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U289" s="6" t="inlineStr"/>
       <c r="V289" s="4" t="inlineStr"/>
       <c r="W289" s="6" t="n">
         <v>136.5</v>
@@ -22403,9 +21767,7 @@
       <c r="T290" s="6" t="n">
         <v>24.1</v>
       </c>
-      <c r="U290" s="6" t="n">
-        <v>20.7</v>
-      </c>
+      <c r="U290" s="6" t="inlineStr"/>
       <c r="V290" s="4" t="inlineStr"/>
       <c r="W290" s="6" t="n">
         <v>138.3</v>
@@ -22478,14 +21840,8 @@
       <c r="T291" s="7" t="n">
         <v>26.8</v>
       </c>
-      <c r="U291" s="7" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="V291" s="7" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U291" s="6" t="inlineStr"/>
+      <c r="V291" s="4" t="inlineStr"/>
       <c r="W291" s="6" t="n">
         <v>139.1</v>
       </c>
@@ -22561,9 +21917,7 @@
       <c r="T292" s="1" t="n">
         <v>26.1</v>
       </c>
-      <c r="U292" s="3" t="n">
-        <v>23.2</v>
-      </c>
+      <c r="U292" s="3" t="inlineStr"/>
       <c r="V292" t="inlineStr"/>
       <c r="W292" s="3" t="n">
         <v>142</v>
@@ -22636,9 +21990,7 @@
       <c r="T293" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="U293" s="3" t="n">
-        <v>20.7</v>
-      </c>
+      <c r="U293" s="3" t="inlineStr"/>
       <c r="V293" t="inlineStr"/>
       <c r="W293" s="3" t="n">
         <v>142.6</v>
@@ -22711,9 +22063,7 @@
       <c r="T294" s="1" t="n">
         <v>25.3</v>
       </c>
-      <c r="U294" s="3" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="U294" s="3" t="inlineStr"/>
       <c r="V294" t="inlineStr"/>
       <c r="W294" s="3" t="n">
         <v>140.9</v>
@@ -22790,9 +22140,7 @@
       <c r="T295" s="7" t="n">
         <v>27.4</v>
       </c>
-      <c r="U295" s="6" t="n">
-        <v>23.9</v>
-      </c>
+      <c r="U295" s="6" t="inlineStr"/>
       <c r="V295" s="4" t="inlineStr"/>
       <c r="W295" s="6" t="n">
         <v>144</v>
@@ -22865,14 +22213,8 @@
       <c r="T296" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="U296" s="1" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="V296" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U296" s="3" t="inlineStr"/>
+      <c r="V296" t="inlineStr"/>
       <c r="W296" s="3" t="n">
         <v>139</v>
       </c>
@@ -22944,9 +22286,7 @@
       <c r="T297" s="1" t="n">
         <v>30.6</v>
       </c>
-      <c r="U297" s="3" t="n">
-        <v>23</v>
-      </c>
+      <c r="U297" s="3" t="inlineStr"/>
       <c r="V297" t="inlineStr"/>
       <c r="W297" s="3" t="n">
         <v>142.2</v>
@@ -23019,9 +22359,7 @@
       <c r="T298" s="1" t="n">
         <v>25.2</v>
       </c>
-      <c r="U298" s="3" t="n">
-        <v>19</v>
-      </c>
+      <c r="U298" s="3" t="inlineStr"/>
       <c r="V298" t="inlineStr"/>
       <c r="W298" s="3" t="n">
         <v>145.4</v>
@@ -23094,9 +22432,7 @@
       <c r="T299" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="U299" s="3" t="n">
-        <v>23</v>
-      </c>
+      <c r="U299" s="3" t="inlineStr"/>
       <c r="V299" t="inlineStr"/>
       <c r="W299" s="3" t="n">
         <v>143.8</v>
@@ -23169,9 +22505,7 @@
       <c r="T300" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="U300" s="1" t="n">
-        <v>27.6</v>
-      </c>
+      <c r="U300" s="3" t="inlineStr"/>
       <c r="V300" t="inlineStr"/>
       <c r="W300" s="3" t="n">
         <v>146.9</v>
@@ -23244,9 +22578,7 @@
       <c r="T301" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="U301" s="3" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U301" s="3" t="inlineStr"/>
       <c r="V301" t="inlineStr"/>
       <c r="W301" s="3" t="n">
         <v>147.6</v>
@@ -23319,14 +22651,8 @@
       <c r="T302" s="1" t="n">
         <v>25.8</v>
       </c>
-      <c r="U302" s="1" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="V302" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U302" s="3" t="inlineStr"/>
+      <c r="V302" t="inlineStr"/>
       <c r="W302" s="3" t="n">
         <v>148.4</v>
       </c>
@@ -23398,9 +22724,7 @@
       <c r="T303" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="U303" s="3" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="U303" s="3" t="inlineStr"/>
       <c r="V303" t="inlineStr"/>
       <c r="W303" s="3" t="n">
         <v>150.4</v>
@@ -23473,9 +22797,7 @@
       <c r="T304" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="U304" s="3" t="n">
-        <v>14.1</v>
-      </c>
+      <c r="U304" s="3" t="inlineStr"/>
       <c r="V304" t="inlineStr"/>
       <c r="W304" s="3" t="n">
         <v>143.3</v>
@@ -23548,9 +22870,7 @@
       <c r="T305" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="U305" s="3" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="U305" s="3" t="inlineStr"/>
       <c r="V305" t="inlineStr"/>
       <c r="W305" s="3" t="n">
         <v>144.2</v>
@@ -23623,9 +22943,7 @@
       <c r="T306" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="U306" s="3" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U306" s="3" t="inlineStr"/>
       <c r="V306" t="inlineStr"/>
       <c r="W306" s="2" t="n">
         <v>156.9</v>
@@ -23698,9 +23016,7 @@
       <c r="T307" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="U307" s="3" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="U307" s="3" t="inlineStr"/>
       <c r="V307" t="inlineStr"/>
       <c r="W307" s="3" t="n">
         <v>149.9</v>
@@ -23773,9 +23089,7 @@
       <c r="T308" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="U308" s="3" t="n">
-        <v>12.6</v>
-      </c>
+      <c r="U308" s="3" t="inlineStr"/>
       <c r="V308" t="inlineStr"/>
       <c r="W308" s="3" t="n">
         <v>139.2</v>
@@ -23848,9 +23162,7 @@
       <c r="T309" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="U309" s="3" t="n">
-        <v>12</v>
-      </c>
+      <c r="U309" s="3" t="inlineStr"/>
       <c r="V309" t="inlineStr"/>
       <c r="W309" s="3" t="n">
         <v>140.7</v>
@@ -23923,9 +23235,7 @@
       <c r="T310" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="U310" s="3" t="n">
-        <v>14.2</v>
-      </c>
+      <c r="U310" s="3" t="inlineStr"/>
       <c r="V310" t="inlineStr"/>
       <c r="W310" s="3" t="n">
         <v>141.8</v>
@@ -23998,9 +23308,7 @@
       <c r="T311" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="U311" s="3" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U311" s="3" t="inlineStr"/>
       <c r="V311" t="inlineStr"/>
       <c r="W311" s="3" t="n">
         <v>141.9</v>
@@ -24077,9 +23385,7 @@
       <c r="T312" s="6" t="n">
         <v>19.5</v>
       </c>
-      <c r="U312" s="6" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U312" s="6" t="inlineStr"/>
       <c r="V312" s="4" t="inlineStr"/>
       <c r="W312" s="6" t="n">
         <v>140.9</v>
@@ -24152,9 +23458,7 @@
       <c r="T313" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="U313" s="3" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U313" s="3" t="inlineStr"/>
       <c r="V313" t="inlineStr"/>
       <c r="W313" s="3" t="n">
         <v>140.8</v>
@@ -24231,9 +23535,7 @@
       <c r="T314" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="U314" s="3" t="n">
-        <v>14.8</v>
-      </c>
+      <c r="U314" s="3" t="inlineStr"/>
       <c r="V314" t="inlineStr"/>
       <c r="W314" s="3" t="n">
         <v>139.6</v>
@@ -24306,9 +23608,7 @@
       <c r="T315" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="U315" s="3" t="n">
-        <v>16.6</v>
-      </c>
+      <c r="U315" s="3" t="inlineStr"/>
       <c r="V315" t="inlineStr"/>
       <c r="W315" s="3" t="n">
         <v>139.1</v>
@@ -24381,9 +23681,7 @@
       <c r="T316" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="U316" s="3" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U316" s="3" t="inlineStr"/>
       <c r="V316" t="inlineStr"/>
       <c r="W316" s="3" t="n">
         <v>139.6</v>
@@ -24460,9 +23758,7 @@
       <c r="T317" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="U317" s="3" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U317" s="3" t="inlineStr"/>
       <c r="V317" t="inlineStr"/>
       <c r="W317" s="3" t="n">
         <v>138.2</v>
@@ -24535,9 +23831,7 @@
       <c r="T318" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="U318" s="3" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U318" s="3" t="inlineStr"/>
       <c r="V318" t="inlineStr"/>
       <c r="W318" s="3" t="n">
         <v>141.9</v>
@@ -24610,9 +23904,7 @@
       <c r="T319" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="U319" s="3" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="U319" s="3" t="inlineStr"/>
       <c r="V319" t="inlineStr"/>
       <c r="W319" s="3" t="n">
         <v>143.3</v>
@@ -24685,9 +23977,7 @@
       <c r="T320" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="U320" s="3" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U320" s="3" t="inlineStr"/>
       <c r="V320" t="inlineStr"/>
       <c r="W320" s="3" t="n">
         <v>141.4</v>
@@ -24760,9 +24050,7 @@
       <c r="T321" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="U321" s="3" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U321" s="3" t="inlineStr"/>
       <c r="V321" t="inlineStr"/>
       <c r="W321" s="3" t="n">
         <v>141.7</v>
@@ -24835,9 +24123,7 @@
       <c r="T322" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="U322" s="3" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U322" s="3" t="inlineStr"/>
       <c r="V322" t="inlineStr"/>
       <c r="W322" s="3" t="n">
         <v>138.7</v>
@@ -24910,9 +24196,7 @@
       <c r="T323" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="U323" s="3" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U323" s="3" t="inlineStr"/>
       <c r="V323" t="inlineStr"/>
       <c r="W323" s="3" t="n">
         <v>135.4</v>
@@ -24985,9 +24269,7 @@
       <c r="T324" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="U324" s="3" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U324" s="3" t="inlineStr"/>
       <c r="V324" t="inlineStr"/>
       <c r="W324" s="3" t="n">
         <v>136.1</v>
@@ -25060,9 +24342,7 @@
       <c r="T325" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="U325" s="3" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U325" s="3" t="inlineStr"/>
       <c r="V325" t="inlineStr"/>
       <c r="W325" s="3" t="n">
         <v>138.2</v>
@@ -25135,9 +24415,7 @@
       <c r="T326" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="U326" s="3" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U326" s="3" t="inlineStr"/>
       <c r="V326" t="inlineStr"/>
       <c r="W326" s="3" t="n">
         <v>140.2</v>
@@ -25210,9 +24488,7 @@
       <c r="T327" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="U327" s="3" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U327" s="3" t="inlineStr"/>
       <c r="V327" t="inlineStr"/>
       <c r="W327" s="3" t="n">
         <v>139.4</v>
@@ -25285,9 +24561,7 @@
       <c r="T328" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="U328" s="3" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U328" s="3" t="inlineStr"/>
       <c r="V328" t="inlineStr"/>
       <c r="W328" s="3" t="n">
         <v>141.5</v>
@@ -25364,9 +24638,7 @@
       <c r="T329" s="3" t="n">
         <v>17.3</v>
       </c>
-      <c r="U329" s="3" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U329" s="3" t="inlineStr"/>
       <c r="V329" t="inlineStr"/>
       <c r="W329" s="3" t="n">
         <v>139.3</v>
@@ -25439,9 +24711,7 @@
       <c r="T330" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="U330" s="3" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U330" s="3" t="inlineStr"/>
       <c r="V330" t="inlineStr"/>
       <c r="W330" s="3" t="n">
         <v>145.8</v>
@@ -25514,9 +24784,7 @@
       <c r="T331" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="U331" s="3" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U331" s="3" t="inlineStr"/>
       <c r="V331" t="inlineStr"/>
       <c r="W331" s="3" t="n">
         <v>138.4</v>
@@ -25589,9 +24857,7 @@
       <c r="T332" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="U332" s="3" t="n">
-        <v>13.3</v>
-      </c>
+      <c r="U332" s="3" t="inlineStr"/>
       <c r="V332" t="inlineStr"/>
       <c r="W332" s="3" t="n">
         <v>135.5</v>
@@ -25664,9 +24930,7 @@
       <c r="T333" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="U333" s="3" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U333" s="3" t="inlineStr"/>
       <c r="V333" t="inlineStr"/>
       <c r="W333" s="3" t="n">
         <v>132.3</v>
@@ -25739,9 +25003,7 @@
       <c r="T334" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="U334" s="3" t="n">
-        <v>14</v>
-      </c>
+      <c r="U334" s="3" t="inlineStr"/>
       <c r="V334" t="inlineStr"/>
       <c r="W334" s="3" t="n">
         <v>137</v>
@@ -25814,9 +25076,7 @@
       <c r="T335" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="U335" s="3" t="n">
-        <v>17.4</v>
-      </c>
+      <c r="U335" s="3" t="inlineStr"/>
       <c r="V335" t="inlineStr"/>
       <c r="W335" s="3" t="n">
         <v>137.4</v>
@@ -25889,9 +25149,7 @@
       <c r="T336" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="U336" s="3" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U336" s="3" t="inlineStr"/>
       <c r="V336" t="inlineStr"/>
       <c r="W336" s="3" t="n">
         <v>139</v>
@@ -25964,9 +25222,7 @@
       <c r="T337" s="3" t="n">
         <v>16.3</v>
       </c>
-      <c r="U337" s="3" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U337" s="3" t="inlineStr"/>
       <c r="V337" t="inlineStr"/>
       <c r="W337" s="3" t="n">
         <v>138.6</v>
@@ -26039,9 +25295,7 @@
       <c r="T338" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="U338" s="3" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U338" s="3" t="inlineStr"/>
       <c r="V338" t="inlineStr"/>
       <c r="W338" s="3" t="n">
         <v>139.5</v>
@@ -26114,9 +25368,7 @@
       <c r="T339" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="U339" s="3" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U339" s="3" t="inlineStr"/>
       <c r="V339" t="inlineStr"/>
       <c r="W339" s="3" t="n">
         <v>144.2</v>
@@ -26189,9 +25441,7 @@
       <c r="T340" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="U340" s="3" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="U340" s="3" t="inlineStr"/>
       <c r="V340" t="inlineStr"/>
       <c r="W340" s="3" t="n">
         <v>142.5</v>
@@ -26264,9 +25514,7 @@
       <c r="T341" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="U341" s="3" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U341" s="3" t="inlineStr"/>
       <c r="V341" t="inlineStr"/>
       <c r="W341" s="3" t="n">
         <v>143.2</v>
@@ -26339,9 +25587,7 @@
       <c r="T342" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="U342" s="3" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U342" s="3" t="inlineStr"/>
       <c r="V342" t="inlineStr"/>
       <c r="W342" s="3" t="n">
         <v>136.9</v>
@@ -26414,9 +25660,7 @@
       <c r="T343" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="U343" s="3" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U343" s="3" t="inlineStr"/>
       <c r="V343" t="inlineStr"/>
       <c r="W343" s="3" t="n">
         <v>142.1</v>
@@ -26489,9 +25733,7 @@
       <c r="T344" s="6" t="n">
         <v>21.5</v>
       </c>
-      <c r="U344" s="7" t="n">
-        <v>28.7</v>
-      </c>
+      <c r="U344" s="6" t="inlineStr"/>
       <c r="V344" s="4" t="inlineStr"/>
       <c r="W344" s="6" t="n">
         <v>152.2</v>
@@ -26564,9 +25806,7 @@
       <c r="T345" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="U345" s="3" t="n">
-        <v>16</v>
-      </c>
+      <c r="U345" s="3" t="inlineStr"/>
       <c r="V345" t="inlineStr"/>
       <c r="W345" s="3" t="n">
         <v>145</v>
@@ -26639,9 +25879,7 @@
       <c r="T346" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="U346" s="3" t="n">
-        <v>20.6</v>
-      </c>
+      <c r="U346" s="3" t="inlineStr"/>
       <c r="V346" t="inlineStr"/>
       <c r="W346" s="3" t="n">
         <v>142</v>
@@ -26718,9 +25956,7 @@
       <c r="T347" s="6" t="n">
         <v>22.2</v>
       </c>
-      <c r="U347" s="6" t="n">
-        <v>23.9</v>
-      </c>
+      <c r="U347" s="6" t="inlineStr"/>
       <c r="V347" s="4" t="inlineStr"/>
       <c r="W347" s="6" t="n">
         <v>143.1</v>
@@ -26793,9 +26029,7 @@
       <c r="T348" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="U348" s="3" t="n">
-        <v>21.1</v>
-      </c>
+      <c r="U348" s="3" t="inlineStr"/>
       <c r="V348" t="inlineStr"/>
       <c r="W348" s="3" t="n">
         <v>143</v>
@@ -26868,9 +26102,7 @@
       <c r="T349" s="3" t="n">
         <v>17.7</v>
       </c>
-      <c r="U349" s="3" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="U349" s="3" t="inlineStr"/>
       <c r="V349" t="inlineStr"/>
       <c r="W349" s="3" t="n">
         <v>142.6</v>
@@ -26943,9 +26175,7 @@
       <c r="T350" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="U350" s="3" t="n">
-        <v>12.9</v>
-      </c>
+      <c r="U350" s="3" t="inlineStr"/>
       <c r="V350" t="inlineStr"/>
       <c r="W350" s="3" t="n">
         <v>144.3</v>
@@ -27018,9 +26248,7 @@
       <c r="T351" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U351" s="3" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U351" s="3" t="inlineStr"/>
       <c r="V351" t="inlineStr"/>
       <c r="W351" s="3" t="n">
         <v>142.7</v>
@@ -27093,9 +26321,7 @@
       <c r="T352" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="U352" s="3" t="n">
-        <v>20.7</v>
-      </c>
+      <c r="U352" s="3" t="inlineStr"/>
       <c r="V352" t="inlineStr"/>
       <c r="W352" s="3" t="n">
         <v>142.6</v>
@@ -27168,9 +26394,7 @@
       <c r="T353" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U353" s="3" t="n">
-        <v>15.7</v>
-      </c>
+      <c r="U353" s="3" t="inlineStr"/>
       <c r="V353" t="inlineStr"/>
       <c r="W353" s="3" t="n">
         <v>146.7</v>
@@ -27243,9 +26467,7 @@
       <c r="T354" s="3" t="n">
         <v>17.3</v>
       </c>
-      <c r="U354" s="3" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U354" s="3" t="inlineStr"/>
       <c r="V354" t="inlineStr"/>
       <c r="W354" s="3" t="n">
         <v>141.9</v>
@@ -27318,9 +26540,7 @@
       <c r="T355" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="U355" s="3" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U355" s="3" t="inlineStr"/>
       <c r="V355" t="inlineStr"/>
       <c r="W355" s="3" t="n">
         <v>143.1</v>
@@ -27397,9 +26617,7 @@
       <c r="T356" s="6" t="n">
         <v>18.6</v>
       </c>
-      <c r="U356" s="6" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U356" s="6" t="inlineStr"/>
       <c r="V356" s="4" t="inlineStr"/>
       <c r="W356" s="6" t="n">
         <v>145.3</v>
@@ -27476,9 +26694,7 @@
       <c r="T357" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="U357" s="3" t="n">
-        <v>16</v>
-      </c>
+      <c r="U357" s="3" t="inlineStr"/>
       <c r="V357" t="inlineStr"/>
       <c r="W357" s="3" t="n">
         <v>139.9</v>
@@ -27551,9 +26767,7 @@
       <c r="T358" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="U358" s="3" t="n">
-        <v>17.6</v>
-      </c>
+      <c r="U358" s="3" t="inlineStr"/>
       <c r="V358" t="inlineStr"/>
       <c r="W358" s="3" t="n">
         <v>139.4</v>
@@ -27626,9 +26840,7 @@
       <c r="T359" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="U359" s="3" t="n">
-        <v>13.6</v>
-      </c>
+      <c r="U359" s="3" t="inlineStr"/>
       <c r="V359" t="inlineStr"/>
       <c r="W359" s="3" t="n">
         <v>144.5</v>
@@ -27701,9 +26913,7 @@
       <c r="T360" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="U360" s="3" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="U360" s="3" t="inlineStr"/>
       <c r="V360" t="inlineStr"/>
       <c r="W360" s="3" t="n">
         <v>149.6</v>
@@ -27776,9 +26986,7 @@
       <c r="T361" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="U361" s="3" t="n">
-        <v>13</v>
-      </c>
+      <c r="U361" s="3" t="inlineStr"/>
       <c r="V361" t="inlineStr"/>
       <c r="W361" s="3" t="n">
         <v>154.8</v>
@@ -27851,9 +27059,7 @@
       <c r="T362" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="U362" s="3" t="n">
-        <v>13.2</v>
-      </c>
+      <c r="U362" s="3" t="inlineStr"/>
       <c r="V362" t="inlineStr"/>
       <c r="W362" s="3" t="n">
         <v>150</v>
@@ -27926,9 +27132,7 @@
       <c r="T363" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="U363" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
+      <c r="U363" s="3" t="inlineStr"/>
       <c r="V363" t="inlineStr"/>
       <c r="W363" s="3" t="n">
         <v>145.4</v>
@@ -28005,9 +27209,7 @@
       <c r="T364" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="U364" s="3" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="U364" s="3" t="inlineStr"/>
       <c r="V364" t="inlineStr"/>
       <c r="W364" s="3" t="n">
         <v>145.7</v>
@@ -28080,9 +27282,7 @@
       <c r="T365" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="U365" s="3" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U365" s="3" t="inlineStr"/>
       <c r="V365" t="inlineStr"/>
       <c r="W365" s="3" t="n">
         <v>149.8</v>
@@ -28155,9 +27355,7 @@
       <c r="T366" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="U366" s="3" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U366" s="3" t="inlineStr"/>
       <c r="V366" t="inlineStr"/>
       <c r="W366" s="3" t="n">
         <v>144.7</v>
@@ -28230,9 +27428,7 @@
       <c r="T367" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="U367" s="3" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U367" s="3" t="inlineStr"/>
       <c r="V367" t="inlineStr"/>
       <c r="W367" s="3" t="n">
         <v>144.3</v>
@@ -28305,9 +27501,7 @@
       <c r="T368" s="6" t="n">
         <v>17.2</v>
       </c>
-      <c r="U368" s="6" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U368" s="6" t="inlineStr"/>
       <c r="V368" s="4" t="inlineStr"/>
       <c r="W368" s="6" t="n">
         <v>145.7</v>
@@ -28380,9 +27574,7 @@
       <c r="T369" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="U369" s="3" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U369" s="3" t="inlineStr"/>
       <c r="V369" t="inlineStr"/>
       <c r="W369" s="3" t="n">
         <v>145.1</v>
@@ -28455,9 +27647,7 @@
       <c r="T370" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="U370" s="3" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U370" s="3" t="inlineStr"/>
       <c r="V370" t="inlineStr"/>
       <c r="W370" s="3" t="n">
         <v>148.5</v>
@@ -28530,9 +27720,7 @@
       <c r="T371" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="U371" s="3" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U371" s="3" t="inlineStr"/>
       <c r="V371" t="inlineStr"/>
       <c r="W371" s="3" t="n">
         <v>145.7</v>
@@ -28605,9 +27793,7 @@
       <c r="T372" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="U372" s="3" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U372" s="3" t="inlineStr"/>
       <c r="V372" t="inlineStr"/>
       <c r="W372" s="3" t="n">
         <v>147.3</v>
@@ -31508,7 +30694,7 @@
         <v>392.84</v>
       </c>
       <c r="G412" t="n">
-        <v>7424200</v>
+        <v>7435100</v>
       </c>
       <c r="H412" s="2" t="n">
         <v>-1.49</v>
@@ -31576,37 +30762,37 @@
         <v>393.11</v>
       </c>
       <c r="D413" t="n">
-        <v>394.33</v>
+        <v>395.3</v>
       </c>
       <c r="E413" t="n">
         <v>391.81</v>
       </c>
       <c r="F413" t="n">
-        <v>393.69</v>
+        <v>394.15</v>
       </c>
       <c r="G413" t="n">
-        <v>4734108</v>
+        <v>6645243</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>0.22</v>
+        <v>0.33</v>
       </c>
       <c r="I413" t="n">
         <v>2.5</v>
       </c>
       <c r="J413" t="n">
-        <v>408.41</v>
+        <v>408.44</v>
       </c>
       <c r="K413" t="n">
-        <v>388.76</v>
+        <v>388.77</v>
       </c>
       <c r="L413" t="n">
-        <v>403.99</v>
+        <v>404</v>
       </c>
       <c r="M413" t="n">
         <v>416.07</v>
       </c>
       <c r="N413" s="1" t="n">
-        <v>27.87</v>
+        <v>28.29</v>
       </c>
       <c r="O413" t="n">
         <v>29</v>
@@ -31627,16 +30813,18 @@
         </is>
       </c>
       <c r="S413" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
       <c r="T413" s="3" t="n">
-        <v>17.6</v>
+        <v>17.2</v>
       </c>
       <c r="U413" s="3" t="n">
-        <v>14.8</v>
+        <v>17.1</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="3" t="inlineStr"/>
+      <c r="W413" s="3" t="n">
+        <v>146.6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -30685,28 +30685,44 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="C412" t="n">
+        <v>393.11</v>
+      </c>
+      <c r="D412" t="n">
+        <v>395.31</v>
+      </c>
+      <c r="E412" t="n">
+        <v>391.81</v>
+      </c>
+      <c r="F412" t="n">
+        <v>394.15</v>
+      </c>
       <c r="G412" t="n">
-        <v>6645243</v>
-      </c>
-      <c r="H412" s="2" t="n">
-        <v>0</v>
+        <v>6679400</v>
+      </c>
+      <c r="H412" s="3" t="n">
+        <v>0.33</v>
       </c>
       <c r="I412" t="n">
         <v>2.5</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>408.44</v>
+      </c>
+      <c r="K412" t="n">
+        <v>388.77</v>
+      </c>
+      <c r="L412" t="n">
+        <v>404</v>
+      </c>
+      <c r="M412" t="n">
+        <v>416.07</v>
+      </c>
       <c r="N412" s="3" t="n">
-        <v>27.07</v>
+        <v>28.29</v>
       </c>
       <c r="O412" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -30718,7 +30734,11 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R412" t="inlineStr"/>
+      <c r="R412" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
       <c r="S412" t="n">
         <v>5</v>
       </c>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -30745,13 +30745,84 @@
       <c r="T412" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U412" s="2" t="n">
-        <v>17.1</v>
-      </c>
+      <c r="U412" s="2" t="inlineStr"/>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="2" t="n">
         <v>146.6</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>398.91</v>
+      </c>
+      <c r="D413" t="n">
+        <v>399.94</v>
+      </c>
+      <c r="E413" t="n">
+        <v>396.46</v>
+      </c>
+      <c r="F413" t="n">
+        <v>398.53</v>
+      </c>
+      <c r="G413" t="n">
+        <v>4158399</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J413" t="n">
+        <v>408.43</v>
+      </c>
+      <c r="K413" t="n">
+        <v>389</v>
+      </c>
+      <c r="L413" t="n">
+        <v>403.85</v>
+      </c>
+      <c r="M413" t="n">
+        <v>416.15</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="O413" t="n">
+        <v>29</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -30698,7 +30698,7 @@
         <v>394.15</v>
       </c>
       <c r="G412" t="n">
-        <v>6679400</v>
+        <v>6705500</v>
       </c>
       <c r="H412" s="3" t="n">
         <v>0.33</v>
@@ -30766,40 +30766,40 @@
         <v>398.91</v>
       </c>
       <c r="D413" t="n">
-        <v>399.94</v>
+        <v>400.59</v>
       </c>
       <c r="E413" t="n">
-        <v>396.46</v>
+        <v>388.39</v>
       </c>
       <c r="F413" t="n">
-        <v>398.53</v>
+        <v>391.67</v>
       </c>
       <c r="G413" t="n">
-        <v>4158399</v>
-      </c>
-      <c r="H413" s="3" t="n">
-        <v>1.11</v>
+        <v>14469303</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-0.63</v>
       </c>
       <c r="I413" t="n">
         <v>2.5</v>
       </c>
       <c r="J413" t="n">
-        <v>408.43</v>
+        <v>408.09</v>
       </c>
       <c r="K413" t="n">
-        <v>389</v>
+        <v>388.89</v>
       </c>
       <c r="L413" t="n">
-        <v>403.85</v>
+        <v>403.79</v>
       </c>
       <c r="M413" t="n">
-        <v>416.15</v>
-      </c>
-      <c r="N413" s="2" t="n">
-        <v>34.96</v>
+        <v>416.11</v>
+      </c>
+      <c r="N413" s="3" t="n">
+        <v>29.93</v>
       </c>
       <c r="O413" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -30811,15 +30811,19 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R413" t="inlineStr"/>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
       <c r="S413" t="n">
-        <v>4.96</v>
+        <v>5.01</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>16.8</v>
+        <v>18.1</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>16.2</v>
+        <v>18</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -4346,7 +4346,7 @@
         <v>2.5</v>
       </c>
       <c r="J53" t="n">
-        <v>280.58</v>
+        <v>280.59</v>
       </c>
       <c r="K53" t="n">
         <v>268.78</v>
@@ -8158,7 +8158,7 @@
         <v>2.5</v>
       </c>
       <c r="J105" t="n">
-        <v>308.88</v>
+        <v>308.89</v>
       </c>
       <c r="K105" t="n">
         <v>302.49</v>
@@ -30772,19 +30772,19 @@
         <v>388.39</v>
       </c>
       <c r="F413" t="n">
-        <v>391.67</v>
+        <v>391.74</v>
       </c>
       <c r="G413" t="n">
-        <v>14469303</v>
+        <v>15606840</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>-0.63</v>
+        <v>-0.61</v>
       </c>
       <c r="I413" t="n">
         <v>2.5</v>
       </c>
       <c r="J413" t="n">
-        <v>408.09</v>
+        <v>408.1</v>
       </c>
       <c r="K413" t="n">
         <v>388.89</v>
@@ -30796,7 +30796,7 @@
         <v>416.11</v>
       </c>
       <c r="N413" s="3" t="n">
-        <v>29.93</v>
+        <v>29.95</v>
       </c>
       <c r="O413" t="n">
         <v>26</v>
@@ -30820,13 +30820,15 @@
         <v>5.01</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>18.1</v>
+        <v>17.7</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>145.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -30766,7 +30766,7 @@
         <v>398.91</v>
       </c>
       <c r="D413" t="n">
-        <v>400.59</v>
+        <v>400.6</v>
       </c>
       <c r="E413" t="n">
         <v>388.39</v>
@@ -30775,7 +30775,7 @@
         <v>391.74</v>
       </c>
       <c r="G413" t="n">
-        <v>15606840</v>
+        <v>15607000</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>-0.61</v>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -30799,7 +30799,7 @@
         <v>29.95</v>
       </c>
       <c r="O413" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -30822,13 +30822,84 @@
       <c r="T413" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="U413" s="2" t="n">
-        <v>17</v>
-      </c>
+      <c r="U413" s="2" t="inlineStr"/>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="n">
         <v>145.9</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>400.28</v>
+      </c>
+      <c r="D414" t="n">
+        <v>401.43</v>
+      </c>
+      <c r="E414" t="n">
+        <v>398.8</v>
+      </c>
+      <c r="F414" t="n">
+        <v>399.64</v>
+      </c>
+      <c r="G414" t="n">
+        <v>5142714</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="I414" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J414" t="n">
+        <v>407.38</v>
+      </c>
+      <c r="K414" t="n">
+        <v>389.26</v>
+      </c>
+      <c r="L414" t="n">
+        <v>403.78</v>
+      </c>
+      <c r="M414" t="n">
+        <v>416.17</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>35.72</v>
+      </c>
+      <c r="O414" t="n">
+        <v>29</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -30775,7 +30775,7 @@
         <v>391.74</v>
       </c>
       <c r="G413" t="n">
-        <v>15607000</v>
+        <v>15773200</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>-0.61</v>
@@ -30846,34 +30846,34 @@
         <v>401.43</v>
       </c>
       <c r="E414" t="n">
-        <v>398.8</v>
+        <v>398.04</v>
       </c>
       <c r="F414" t="n">
-        <v>399.64</v>
+        <v>398.36</v>
       </c>
       <c r="G414" t="n">
-        <v>5142714</v>
+        <v>7581577</v>
       </c>
       <c r="H414" s="3" t="n">
-        <v>2.02</v>
+        <v>1.69</v>
       </c>
       <c r="I414" t="n">
         <v>2.5</v>
       </c>
       <c r="J414" t="n">
-        <v>407.38</v>
+        <v>407.32</v>
       </c>
       <c r="K414" t="n">
-        <v>389.26</v>
+        <v>389.24</v>
       </c>
       <c r="L414" t="n">
-        <v>403.78</v>
+        <v>403.77</v>
       </c>
       <c r="M414" t="n">
-        <v>416.17</v>
+        <v>416.16</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>35.72</v>
+        <v>34.68</v>
       </c>
       <c r="O414" t="n">
         <v>29</v>
@@ -30893,13 +30893,15 @@
         <v>4.95</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>15.6</v>
+        <v>15.4</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>11.7</v>
+        <v>13.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>145.7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -30843,7 +30843,7 @@
         <v>400.28</v>
       </c>
       <c r="D414" t="n">
-        <v>401.43</v>
+        <v>401.44</v>
       </c>
       <c r="E414" t="n">
         <v>398.04</v>
@@ -30852,7 +30852,7 @@
         <v>398.36</v>
       </c>
       <c r="G414" t="n">
-        <v>7581577</v>
+        <v>7596700</v>
       </c>
       <c r="H414" s="3" t="n">
         <v>1.69</v>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -30876,7 +30876,7 @@
         <v>34.68</v>
       </c>
       <c r="O414" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -30895,13 +30895,84 @@
       <c r="T414" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U414" s="2" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U414" s="2" t="inlineStr"/>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="n">
         <v>145.7</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>400.48</v>
+      </c>
+      <c r="D415" t="n">
+        <v>400.49</v>
+      </c>
+      <c r="E415" t="n">
+        <v>398.6</v>
+      </c>
+      <c r="F415" t="n">
+        <v>399.18</v>
+      </c>
+      <c r="G415" t="n">
+        <v>2016359</v>
+      </c>
+      <c r="H415" s="3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I415" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J415" t="n">
+        <v>406.52</v>
+      </c>
+      <c r="K415" t="n">
+        <v>389.8</v>
+      </c>
+      <c r="L415" t="n">
+        <v>403.64</v>
+      </c>
+      <c r="M415" t="n">
+        <v>416.21</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>42.67</v>
+      </c>
+      <c r="O415" t="n">
+        <v>29</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -645,7 +645,9 @@
       <c r="T2" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U2" s="2" t="inlineStr"/>
+      <c r="U2" s="2" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" s="1" t="n">
         <v>168.6</v>
@@ -718,7 +720,9 @@
       <c r="T3" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U3" s="2" t="inlineStr"/>
+      <c r="U3" s="2" t="n">
+        <v>13.5</v>
+      </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" s="1" t="n">
         <v>163.6</v>
@@ -791,7 +795,9 @@
       <c r="T4" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U4" s="2" t="inlineStr"/>
+      <c r="U4" s="2" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" s="1" t="n">
         <v>157.4</v>
@@ -864,7 +870,9 @@
       <c r="T5" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" s="1" t="n">
         <v>156.7</v>
@@ -937,7 +945,9 @@
       <c r="T6" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="n">
+        <v>16.5</v>
+      </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" s="1" t="n">
         <v>158.5</v>
@@ -1010,7 +1020,9 @@
       <c r="T7" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="n">
+        <v>18.2</v>
+      </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" s="1" t="n">
         <v>155.4</v>
@@ -1083,7 +1095,9 @@
       <c r="T8" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" s="1" t="n">
         <v>159.4</v>
@@ -1156,7 +1170,9 @@
       <c r="T9" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" s="1" t="n">
         <v>162.6</v>
@@ -1229,7 +1245,9 @@
       <c r="T10" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="U10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="n">
+        <v>15.8</v>
+      </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" s="1" t="n">
         <v>163.6</v>
@@ -1302,7 +1320,9 @@
       <c r="T11" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" s="1" t="n">
         <v>166.5</v>
@@ -1375,7 +1395,9 @@
       <c r="T12" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="n">
+        <v>11.3</v>
+      </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" s="1" t="n">
         <v>166.9</v>
@@ -1448,7 +1470,9 @@
       <c r="T13" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="n">
+        <v>14.1</v>
+      </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" s="1" t="n">
         <v>168.8</v>
@@ -1521,7 +1545,9 @@
       <c r="T14" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="n">
+        <v>12.8</v>
+      </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" s="1" t="n">
         <v>166.1</v>
@@ -1594,7 +1620,9 @@
       <c r="T15" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="n">
+        <v>11</v>
+      </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" s="1" t="n">
         <v>163.4</v>
@@ -1667,7 +1695,9 @@
       <c r="T16" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" s="1" t="n">
         <v>168</v>
@@ -1740,7 +1770,9 @@
       <c r="T17" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" s="1" t="n">
         <v>183.1</v>
@@ -1813,7 +1845,9 @@
       <c r="T18" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" s="1" t="n">
         <v>175.8</v>
@@ -1886,7 +1920,9 @@
       <c r="T19" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="n">
+        <v>11.2</v>
+      </c>
       <c r="V19" t="inlineStr"/>
       <c r="W19" s="1" t="n">
         <v>178.6</v>
@@ -1959,7 +1995,9 @@
       <c r="T20" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="n">
+        <v>18.2</v>
+      </c>
       <c r="V20" t="inlineStr"/>
       <c r="W20" s="1" t="n">
         <v>165</v>
@@ -2032,7 +2070,9 @@
       <c r="T21" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" s="1" t="n">
         <v>156.9</v>
@@ -2105,7 +2145,9 @@
       <c r="T22" s="2" t="n">
         <v>19.4</v>
       </c>
-      <c r="U22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V22" t="inlineStr"/>
       <c r="W22" s="1" t="n">
         <v>157.6</v>
@@ -2178,7 +2220,9 @@
       <c r="T23" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="n">
+        <v>20.5</v>
+      </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" s="2" t="n">
         <v>153.4</v>
@@ -2255,7 +2299,9 @@
       <c r="T24" s="2" t="n">
         <v>21.1</v>
       </c>
-      <c r="U24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="n">
+        <v>19.5</v>
+      </c>
       <c r="V24" t="inlineStr"/>
       <c r="W24" s="2" t="n">
         <v>149.3</v>
@@ -2328,7 +2374,9 @@
       <c r="T25" s="2" t="n">
         <v>19.6</v>
       </c>
-      <c r="U25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="n">
+        <v>18.7</v>
+      </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" s="1" t="n">
         <v>157.9</v>
@@ -2401,7 +2449,9 @@
       <c r="T26" s="2" t="n">
         <v>22.8</v>
       </c>
-      <c r="U26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="n">
+        <v>21.8</v>
+      </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" s="2" t="n">
         <v>154.3</v>
@@ -2474,7 +2524,9 @@
       <c r="T27" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="n">
+        <v>24.6</v>
+      </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" s="2" t="n">
         <v>151.4</v>
@@ -2547,7 +2599,9 @@
       <c r="T28" s="2" t="n">
         <v>21.9</v>
       </c>
-      <c r="U28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V28" t="inlineStr"/>
       <c r="W28" s="2" t="n">
         <v>138.9</v>
@@ -2620,7 +2674,9 @@
       <c r="T29" s="2" t="n">
         <v>24.9</v>
       </c>
-      <c r="U29" s="2" t="inlineStr"/>
+      <c r="U29" s="3" t="n">
+        <v>31.1</v>
+      </c>
       <c r="V29" t="inlineStr"/>
       <c r="W29" s="2" t="n">
         <v>137.6</v>
@@ -2693,7 +2749,9 @@
       <c r="T30" s="2" t="n">
         <v>23.4</v>
       </c>
-      <c r="U30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="n">
+        <v>24.7</v>
+      </c>
       <c r="V30" t="inlineStr"/>
       <c r="W30" s="2" t="n">
         <v>139.9</v>
@@ -2770,8 +2828,14 @@
       <c r="T31" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="U31" s="2" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
+      <c r="U31" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W31" s="2" t="n">
         <v>146</v>
       </c>
@@ -2843,8 +2907,14 @@
       <c r="T32" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="U32" s="2" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
+      <c r="U32" s="3" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W32" s="2" t="n">
         <v>132.8</v>
       </c>
@@ -2916,7 +2986,9 @@
       <c r="T33" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="n">
+        <v>23.2</v>
+      </c>
       <c r="V33" t="inlineStr"/>
       <c r="W33" s="2" t="n">
         <v>128.7</v>
@@ -2989,7 +3061,9 @@
       <c r="T34" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="n">
+        <v>23.4</v>
+      </c>
       <c r="V34" t="inlineStr"/>
       <c r="W34" s="2" t="n">
         <v>128.9</v>
@@ -3062,7 +3136,9 @@
       <c r="T35" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="U35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="n">
+        <v>21.4</v>
+      </c>
       <c r="V35" t="inlineStr"/>
       <c r="W35" s="2" t="n">
         <v>130.3</v>
@@ -3135,7 +3211,9 @@
       <c r="T36" s="2" t="n">
         <v>20.5</v>
       </c>
-      <c r="U36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="n">
+        <v>16.4</v>
+      </c>
       <c r="V36" t="inlineStr"/>
       <c r="W36" s="2" t="n">
         <v>133.9</v>
@@ -3208,7 +3286,9 @@
       <c r="T37" s="2" t="n">
         <v>21.7</v>
       </c>
-      <c r="U37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V37" t="inlineStr"/>
       <c r="W37" s="2" t="n">
         <v>136.8</v>
@@ -3281,7 +3361,9 @@
       <c r="T38" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="n">
+        <v>18.5</v>
+      </c>
       <c r="V38" t="inlineStr"/>
       <c r="W38" s="2" t="n">
         <v>136.4</v>
@@ -3354,7 +3436,9 @@
       <c r="T39" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="n">
+        <v>18.6</v>
+      </c>
       <c r="V39" t="inlineStr"/>
       <c r="W39" s="2" t="n">
         <v>140.8</v>
@@ -3427,7 +3511,9 @@
       <c r="T40" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V40" t="inlineStr"/>
       <c r="W40" s="2" t="n">
         <v>141.7</v>
@@ -3500,7 +3586,9 @@
       <c r="T41" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="n">
+        <v>13</v>
+      </c>
       <c r="V41" t="inlineStr"/>
       <c r="W41" s="2" t="n">
         <v>144</v>
@@ -3573,7 +3661,9 @@
       <c r="T42" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V42" t="inlineStr"/>
       <c r="W42" s="2" t="n">
         <v>148.7</v>
@@ -3646,7 +3736,9 @@
       <c r="T43" s="2" t="n">
         <v>18.3</v>
       </c>
-      <c r="U43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V43" t="inlineStr"/>
       <c r="W43" s="2" t="n">
         <v>144.8</v>
@@ -3719,7 +3811,9 @@
       <c r="T44" s="2" t="n">
         <v>18.7</v>
       </c>
-      <c r="U44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="n">
+        <v>17.1</v>
+      </c>
       <c r="V44" t="inlineStr"/>
       <c r="W44" s="2" t="n">
         <v>140.9</v>
@@ -3792,7 +3886,9 @@
       <c r="T45" s="2" t="n">
         <v>21.6</v>
       </c>
-      <c r="U45" s="2" t="inlineStr"/>
+      <c r="U45" s="3" t="n">
+        <v>25.4</v>
+      </c>
       <c r="V45" t="inlineStr"/>
       <c r="W45" s="2" t="n">
         <v>139</v>
@@ -3865,7 +3961,9 @@
       <c r="T46" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="U46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="n">
+        <v>21.8</v>
+      </c>
       <c r="V46" t="inlineStr"/>
       <c r="W46" s="2" t="n">
         <v>148.6</v>
@@ -3938,7 +4036,9 @@
       <c r="T47" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="U47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="n">
+        <v>20.1</v>
+      </c>
       <c r="V47" t="inlineStr"/>
       <c r="W47" s="2" t="n">
         <v>143</v>
@@ -4011,7 +4111,9 @@
       <c r="T48" s="2" t="n">
         <v>21.5</v>
       </c>
-      <c r="U48" s="2" t="inlineStr"/>
+      <c r="U48" s="3" t="n">
+        <v>26.7</v>
+      </c>
       <c r="V48" t="inlineStr"/>
       <c r="W48" s="2" t="n">
         <v>144.3</v>
@@ -4084,8 +4186,14 @@
       <c r="T49" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="U49" s="2" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
+      <c r="U49" s="3" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W49" s="2" t="n">
         <v>139.2</v>
       </c>
@@ -4157,8 +4265,14 @@
       <c r="T50" s="3" t="n">
         <v>45.3</v>
       </c>
-      <c r="U50" s="2" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
+      <c r="U50" s="3" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="V50" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W50" s="2" t="n">
         <v>136.5</v>
       </c>
@@ -4234,8 +4348,14 @@
       <c r="T51" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="U51" s="2" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
+      <c r="U51" s="3" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W51" s="2" t="n">
         <v>133.8</v>
       </c>
@@ -4307,8 +4427,14 @@
       <c r="T52" s="3" t="n">
         <v>52.3</v>
       </c>
-      <c r="U52" s="2" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
+      <c r="U52" s="3" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="V52" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W52" s="2" t="n">
         <v>135.7</v>
       </c>
@@ -4380,8 +4506,14 @@
       <c r="T53" s="3" t="n">
         <v>33.6</v>
       </c>
-      <c r="U53" s="2" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
+      <c r="U53" s="3" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="V53" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W53" s="2" t="n">
         <v>142.2</v>
       </c>
@@ -4453,8 +4585,14 @@
       <c r="T54" s="3" t="n">
         <v>40.7</v>
       </c>
-      <c r="U54" s="2" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
+      <c r="U54" s="3" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="V54" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W54" s="2" t="n">
         <v>127.5</v>
       </c>
@@ -4526,8 +4664,14 @@
       <c r="T55" s="3" t="n">
         <v>37.6</v>
       </c>
-      <c r="U55" s="2" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
+      <c r="U55" s="3" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="V55" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W55" s="2" t="n">
         <v>128.6</v>
       </c>
@@ -4599,7 +4743,9 @@
       <c r="T56" s="3" t="n">
         <v>30.9</v>
       </c>
-      <c r="U56" s="2" t="inlineStr"/>
+      <c r="U56" s="3" t="n">
+        <v>28.5</v>
+      </c>
       <c r="V56" t="inlineStr"/>
       <c r="W56" s="2" t="n">
         <v>135.7</v>
@@ -4672,7 +4818,9 @@
       <c r="T57" s="3" t="n">
         <v>30.1</v>
       </c>
-      <c r="U57" s="2" t="inlineStr"/>
+      <c r="U57" s="3" t="n">
+        <v>26</v>
+      </c>
       <c r="V57" t="inlineStr"/>
       <c r="W57" s="2" t="n">
         <v>135.8</v>
@@ -4745,8 +4893,14 @@
       <c r="T58" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="U58" s="2" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
+      <c r="U58" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V58" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W58" s="2" t="n">
         <v>131.3</v>
       </c>
@@ -4818,8 +4972,14 @@
       <c r="T59" s="3" t="n">
         <v>29.6</v>
       </c>
-      <c r="U59" s="2" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
+      <c r="U59" s="3" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="V59" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W59" s="2" t="n">
         <v>130</v>
       </c>
@@ -4891,7 +5051,9 @@
       <c r="T60" s="3" t="n">
         <v>33.8</v>
       </c>
-      <c r="U60" s="2" t="inlineStr"/>
+      <c r="U60" s="3" t="n">
+        <v>30.6</v>
+      </c>
       <c r="V60" t="inlineStr"/>
       <c r="W60" s="3" t="n">
         <v>125.8</v>
@@ -4964,7 +5126,9 @@
       <c r="T61" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="U61" s="2" t="inlineStr"/>
+      <c r="U61" s="3" t="n">
+        <v>29.1</v>
+      </c>
       <c r="V61" t="inlineStr"/>
       <c r="W61" s="3" t="n">
         <v>125.9</v>
@@ -5037,8 +5201,14 @@
       <c r="T62" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="U62" s="2" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
+      <c r="U62" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="V62" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W62" s="3" t="n">
         <v>126.7</v>
       </c>
@@ -5110,7 +5280,9 @@
       <c r="T63" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="U63" s="2" t="inlineStr"/>
+      <c r="U63" s="3" t="n">
+        <v>25.7</v>
+      </c>
       <c r="V63" t="inlineStr"/>
       <c r="W63" s="2" t="n">
         <v>129</v>
@@ -5183,7 +5355,9 @@
       <c r="T64" s="2" t="n">
         <v>24.8</v>
       </c>
-      <c r="U64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="n">
+        <v>23.6</v>
+      </c>
       <c r="V64" t="inlineStr"/>
       <c r="W64" s="2" t="n">
         <v>132.4</v>
@@ -5256,7 +5430,9 @@
       <c r="T65" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="U65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="n">
+        <v>21.4</v>
+      </c>
       <c r="V65" t="inlineStr"/>
       <c r="W65" s="2" t="n">
         <v>131.3</v>
@@ -5329,7 +5505,9 @@
       <c r="T66" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V66" t="inlineStr"/>
       <c r="W66" s="2" t="n">
         <v>134.3</v>
@@ -5402,7 +5580,9 @@
       <c r="T67" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="n">
+        <v>22.9</v>
+      </c>
       <c r="V67" t="inlineStr"/>
       <c r="W67" s="2" t="n">
         <v>132.7</v>
@@ -5479,7 +5659,9 @@
       <c r="T68" s="2" t="n">
         <v>24.6</v>
       </c>
-      <c r="U68" s="2" t="inlineStr"/>
+      <c r="U68" s="3" t="n">
+        <v>27.5</v>
+      </c>
       <c r="V68" t="inlineStr"/>
       <c r="W68" s="2" t="n">
         <v>134.1</v>
@@ -5552,7 +5734,9 @@
       <c r="T69" s="2" t="n">
         <v>22.7</v>
       </c>
-      <c r="U69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="n">
+        <v>20</v>
+      </c>
       <c r="V69" t="inlineStr"/>
       <c r="W69" s="2" t="n">
         <v>134.8</v>
@@ -5625,7 +5809,9 @@
       <c r="T70" s="2" t="n">
         <v>23.6</v>
       </c>
-      <c r="U70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V70" t="inlineStr"/>
       <c r="W70" s="2" t="n">
         <v>134.1</v>
@@ -5698,7 +5884,9 @@
       <c r="T71" s="2" t="n">
         <v>24.8</v>
       </c>
-      <c r="U71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="n">
+        <v>22.2</v>
+      </c>
       <c r="V71" t="inlineStr"/>
       <c r="W71" s="2" t="n">
         <v>133.2</v>
@@ -5771,7 +5959,9 @@
       <c r="T72" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="n">
+        <v>19.8</v>
+      </c>
       <c r="V72" t="inlineStr"/>
       <c r="W72" s="2" t="n">
         <v>132.2</v>
@@ -5848,7 +6038,9 @@
       <c r="T73" s="2" t="n">
         <v>22.5</v>
       </c>
-      <c r="U73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V73" t="inlineStr"/>
       <c r="W73" s="2" t="n">
         <v>131.5</v>
@@ -5921,7 +6113,9 @@
       <c r="T74" s="2" t="n">
         <v>21.9</v>
       </c>
-      <c r="U74" s="2" t="inlineStr"/>
+      <c r="U74" s="3" t="n">
+        <v>26.9</v>
+      </c>
       <c r="V74" t="inlineStr"/>
       <c r="W74" s="2" t="n">
         <v>128.4</v>
@@ -5998,7 +6192,9 @@
       <c r="T75" s="6" t="n">
         <v>18.4</v>
       </c>
-      <c r="U75" s="6" t="inlineStr"/>
+      <c r="U75" s="6" t="n">
+        <v>18.7</v>
+      </c>
       <c r="V75" s="4" t="inlineStr"/>
       <c r="W75" s="6" t="n">
         <v>137.7</v>
@@ -6071,7 +6267,9 @@
       <c r="T76" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="n">
+        <v>15.4</v>
+      </c>
       <c r="V76" t="inlineStr"/>
       <c r="W76" s="2" t="n">
         <v>140.5</v>
@@ -6144,7 +6342,9 @@
       <c r="T77" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="n">
+        <v>15.2</v>
+      </c>
       <c r="V77" t="inlineStr"/>
       <c r="W77" s="2" t="n">
         <v>138.9</v>
@@ -6217,7 +6417,9 @@
       <c r="T78" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V78" t="inlineStr"/>
       <c r="W78" s="2" t="n">
         <v>140.9</v>
@@ -6290,7 +6492,9 @@
       <c r="T79" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V79" t="inlineStr"/>
       <c r="W79" s="2" t="n">
         <v>136</v>
@@ -6363,7 +6567,9 @@
       <c r="T80" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="n">
+        <v>13.5</v>
+      </c>
       <c r="V80" t="inlineStr"/>
       <c r="W80" s="2" t="n">
         <v>135.9</v>
@@ -6436,7 +6642,9 @@
       <c r="T81" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V81" t="inlineStr"/>
       <c r="W81" s="2" t="n">
         <v>137.3</v>
@@ -6509,7 +6717,9 @@
       <c r="T82" s="2" t="n">
         <v>20.9</v>
       </c>
-      <c r="U82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V82" t="inlineStr"/>
       <c r="W82" s="2" t="n">
         <v>137.3</v>
@@ -6582,7 +6792,9 @@
       <c r="T83" s="2" t="n">
         <v>20.3</v>
       </c>
-      <c r="U83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="n">
+        <v>16.5</v>
+      </c>
       <c r="V83" t="inlineStr"/>
       <c r="W83" s="2" t="n">
         <v>139</v>
@@ -6655,7 +6867,9 @@
       <c r="T84" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="U84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="n">
+        <v>21.7</v>
+      </c>
       <c r="V84" t="inlineStr"/>
       <c r="W84" s="2" t="n">
         <v>139.3</v>
@@ -6728,7 +6942,9 @@
       <c r="T85" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V85" t="inlineStr"/>
       <c r="W85" s="2" t="n">
         <v>140.9</v>
@@ -6801,7 +7017,9 @@
       <c r="T86" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="n">
+        <v>19.5</v>
+      </c>
       <c r="V86" t="inlineStr"/>
       <c r="W86" s="2" t="n">
         <v>137.6</v>
@@ -6874,7 +7092,9 @@
       <c r="T87" s="2" t="n">
         <v>19.2</v>
       </c>
-      <c r="U87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="n">
+        <v>17.4</v>
+      </c>
       <c r="V87" t="inlineStr"/>
       <c r="W87" s="2" t="n">
         <v>137.3</v>
@@ -6947,7 +7167,9 @@
       <c r="T88" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="n">
+        <v>17</v>
+      </c>
       <c r="V88" t="inlineStr"/>
       <c r="W88" s="2" t="n">
         <v>138.2</v>
@@ -7020,7 +7242,9 @@
       <c r="T89" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="n">
+        <v>13.3</v>
+      </c>
       <c r="V89" t="inlineStr"/>
       <c r="W89" s="2" t="n">
         <v>141</v>
@@ -7093,7 +7317,9 @@
       <c r="T90" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="U90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V90" t="inlineStr"/>
       <c r="W90" s="2" t="n">
         <v>141.6</v>
@@ -7166,7 +7392,9 @@
       <c r="T91" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V91" t="inlineStr"/>
       <c r="W91" s="2" t="n">
         <v>137.5</v>
@@ -7239,7 +7467,9 @@
       <c r="T92" s="2" t="n">
         <v>18.5</v>
       </c>
-      <c r="U92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="n">
+        <v>19</v>
+      </c>
       <c r="V92" t="inlineStr"/>
       <c r="W92" s="2" t="n">
         <v>140.1</v>
@@ -7312,7 +7542,9 @@
       <c r="T93" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="n">
+        <v>14.3</v>
+      </c>
       <c r="V93" t="inlineStr"/>
       <c r="W93" s="2" t="n">
         <v>138.9</v>
@@ -7385,7 +7617,9 @@
       <c r="T94" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V94" t="inlineStr"/>
       <c r="W94" s="2" t="n">
         <v>139.2</v>
@@ -7458,7 +7692,9 @@
       <c r="T95" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="n">
+        <v>15.9</v>
+      </c>
       <c r="V95" t="inlineStr"/>
       <c r="W95" s="2" t="n">
         <v>141.2</v>
@@ -7531,7 +7767,9 @@
       <c r="T96" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="n">
+        <v>13.9</v>
+      </c>
       <c r="V96" t="inlineStr"/>
       <c r="W96" s="2" t="n">
         <v>141.4</v>
@@ -7604,7 +7842,9 @@
       <c r="T97" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V97" t="inlineStr"/>
       <c r="W97" s="2" t="n">
         <v>145.6</v>
@@ -7677,7 +7917,9 @@
       <c r="T98" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="n">
+        <v>21.7</v>
+      </c>
       <c r="V98" t="inlineStr"/>
       <c r="W98" s="2" t="n">
         <v>149.6</v>
@@ -7750,7 +7992,9 @@
       <c r="T99" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V99" t="inlineStr"/>
       <c r="W99" s="1" t="n">
         <v>156.6</v>
@@ -7823,7 +8067,9 @@
       <c r="T100" s="2" t="n">
         <v>21.6</v>
       </c>
-      <c r="U100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="n">
+        <v>21</v>
+      </c>
       <c r="V100" t="inlineStr"/>
       <c r="W100" s="2" t="n">
         <v>154.4</v>
@@ -7896,7 +8142,9 @@
       <c r="T101" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="U101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V101" t="inlineStr"/>
       <c r="W101" s="2" t="n">
         <v>148.4</v>
@@ -7969,7 +8217,9 @@
       <c r="T102" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="n">
+        <v>18.4</v>
+      </c>
       <c r="V102" t="inlineStr"/>
       <c r="W102" s="2" t="n">
         <v>149.2</v>
@@ -8042,7 +8292,9 @@
       <c r="T103" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V103" t="inlineStr"/>
       <c r="W103" s="2" t="n">
         <v>154.8</v>
@@ -8119,7 +8371,9 @@
       <c r="T104" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="n">
+        <v>11.2</v>
+      </c>
       <c r="V104" t="inlineStr"/>
       <c r="W104" s="1" t="n">
         <v>155</v>
@@ -8192,7 +8446,9 @@
       <c r="T105" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V105" t="inlineStr"/>
       <c r="W105" s="2" t="n">
         <v>152.2</v>
@@ -8265,7 +8521,9 @@
       <c r="T106" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V106" t="inlineStr"/>
       <c r="W106" s="2" t="n">
         <v>147.5</v>
@@ -8342,7 +8600,9 @@
       <c r="T107" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V107" t="inlineStr"/>
       <c r="W107" s="2" t="n">
         <v>143.4</v>
@@ -8415,7 +8675,9 @@
       <c r="T108" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V108" t="inlineStr"/>
       <c r="W108" s="2" t="n">
         <v>139.6</v>
@@ -8488,7 +8750,9 @@
       <c r="T109" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U109" s="2" t="inlineStr"/>
+      <c r="U109" s="2" t="n">
+        <v>9.699999999999999</v>
+      </c>
       <c r="V109" t="inlineStr"/>
       <c r="W109" s="2" t="n">
         <v>140.1</v>
@@ -8561,7 +8825,9 @@
       <c r="T110" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U110" s="2" t="inlineStr"/>
+      <c r="U110" s="2" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V110" t="inlineStr"/>
       <c r="W110" s="2" t="n">
         <v>139.3</v>
@@ -8638,7 +8904,9 @@
       <c r="T111" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U111" s="2" t="inlineStr"/>
+      <c r="U111" s="2" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V111" t="inlineStr"/>
       <c r="W111" s="2" t="n">
         <v>141.4</v>
@@ -8711,7 +8979,9 @@
       <c r="T112" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U112" s="2" t="inlineStr"/>
+      <c r="U112" s="2" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V112" t="inlineStr"/>
       <c r="W112" s="2" t="n">
         <v>138</v>
@@ -8788,7 +9058,9 @@
       <c r="T113" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U113" s="2" t="inlineStr"/>
+      <c r="U113" s="2" t="n">
+        <v>10.5</v>
+      </c>
       <c r="V113" t="inlineStr"/>
       <c r="W113" s="2" t="n">
         <v>140.8</v>
@@ -8861,7 +9133,9 @@
       <c r="T114" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U114" s="2" t="inlineStr"/>
+      <c r="U114" s="2" t="n">
+        <v>9.6</v>
+      </c>
       <c r="V114" t="inlineStr"/>
       <c r="W114" s="2" t="n">
         <v>141.8</v>
@@ -8934,7 +9208,9 @@
       <c r="T115" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U115" s="2" t="inlineStr"/>
+      <c r="U115" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V115" t="inlineStr"/>
       <c r="W115" s="2" t="n">
         <v>143.3</v>
@@ -9007,7 +9283,9 @@
       <c r="T116" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U116" s="2" t="inlineStr"/>
+      <c r="U116" s="2" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V116" t="inlineStr"/>
       <c r="W116" s="2" t="n">
         <v>145</v>
@@ -9084,7 +9362,9 @@
       <c r="T117" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U117" s="2" t="inlineStr"/>
+      <c r="U117" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V117" t="inlineStr"/>
       <c r="W117" s="2" t="n">
         <v>147</v>
@@ -9157,7 +9437,9 @@
       <c r="T118" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U118" s="2" t="inlineStr"/>
+      <c r="U118" s="2" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V118" t="inlineStr"/>
       <c r="W118" s="2" t="n">
         <v>143.7</v>
@@ -9230,7 +9512,9 @@
       <c r="T119" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U119" s="2" t="inlineStr"/>
+      <c r="U119" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V119" t="inlineStr"/>
       <c r="W119" s="2" t="n">
         <v>146.7</v>
@@ -9303,7 +9587,9 @@
       <c r="T120" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U120" s="2" t="inlineStr"/>
+      <c r="U120" s="2" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V120" t="inlineStr"/>
       <c r="W120" s="2" t="n">
         <v>151.1</v>
@@ -9376,7 +9662,9 @@
       <c r="T121" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U121" s="2" t="inlineStr"/>
+      <c r="U121" s="2" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V121" t="inlineStr"/>
       <c r="W121" s="2" t="n">
         <v>150.4</v>
@@ -9449,7 +9737,9 @@
       <c r="T122" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U122" s="2" t="inlineStr"/>
+      <c r="U122" s="2" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V122" t="inlineStr"/>
       <c r="W122" s="2" t="n">
         <v>154.8</v>
@@ -9522,7 +9812,9 @@
       <c r="T123" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U123" s="2" t="inlineStr"/>
+      <c r="U123" s="2" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V123" t="inlineStr"/>
       <c r="W123" s="2" t="n">
         <v>153.4</v>
@@ -9595,7 +9887,9 @@
       <c r="T124" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U124" s="2" t="inlineStr"/>
+      <c r="U124" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V124" t="inlineStr"/>
       <c r="W124" s="1" t="n">
         <v>159.3</v>
@@ -9668,7 +9962,9 @@
       <c r="T125" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U125" s="2" t="inlineStr"/>
+      <c r="U125" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V125" t="inlineStr"/>
       <c r="W125" s="1" t="n">
         <v>159.4</v>
@@ -9745,7 +10041,9 @@
       <c r="T126" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U126" s="2" t="inlineStr"/>
+      <c r="U126" s="2" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V126" t="inlineStr"/>
       <c r="W126" s="2" t="n">
         <v>145.6</v>
@@ -9822,7 +10120,9 @@
       <c r="T127" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U127" s="2" t="inlineStr"/>
+      <c r="U127" s="2" t="n">
+        <v>7.9</v>
+      </c>
       <c r="V127" t="inlineStr"/>
       <c r="W127" s="2" t="n">
         <v>147.6</v>
@@ -9895,7 +10195,9 @@
       <c r="T128" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U128" s="2" t="inlineStr"/>
+      <c r="U128" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V128" t="inlineStr"/>
       <c r="W128" s="2" t="n">
         <v>149.1</v>
@@ -9968,7 +10270,9 @@
       <c r="T129" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="U129" s="2" t="inlineStr"/>
+      <c r="U129" s="2" t="n">
+        <v>13.8</v>
+      </c>
       <c r="V129" t="inlineStr"/>
       <c r="W129" s="2" t="n">
         <v>154.1</v>
@@ -10041,7 +10345,9 @@
       <c r="T130" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U130" s="2" t="inlineStr"/>
+      <c r="U130" s="2" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V130" t="inlineStr"/>
       <c r="W130" s="2" t="n">
         <v>152.3</v>
@@ -10114,7 +10420,9 @@
       <c r="T131" s="2" t="n">
         <v>20.4</v>
       </c>
-      <c r="U131" s="2" t="inlineStr"/>
+      <c r="U131" s="2" t="n">
+        <v>20</v>
+      </c>
       <c r="V131" t="inlineStr"/>
       <c r="W131" s="1" t="n">
         <v>155.5</v>
@@ -10187,7 +10495,9 @@
       <c r="T132" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U132" s="2" t="inlineStr"/>
+      <c r="U132" s="2" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V132" t="inlineStr"/>
       <c r="W132" s="1" t="n">
         <v>159.3</v>
@@ -10260,7 +10570,9 @@
       <c r="T133" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U133" s="2" t="inlineStr"/>
+      <c r="U133" s="2" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V133" t="inlineStr"/>
       <c r="W133" s="2" t="n">
         <v>149.9</v>
@@ -10333,7 +10645,9 @@
       <c r="T134" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U134" s="2" t="inlineStr"/>
+      <c r="U134" s="2" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V134" t="inlineStr"/>
       <c r="W134" s="2" t="n">
         <v>149.7</v>
@@ -10406,7 +10720,9 @@
       <c r="T135" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U135" s="2" t="inlineStr"/>
+      <c r="U135" s="2" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V135" t="inlineStr"/>
       <c r="W135" s="2" t="n">
         <v>147</v>
@@ -10479,7 +10795,9 @@
       <c r="T136" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U136" s="2" t="inlineStr"/>
+      <c r="U136" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V136" t="inlineStr"/>
       <c r="W136" s="2" t="n">
         <v>147.5</v>
@@ -10556,7 +10874,9 @@
       <c r="T137" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U137" s="2" t="inlineStr"/>
+      <c r="U137" s="2" t="n">
+        <v>15.9</v>
+      </c>
       <c r="V137" t="inlineStr"/>
       <c r="W137" s="2" t="n">
         <v>148.6</v>
@@ -10629,7 +10949,9 @@
       <c r="T138" s="2" t="n">
         <v>14.7</v>
       </c>
-      <c r="U138" s="2" t="inlineStr"/>
+      <c r="U138" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V138" t="inlineStr"/>
       <c r="W138" s="2" t="n">
         <v>151.4</v>
@@ -10702,7 +11024,9 @@
       <c r="T139" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U139" s="2" t="inlineStr"/>
+      <c r="U139" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V139" t="inlineStr"/>
       <c r="W139" s="2" t="n">
         <v>153.1</v>
@@ -10779,7 +11103,9 @@
       <c r="T140" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U140" s="2" t="inlineStr"/>
+      <c r="U140" s="2" t="n">
+        <v>11.9</v>
+      </c>
       <c r="V140" t="inlineStr"/>
       <c r="W140" s="2" t="n">
         <v>150.6</v>
@@ -10852,7 +11178,9 @@
       <c r="T141" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U141" s="2" t="inlineStr"/>
+      <c r="U141" s="2" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V141" t="inlineStr"/>
       <c r="W141" s="2" t="n">
         <v>153.8</v>
@@ -10925,7 +11253,9 @@
       <c r="T142" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U142" s="2" t="inlineStr"/>
+      <c r="U142" s="2" t="n">
+        <v>7.8</v>
+      </c>
       <c r="V142" t="inlineStr"/>
       <c r="W142" s="2" t="n">
         <v>153.9</v>
@@ -10998,7 +11328,9 @@
       <c r="T143" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U143" s="2" t="inlineStr"/>
+      <c r="U143" s="2" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V143" t="inlineStr"/>
       <c r="W143" s="2" t="n">
         <v>153.2</v>
@@ -11071,7 +11403,9 @@
       <c r="T144" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U144" s="2" t="inlineStr"/>
+      <c r="U144" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V144" t="inlineStr"/>
       <c r="W144" s="2" t="n">
         <v>144.6</v>
@@ -11148,7 +11482,9 @@
       <c r="T145" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U145" s="2" t="inlineStr"/>
+      <c r="U145" s="2" t="n">
+        <v>18.2</v>
+      </c>
       <c r="V145" t="inlineStr"/>
       <c r="W145" s="2" t="n">
         <v>144.3</v>
@@ -11221,7 +11557,9 @@
       <c r="T146" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="U146" s="2" t="inlineStr"/>
+      <c r="U146" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V146" t="inlineStr"/>
       <c r="W146" s="2" t="n">
         <v>146.4</v>
@@ -11294,7 +11632,9 @@
       <c r="T147" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U147" s="2" t="inlineStr"/>
+      <c r="U147" s="2" t="n">
+        <v>8.1</v>
+      </c>
       <c r="V147" t="inlineStr"/>
       <c r="W147" s="2" t="n">
         <v>150</v>
@@ -11367,7 +11707,9 @@
       <c r="T148" s="2" t="n">
         <v>14.6</v>
       </c>
-      <c r="U148" s="2" t="inlineStr"/>
+      <c r="U148" s="2" t="n">
+        <v>7.8</v>
+      </c>
       <c r="V148" t="inlineStr"/>
       <c r="W148" s="1" t="n">
         <v>156.5</v>
@@ -11440,7 +11782,9 @@
       <c r="T149" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U149" s="2" t="inlineStr"/>
+      <c r="U149" s="2" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V149" t="inlineStr"/>
       <c r="W149" s="2" t="n">
         <v>150.9</v>
@@ -11513,7 +11857,9 @@
       <c r="T150" s="2" t="n">
         <v>14.4</v>
       </c>
-      <c r="U150" s="2" t="inlineStr"/>
+      <c r="U150" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V150" t="inlineStr"/>
       <c r="W150" s="2" t="n">
         <v>152.5</v>
@@ -11586,7 +11932,9 @@
       <c r="T151" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U151" s="2" t="inlineStr"/>
+      <c r="U151" s="2" t="n">
+        <v>11.6</v>
+      </c>
       <c r="V151" t="inlineStr"/>
       <c r="W151" s="2" t="n">
         <v>152.1</v>
@@ -11659,7 +12007,9 @@
       <c r="T152" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U152" s="2" t="inlineStr"/>
+      <c r="U152" s="2" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V152" t="inlineStr"/>
       <c r="W152" s="2" t="n">
         <v>151.5</v>
@@ -11732,7 +12082,9 @@
       <c r="T153" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U153" s="2" t="inlineStr"/>
+      <c r="U153" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V153" t="inlineStr"/>
       <c r="W153" s="2" t="n">
         <v>150.2</v>
@@ -11805,7 +12157,9 @@
       <c r="T154" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U154" s="2" t="inlineStr"/>
+      <c r="U154" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V154" t="inlineStr"/>
       <c r="W154" s="2" t="n">
         <v>154</v>
@@ -11878,7 +12232,9 @@
       <c r="T155" s="2" t="n">
         <v>15.2</v>
       </c>
-      <c r="U155" s="2" t="inlineStr"/>
+      <c r="U155" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V155" t="inlineStr"/>
       <c r="W155" s="2" t="n">
         <v>148.2</v>
@@ -11951,7 +12307,9 @@
       <c r="T156" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U156" s="2" t="inlineStr"/>
+      <c r="U156" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="V156" t="inlineStr"/>
       <c r="W156" s="2" t="n">
         <v>148.8</v>
@@ -12024,7 +12382,9 @@
       <c r="T157" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U157" s="2" t="inlineStr"/>
+      <c r="U157" s="2" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V157" t="inlineStr"/>
       <c r="W157" s="2" t="n">
         <v>150.9</v>
@@ -12097,7 +12457,9 @@
       <c r="T158" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U158" s="2" t="inlineStr"/>
+      <c r="U158" s="2" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V158" t="inlineStr"/>
       <c r="W158" s="2" t="n">
         <v>151.9</v>
@@ -12170,7 +12532,9 @@
       <c r="T159" s="2" t="n">
         <v>14.7</v>
       </c>
-      <c r="U159" s="2" t="inlineStr"/>
+      <c r="U159" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V159" t="inlineStr"/>
       <c r="W159" s="2" t="n">
         <v>147.6</v>
@@ -12243,7 +12607,9 @@
       <c r="T160" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U160" s="2" t="inlineStr"/>
+      <c r="U160" s="2" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V160" t="inlineStr"/>
       <c r="W160" s="2" t="n">
         <v>149.5</v>
@@ -12316,7 +12682,9 @@
       <c r="T161" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U161" s="2" t="inlineStr"/>
+      <c r="U161" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="V161" t="inlineStr"/>
       <c r="W161" s="2" t="n">
         <v>152.1</v>
@@ -12389,7 +12757,9 @@
       <c r="T162" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U162" s="2" t="inlineStr"/>
+      <c r="U162" s="2" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V162" t="inlineStr"/>
       <c r="W162" s="2" t="n">
         <v>148.2</v>
@@ -12462,7 +12832,9 @@
       <c r="T163" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U163" s="2" t="inlineStr"/>
+      <c r="U163" s="2" t="n">
+        <v>14.8</v>
+      </c>
       <c r="V163" t="inlineStr"/>
       <c r="W163" s="2" t="n">
         <v>146.4</v>
@@ -12535,7 +12907,9 @@
       <c r="T164" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U164" s="2" t="inlineStr"/>
+      <c r="U164" s="2" t="n">
+        <v>14.4</v>
+      </c>
       <c r="V164" t="inlineStr"/>
       <c r="W164" s="2" t="n">
         <v>148.2</v>
@@ -12608,7 +12982,9 @@
       <c r="T165" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U165" s="2" t="inlineStr"/>
+      <c r="U165" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V165" t="inlineStr"/>
       <c r="W165" s="2" t="n">
         <v>147</v>
@@ -12681,7 +13057,9 @@
       <c r="T166" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U166" s="2" t="inlineStr"/>
+      <c r="U166" s="2" t="n">
+        <v>9.1</v>
+      </c>
       <c r="V166" t="inlineStr"/>
       <c r="W166" s="2" t="n">
         <v>145.5</v>
@@ -12754,7 +13132,9 @@
       <c r="T167" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U167" s="2" t="inlineStr"/>
+      <c r="U167" s="2" t="n">
+        <v>9.699999999999999</v>
+      </c>
       <c r="V167" t="inlineStr"/>
       <c r="W167" s="2" t="n">
         <v>146.5</v>
@@ -12827,7 +13207,9 @@
       <c r="T168" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U168" s="2" t="inlineStr"/>
+      <c r="U168" s="2" t="n">
+        <v>9.4</v>
+      </c>
       <c r="V168" t="inlineStr"/>
       <c r="W168" s="2" t="n">
         <v>145.9</v>
@@ -12900,7 +13282,9 @@
       <c r="T169" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U169" s="2" t="inlineStr"/>
+      <c r="U169" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V169" t="inlineStr"/>
       <c r="W169" s="2" t="n">
         <v>145.9</v>
@@ -12973,7 +13357,9 @@
       <c r="T170" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U170" s="2" t="inlineStr"/>
+      <c r="U170" s="2" t="n">
+        <v>10.3</v>
+      </c>
       <c r="V170" t="inlineStr"/>
       <c r="W170" s="2" t="n">
         <v>141.5</v>
@@ -13046,7 +13432,9 @@
       <c r="T171" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U171" s="2" t="inlineStr"/>
+      <c r="U171" s="2" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V171" t="inlineStr"/>
       <c r="W171" s="2" t="n">
         <v>143</v>
@@ -13119,7 +13507,9 @@
       <c r="T172" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U172" s="2" t="inlineStr"/>
+      <c r="U172" s="2" t="n">
+        <v>12</v>
+      </c>
       <c r="V172" t="inlineStr"/>
       <c r="W172" s="2" t="n">
         <v>143.4</v>
@@ -13192,7 +13582,9 @@
       <c r="T173" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U173" s="2" t="inlineStr"/>
+      <c r="U173" s="2" t="n">
+        <v>10.3</v>
+      </c>
       <c r="V173" t="inlineStr"/>
       <c r="W173" s="2" t="n">
         <v>143.7</v>
@@ -13265,7 +13657,9 @@
       <c r="T174" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U174" s="2" t="inlineStr"/>
+      <c r="U174" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V174" t="inlineStr"/>
       <c r="W174" s="2" t="n">
         <v>145.9</v>
@@ -13338,7 +13732,9 @@
       <c r="T175" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U175" s="2" t="inlineStr"/>
+      <c r="U175" s="2" t="n">
+        <v>11.9</v>
+      </c>
       <c r="V175" t="inlineStr"/>
       <c r="W175" s="2" t="n">
         <v>144.6</v>
@@ -13411,7 +13807,9 @@
       <c r="T176" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U176" s="2" t="inlineStr"/>
+      <c r="U176" s="2" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V176" t="inlineStr"/>
       <c r="W176" s="2" t="n">
         <v>142.5</v>
@@ -13484,7 +13882,9 @@
       <c r="T177" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U177" s="2" t="inlineStr"/>
+      <c r="U177" s="2" t="n">
+        <v>11.3</v>
+      </c>
       <c r="V177" t="inlineStr"/>
       <c r="W177" s="2" t="n">
         <v>145.2</v>
@@ -13557,7 +13957,9 @@
       <c r="T178" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U178" s="2" t="inlineStr"/>
+      <c r="U178" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V178" t="inlineStr"/>
       <c r="W178" s="2" t="n">
         <v>145.8</v>
@@ -13630,7 +14032,9 @@
       <c r="T179" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U179" s="2" t="inlineStr"/>
+      <c r="U179" s="2" t="n">
+        <v>11.3</v>
+      </c>
       <c r="V179" t="inlineStr"/>
       <c r="W179" s="2" t="n">
         <v>145.3</v>
@@ -13703,7 +14107,9 @@
       <c r="T180" s="2" t="n">
         <v>21.7</v>
       </c>
-      <c r="U180" s="2" t="inlineStr"/>
+      <c r="U180" s="3" t="n">
+        <v>25.7</v>
+      </c>
       <c r="V180" t="inlineStr"/>
       <c r="W180" s="2" t="n">
         <v>138.9</v>
@@ -13776,7 +14182,9 @@
       <c r="T181" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U181" s="2" t="inlineStr"/>
+      <c r="U181" s="2" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V181" t="inlineStr"/>
       <c r="W181" s="2" t="n">
         <v>142.8</v>
@@ -13849,7 +14257,9 @@
       <c r="T182" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U182" s="2" t="inlineStr"/>
+      <c r="U182" s="2" t="n">
+        <v>17.7</v>
+      </c>
       <c r="V182" t="inlineStr"/>
       <c r="W182" s="2" t="n">
         <v>146.5</v>
@@ -13922,7 +14332,9 @@
       <c r="T183" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U183" s="2" t="inlineStr"/>
+      <c r="U183" s="2" t="n">
+        <v>17.1</v>
+      </c>
       <c r="V183" t="inlineStr"/>
       <c r="W183" s="2" t="n">
         <v>145</v>
@@ -13995,7 +14407,9 @@
       <c r="T184" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="U184" s="2" t="inlineStr"/>
+      <c r="U184" s="2" t="n">
+        <v>23.8</v>
+      </c>
       <c r="V184" t="inlineStr"/>
       <c r="W184" s="2" t="n">
         <v>147.1</v>
@@ -14068,7 +14482,9 @@
       <c r="T185" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U185" s="2" t="inlineStr"/>
+      <c r="U185" s="2" t="n">
+        <v>17.9</v>
+      </c>
       <c r="V185" t="inlineStr"/>
       <c r="W185" s="2" t="n">
         <v>147.6</v>
@@ -14141,7 +14557,9 @@
       <c r="T186" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U186" s="2" t="inlineStr"/>
+      <c r="U186" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V186" t="inlineStr"/>
       <c r="W186" s="2" t="n">
         <v>151.3</v>
@@ -14214,7 +14632,9 @@
       <c r="T187" s="6" t="n">
         <v>17.9</v>
       </c>
-      <c r="U187" s="6" t="inlineStr"/>
+      <c r="U187" s="6" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V187" s="4" t="inlineStr"/>
       <c r="W187" s="6" t="n">
         <v>149.9</v>
@@ -14287,7 +14707,9 @@
       <c r="T188" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U188" s="2" t="inlineStr"/>
+      <c r="U188" s="2" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V188" t="inlineStr"/>
       <c r="W188" s="2" t="n">
         <v>152.9</v>
@@ -14360,7 +14782,9 @@
       <c r="T189" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U189" s="2" t="inlineStr"/>
+      <c r="U189" s="2" t="n">
+        <v>13.8</v>
+      </c>
       <c r="V189" t="inlineStr"/>
       <c r="W189" s="2" t="n">
         <v>154.3</v>
@@ -14433,7 +14857,9 @@
       <c r="T190" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U190" s="2" t="inlineStr"/>
+      <c r="U190" s="2" t="n">
+        <v>14.5</v>
+      </c>
       <c r="V190" t="inlineStr"/>
       <c r="W190" s="2" t="n">
         <v>153.5</v>
@@ -14510,7 +14936,9 @@
       <c r="T191" s="6" t="n">
         <v>15.8</v>
       </c>
-      <c r="U191" s="6" t="inlineStr"/>
+      <c r="U191" s="6" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V191" s="4" t="inlineStr"/>
       <c r="W191" s="6" t="n">
         <v>148.5</v>
@@ -14583,7 +15011,9 @@
       <c r="T192" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U192" s="2" t="inlineStr"/>
+      <c r="U192" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V192" t="inlineStr"/>
       <c r="W192" s="2" t="n">
         <v>140.4</v>
@@ -14656,7 +15086,9 @@
       <c r="T193" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U193" s="2" t="inlineStr"/>
+      <c r="U193" s="2" t="n">
+        <v>15.2</v>
+      </c>
       <c r="V193" t="inlineStr"/>
       <c r="W193" s="2" t="n">
         <v>139.4</v>
@@ -14729,7 +15161,9 @@
       <c r="T194" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U194" s="2" t="inlineStr"/>
+      <c r="U194" s="2" t="n">
+        <v>14.2</v>
+      </c>
       <c r="V194" t="inlineStr"/>
       <c r="W194" s="2" t="n">
         <v>141.1</v>
@@ -14802,7 +15236,9 @@
       <c r="T195" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U195" s="2" t="inlineStr"/>
+      <c r="U195" s="2" t="n">
+        <v>13.8</v>
+      </c>
       <c r="V195" t="inlineStr"/>
       <c r="W195" s="2" t="n">
         <v>142.8</v>
@@ -14875,7 +15311,9 @@
       <c r="T196" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U196" s="2" t="inlineStr"/>
+      <c r="U196" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V196" t="inlineStr"/>
       <c r="W196" s="2" t="n">
         <v>142</v>
@@ -14948,7 +15386,9 @@
       <c r="T197" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U197" s="2" t="inlineStr"/>
+      <c r="U197" s="2" t="n">
+        <v>15.2</v>
+      </c>
       <c r="V197" t="inlineStr"/>
       <c r="W197" s="2" t="n">
         <v>144</v>
@@ -15021,7 +15461,9 @@
       <c r="T198" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U198" s="2" t="inlineStr"/>
+      <c r="U198" s="2" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V198" t="inlineStr"/>
       <c r="W198" s="2" t="n">
         <v>143.6</v>
@@ -15094,7 +15536,9 @@
       <c r="T199" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U199" s="2" t="inlineStr"/>
+      <c r="U199" s="2" t="n">
+        <v>15.9</v>
+      </c>
       <c r="V199" t="inlineStr"/>
       <c r="W199" s="2" t="n">
         <v>143.5</v>
@@ -15167,7 +15611,9 @@
       <c r="T200" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U200" s="2" t="inlineStr"/>
+      <c r="U200" s="2" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V200" t="inlineStr"/>
       <c r="W200" s="2" t="n">
         <v>141.3</v>
@@ -15240,7 +15686,9 @@
       <c r="T201" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U201" s="2" t="inlineStr"/>
+      <c r="U201" s="2" t="n">
+        <v>11.2</v>
+      </c>
       <c r="V201" t="inlineStr"/>
       <c r="W201" s="2" t="n">
         <v>142.9</v>
@@ -15313,7 +15761,9 @@
       <c r="T202" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U202" s="2" t="inlineStr"/>
+      <c r="U202" s="2" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V202" t="inlineStr"/>
       <c r="W202" s="2" t="n">
         <v>143.4</v>
@@ -15386,7 +15836,9 @@
       <c r="T203" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U203" s="2" t="inlineStr"/>
+      <c r="U203" s="2" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V203" t="inlineStr"/>
       <c r="W203" s="2" t="n">
         <v>138.6</v>
@@ -15459,7 +15911,9 @@
       <c r="T204" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="U204" s="2" t="inlineStr"/>
+      <c r="U204" s="2" t="n">
+        <v>17</v>
+      </c>
       <c r="V204" t="inlineStr"/>
       <c r="W204" s="2" t="n">
         <v>142.5</v>
@@ -15532,7 +15986,9 @@
       <c r="T205" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U205" s="2" t="inlineStr"/>
+      <c r="U205" s="2" t="n">
+        <v>18.5</v>
+      </c>
       <c r="V205" t="inlineStr"/>
       <c r="W205" s="2" t="n">
         <v>137.9</v>
@@ -15609,7 +16065,9 @@
       <c r="T206" s="2" t="n">
         <v>22.4</v>
       </c>
-      <c r="U206" s="2" t="inlineStr"/>
+      <c r="U206" s="2" t="n">
+        <v>19.4</v>
+      </c>
       <c r="V206" t="inlineStr"/>
       <c r="W206" s="2" t="n">
         <v>140.9</v>
@@ -15682,7 +16140,9 @@
       <c r="T207" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U207" s="2" t="inlineStr"/>
+      <c r="U207" s="2" t="n">
+        <v>20.9</v>
+      </c>
       <c r="V207" t="inlineStr"/>
       <c r="W207" s="2" t="n">
         <v>143</v>
@@ -15755,7 +16215,9 @@
       <c r="T208" s="2" t="n">
         <v>23.7</v>
       </c>
-      <c r="U208" s="2" t="inlineStr"/>
+      <c r="U208" s="3" t="n">
+        <v>26.9</v>
+      </c>
       <c r="V208" t="inlineStr"/>
       <c r="W208" s="2" t="n">
         <v>143.1</v>
@@ -15828,8 +16290,14 @@
       <c r="T209" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="U209" s="2" t="inlineStr"/>
-      <c r="V209" t="inlineStr"/>
+      <c r="U209" s="3" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="V209" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W209" s="2" t="n">
         <v>145</v>
       </c>
@@ -15901,7 +16369,9 @@
       <c r="T210" s="2" t="n">
         <v>23.4</v>
       </c>
-      <c r="U210" s="2" t="inlineStr"/>
+      <c r="U210" s="2" t="n">
+        <v>23.3</v>
+      </c>
       <c r="V210" t="inlineStr"/>
       <c r="W210" s="2" t="n">
         <v>148.3</v>
@@ -15974,7 +16444,9 @@
       <c r="T211" s="2" t="n">
         <v>20.5</v>
       </c>
-      <c r="U211" s="2" t="inlineStr"/>
+      <c r="U211" s="2" t="n">
+        <v>14.3</v>
+      </c>
       <c r="V211" t="inlineStr"/>
       <c r="W211" s="2" t="n">
         <v>148.6</v>
@@ -16047,7 +16519,9 @@
       <c r="T212" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U212" s="2" t="inlineStr"/>
+      <c r="U212" s="2" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V212" t="inlineStr"/>
       <c r="W212" s="2" t="n">
         <v>151.7</v>
@@ -16120,7 +16594,9 @@
       <c r="T213" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U213" s="2" t="inlineStr"/>
+      <c r="U213" s="2" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V213" t="inlineStr"/>
       <c r="W213" s="2" t="n">
         <v>145</v>
@@ -16193,7 +16669,9 @@
       <c r="T214" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U214" s="2" t="inlineStr"/>
+      <c r="U214" s="2" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V214" t="inlineStr"/>
       <c r="W214" s="2" t="n">
         <v>143</v>
@@ -16266,7 +16744,9 @@
       <c r="T215" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U215" s="2" t="inlineStr"/>
+      <c r="U215" s="2" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V215" t="inlineStr"/>
       <c r="W215" s="2" t="n">
         <v>144.9</v>
@@ -16339,7 +16819,9 @@
       <c r="T216" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U216" s="2" t="inlineStr"/>
+      <c r="U216" s="2" t="n">
+        <v>10.5</v>
+      </c>
       <c r="V216" t="inlineStr"/>
       <c r="W216" s="2" t="n">
         <v>144.9</v>
@@ -16412,7 +16894,9 @@
       <c r="T217" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U217" s="2" t="inlineStr"/>
+      <c r="U217" s="2" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="V217" t="inlineStr"/>
       <c r="W217" s="2" t="n">
         <v>149.2</v>
@@ -16485,7 +16969,9 @@
       <c r="T218" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U218" s="2" t="inlineStr"/>
+      <c r="U218" s="2" t="n">
+        <v>10.3</v>
+      </c>
       <c r="V218" t="inlineStr"/>
       <c r="W218" s="2" t="n">
         <v>148.9</v>
@@ -16558,7 +17044,9 @@
       <c r="T219" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U219" s="2" t="inlineStr"/>
+      <c r="U219" s="2" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V219" t="inlineStr"/>
       <c r="W219" s="2" t="n">
         <v>148.8</v>
@@ -16631,7 +17119,9 @@
       <c r="T220" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U220" s="2" t="inlineStr"/>
+      <c r="U220" s="2" t="n">
+        <v>9.4</v>
+      </c>
       <c r="V220" t="inlineStr"/>
       <c r="W220" s="2" t="n">
         <v>150.6</v>
@@ -16704,7 +17194,9 @@
       <c r="T221" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U221" s="2" t="inlineStr"/>
+      <c r="U221" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V221" t="inlineStr"/>
       <c r="W221" s="2" t="n">
         <v>150.3</v>
@@ -16777,7 +17269,9 @@
       <c r="T222" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U222" s="2" t="inlineStr"/>
+      <c r="U222" s="2" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V222" t="inlineStr"/>
       <c r="W222" s="2" t="n">
         <v>147.6</v>
@@ -16850,7 +17344,9 @@
       <c r="T223" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U223" s="2" t="inlineStr"/>
+      <c r="U223" s="2" t="n">
+        <v>10.7</v>
+      </c>
       <c r="V223" t="inlineStr"/>
       <c r="W223" s="2" t="n">
         <v>148.3</v>
@@ -16923,7 +17419,9 @@
       <c r="T224" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U224" s="2" t="inlineStr"/>
+      <c r="U224" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V224" t="inlineStr"/>
       <c r="W224" s="2" t="n">
         <v>153.6</v>
@@ -16996,7 +17494,9 @@
       <c r="T225" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U225" s="2" t="inlineStr"/>
+      <c r="U225" s="2" t="n">
+        <v>12.9</v>
+      </c>
       <c r="V225" t="inlineStr"/>
       <c r="W225" s="1" t="n">
         <v>161.9</v>
@@ -17069,7 +17569,9 @@
       <c r="T226" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U226" s="2" t="inlineStr"/>
+      <c r="U226" s="2" t="n">
+        <v>11.9</v>
+      </c>
       <c r="V226" t="inlineStr"/>
       <c r="W226" s="1" t="n">
         <v>157</v>
@@ -17142,7 +17644,9 @@
       <c r="T227" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U227" s="2" t="inlineStr"/>
+      <c r="U227" s="2" t="n">
+        <v>16.9</v>
+      </c>
       <c r="V227" t="inlineStr"/>
       <c r="W227" s="2" t="n">
         <v>153.5</v>
@@ -17215,7 +17719,9 @@
       <c r="T228" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U228" s="2" t="inlineStr"/>
+      <c r="U228" s="2" t="n">
+        <v>15.8</v>
+      </c>
       <c r="V228" t="inlineStr"/>
       <c r="W228" s="1" t="n">
         <v>155.4</v>
@@ -17288,7 +17794,9 @@
       <c r="T229" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U229" s="2" t="inlineStr"/>
+      <c r="U229" s="2" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V229" t="inlineStr"/>
       <c r="W229" s="1" t="n">
         <v>155.9</v>
@@ -17361,7 +17869,9 @@
       <c r="T230" s="2" t="n">
         <v>14.1</v>
       </c>
-      <c r="U230" s="2" t="inlineStr"/>
+      <c r="U230" s="2" t="n">
+        <v>7.7</v>
+      </c>
       <c r="V230" t="inlineStr"/>
       <c r="W230" s="1" t="n">
         <v>159.9</v>
@@ -17434,7 +17944,9 @@
       <c r="T231" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="U231" s="2" t="inlineStr"/>
+      <c r="U231" s="2" t="n">
+        <v>7.6</v>
+      </c>
       <c r="V231" t="inlineStr"/>
       <c r="W231" s="1" t="n">
         <v>160.5</v>
@@ -17507,7 +18019,9 @@
       <c r="T232" s="2" t="n">
         <v>13.5</v>
       </c>
-      <c r="U232" s="2" t="inlineStr"/>
+      <c r="U232" s="2" t="n">
+        <v>7.4</v>
+      </c>
       <c r="V232" t="inlineStr"/>
       <c r="W232" s="1" t="n">
         <v>160.5</v>
@@ -17580,7 +18094,9 @@
       <c r="T233" s="2" t="n">
         <v>13.6</v>
       </c>
-      <c r="U233" s="2" t="inlineStr"/>
+      <c r="U233" s="2" t="n">
+        <v>7.7</v>
+      </c>
       <c r="V233" t="inlineStr"/>
       <c r="W233" s="2" t="n">
         <v>151.4</v>
@@ -17653,7 +18169,9 @@
       <c r="T234" s="6" t="n">
         <v>14.2</v>
       </c>
-      <c r="U234" s="6" t="inlineStr"/>
+      <c r="U234" s="6" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="V234" s="4" t="inlineStr"/>
       <c r="W234" s="6" t="n">
         <v>150.5</v>
@@ -17726,7 +18244,9 @@
       <c r="T235" s="2" t="n">
         <v>14.3</v>
       </c>
-      <c r="U235" s="2" t="inlineStr"/>
+      <c r="U235" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V235" t="inlineStr"/>
       <c r="W235" s="2" t="n">
         <v>148.3</v>
@@ -17803,7 +18323,9 @@
       <c r="T236" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U236" s="2" t="inlineStr"/>
+      <c r="U236" s="2" t="n">
+        <v>10.7</v>
+      </c>
       <c r="V236" t="inlineStr"/>
       <c r="W236" s="2" t="n">
         <v>148.7</v>
@@ -17876,7 +18398,9 @@
       <c r="T237" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U237" s="2" t="inlineStr"/>
+      <c r="U237" s="2" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V237" t="inlineStr"/>
       <c r="W237" s="2" t="n">
         <v>141.9</v>
@@ -17949,7 +18473,9 @@
       <c r="T238" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U238" s="2" t="inlineStr"/>
+      <c r="U238" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="V238" t="inlineStr"/>
       <c r="W238" s="2" t="n">
         <v>142.4</v>
@@ -18022,7 +18548,9 @@
       <c r="T239" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U239" s="2" t="inlineStr"/>
+      <c r="U239" s="2" t="n">
+        <v>8</v>
+      </c>
       <c r="V239" t="inlineStr"/>
       <c r="W239" s="2" t="n">
         <v>146.2</v>
@@ -18095,7 +18623,9 @@
       <c r="T240" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U240" s="2" t="inlineStr"/>
+      <c r="U240" s="2" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="V240" t="inlineStr"/>
       <c r="W240" s="2" t="n">
         <v>143.6</v>
@@ -18168,7 +18698,9 @@
       <c r="T241" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U241" s="2" t="inlineStr"/>
+      <c r="U241" s="2" t="n">
+        <v>13.6</v>
+      </c>
       <c r="V241" t="inlineStr"/>
       <c r="W241" s="2" t="n">
         <v>147.1</v>
@@ -18241,7 +18773,9 @@
       <c r="T242" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U242" s="2" t="inlineStr"/>
+      <c r="U242" s="2" t="n">
+        <v>8.5</v>
+      </c>
       <c r="V242" t="inlineStr"/>
       <c r="W242" s="2" t="n">
         <v>146</v>
@@ -18314,7 +18848,9 @@
       <c r="T243" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U243" s="2" t="inlineStr"/>
+      <c r="U243" s="2" t="n">
+        <v>9.6</v>
+      </c>
       <c r="V243" t="inlineStr"/>
       <c r="W243" s="2" t="n">
         <v>149.8</v>
@@ -18387,7 +18923,9 @@
       <c r="T244" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U244" s="2" t="inlineStr"/>
+      <c r="U244" s="2" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V244" t="inlineStr"/>
       <c r="W244" s="2" t="n">
         <v>151.6</v>
@@ -18460,7 +18998,9 @@
       <c r="T245" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U245" s="2" t="inlineStr"/>
+      <c r="U245" s="2" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V245" t="inlineStr"/>
       <c r="W245" s="2" t="n">
         <v>152.5</v>
@@ -18533,7 +19073,9 @@
       <c r="T246" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U246" s="2" t="inlineStr"/>
+      <c r="U246" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V246" t="inlineStr"/>
       <c r="W246" s="2" t="n">
         <v>151.6</v>
@@ -18606,7 +19148,9 @@
       <c r="T247" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U247" s="2" t="inlineStr"/>
+      <c r="U247" s="2" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V247" t="inlineStr"/>
       <c r="W247" s="2" t="n">
         <v>153.6</v>
@@ -18679,7 +19223,9 @@
       <c r="T248" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="U248" s="2" t="inlineStr"/>
+      <c r="U248" s="2" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V248" t="inlineStr"/>
       <c r="W248" s="1" t="n">
         <v>155</v>
@@ -18752,7 +19298,9 @@
       <c r="T249" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U249" s="2" t="inlineStr"/>
+      <c r="U249" s="2" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V249" t="inlineStr"/>
       <c r="W249" s="2" t="n">
         <v>144.4</v>
@@ -18825,7 +19373,9 @@
       <c r="T250" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U250" s="2" t="inlineStr"/>
+      <c r="U250" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V250" t="inlineStr"/>
       <c r="W250" s="2" t="n">
         <v>141.3</v>
@@ -18898,7 +19448,9 @@
       <c r="T251" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U251" s="2" t="inlineStr"/>
+      <c r="U251" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V251" t="inlineStr"/>
       <c r="W251" s="2" t="n">
         <v>144</v>
@@ -18971,7 +19523,9 @@
       <c r="T252" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U252" s="2" t="inlineStr"/>
+      <c r="U252" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="V252" t="inlineStr"/>
       <c r="W252" s="2" t="n">
         <v>148.1</v>
@@ -19044,7 +19598,9 @@
       <c r="T253" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U253" s="2" t="inlineStr"/>
+      <c r="U253" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V253" t="inlineStr"/>
       <c r="W253" s="2" t="n">
         <v>147.2</v>
@@ -19117,7 +19673,9 @@
       <c r="T254" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U254" s="2" t="inlineStr"/>
+      <c r="U254" s="2" t="n">
+        <v>13.2</v>
+      </c>
       <c r="V254" t="inlineStr"/>
       <c r="W254" s="2" t="n">
         <v>145</v>
@@ -19190,7 +19748,9 @@
       <c r="T255" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U255" s="2" t="inlineStr"/>
+      <c r="U255" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V255" t="inlineStr"/>
       <c r="W255" s="2" t="n">
         <v>143.7</v>
@@ -19263,7 +19823,9 @@
       <c r="T256" s="6" t="n">
         <v>17.4</v>
       </c>
-      <c r="U256" s="6" t="inlineStr"/>
+      <c r="U256" s="6" t="n">
+        <v>16.4</v>
+      </c>
       <c r="V256" s="4" t="inlineStr"/>
       <c r="W256" s="6" t="n">
         <v>143.6</v>
@@ -19340,7 +19902,9 @@
       <c r="T257" s="6" t="n">
         <v>16.3</v>
       </c>
-      <c r="U257" s="6" t="inlineStr"/>
+      <c r="U257" s="6" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V257" s="4" t="inlineStr"/>
       <c r="W257" s="6" t="n">
         <v>146.6</v>
@@ -19413,7 +19977,9 @@
       <c r="T258" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U258" s="2" t="inlineStr"/>
+      <c r="U258" s="2" t="n">
+        <v>14.5</v>
+      </c>
       <c r="V258" t="inlineStr"/>
       <c r="W258" s="2" t="n">
         <v>143.9</v>
@@ -19486,7 +20052,9 @@
       <c r="T259" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U259" s="2" t="inlineStr"/>
+      <c r="U259" s="2" t="n">
+        <v>17.5</v>
+      </c>
       <c r="V259" t="inlineStr"/>
       <c r="W259" s="2" t="n">
         <v>143.2</v>
@@ -19563,7 +20131,9 @@
       <c r="T260" s="6" t="n">
         <v>21.8</v>
       </c>
-      <c r="U260" s="6" t="inlineStr"/>
+      <c r="U260" s="6" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V260" s="4" t="inlineStr"/>
       <c r="W260" s="6" t="n">
         <v>137.2</v>
@@ -19636,7 +20206,9 @@
       <c r="T261" s="2" t="n">
         <v>20.4</v>
       </c>
-      <c r="U261" s="2" t="inlineStr"/>
+      <c r="U261" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="V261" t="inlineStr"/>
       <c r="W261" s="2" t="n">
         <v>140.3</v>
@@ -19709,7 +20281,9 @@
       <c r="T262" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U262" s="2" t="inlineStr"/>
+      <c r="U262" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V262" t="inlineStr"/>
       <c r="W262" s="2" t="n">
         <v>145.2</v>
@@ -19782,7 +20356,9 @@
       <c r="T263" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U263" s="2" t="inlineStr"/>
+      <c r="U263" s="2" t="n">
+        <v>13.6</v>
+      </c>
       <c r="V263" t="inlineStr"/>
       <c r="W263" s="2" t="n">
         <v>145.7</v>
@@ -19855,7 +20431,9 @@
       <c r="T264" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U264" s="2" t="inlineStr"/>
+      <c r="U264" s="2" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V264" t="inlineStr"/>
       <c r="W264" s="2" t="n">
         <v>143.8</v>
@@ -19932,7 +20510,9 @@
       <c r="T265" s="6" t="n">
         <v>20.8</v>
       </c>
-      <c r="U265" s="6" t="inlineStr"/>
+      <c r="U265" s="6" t="n">
+        <v>21.5</v>
+      </c>
       <c r="V265" s="4" t="inlineStr"/>
       <c r="W265" s="6" t="n">
         <v>142.5</v>
@@ -20005,7 +20585,9 @@
       <c r="T266" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U266" s="2" t="inlineStr"/>
+      <c r="U266" s="2" t="n">
+        <v>22.4</v>
+      </c>
       <c r="V266" t="inlineStr"/>
       <c r="W266" s="2" t="n">
         <v>139.4</v>
@@ -20082,7 +20664,9 @@
       <c r="T267" s="6" t="n">
         <v>20.3</v>
       </c>
-      <c r="U267" s="6" t="inlineStr"/>
+      <c r="U267" s="6" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V267" s="4" t="inlineStr"/>
       <c r="W267" s="6" t="n">
         <v>140.3</v>
@@ -20155,7 +20739,9 @@
       <c r="T268" s="2" t="n">
         <v>19.6</v>
       </c>
-      <c r="U268" s="2" t="inlineStr"/>
+      <c r="U268" s="2" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V268" t="inlineStr"/>
       <c r="W268" s="2" t="n">
         <v>139.2</v>
@@ -20228,7 +20814,9 @@
       <c r="T269" s="2" t="n">
         <v>20.2</v>
       </c>
-      <c r="U269" s="2" t="inlineStr"/>
+      <c r="U269" s="2" t="n">
+        <v>16.6</v>
+      </c>
       <c r="V269" t="inlineStr"/>
       <c r="W269" s="2" t="n">
         <v>141.2</v>
@@ -20301,7 +20889,9 @@
       <c r="T270" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U270" s="2" t="inlineStr"/>
+      <c r="U270" s="2" t="n">
+        <v>17.8</v>
+      </c>
       <c r="V270" t="inlineStr"/>
       <c r="W270" s="2" t="n">
         <v>145.5</v>
@@ -20374,7 +20964,9 @@
       <c r="T271" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="U271" s="2" t="inlineStr"/>
+      <c r="U271" s="2" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V271" t="inlineStr"/>
       <c r="W271" s="2" t="n">
         <v>141.4</v>
@@ -20447,7 +21039,9 @@
       <c r="T272" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U272" s="2" t="inlineStr"/>
+      <c r="U272" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V272" t="inlineStr"/>
       <c r="W272" s="2" t="n">
         <v>141.9</v>
@@ -20520,7 +21114,9 @@
       <c r="T273" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U273" s="2" t="inlineStr"/>
+      <c r="U273" s="2" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V273" t="inlineStr"/>
       <c r="W273" s="2" t="n">
         <v>146.1</v>
@@ -20593,7 +21189,9 @@
       <c r="T274" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U274" s="2" t="inlineStr"/>
+      <c r="U274" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V274" t="inlineStr"/>
       <c r="W274" s="2" t="n">
         <v>146.6</v>
@@ -20666,7 +21264,9 @@
       <c r="T275" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U275" s="2" t="inlineStr"/>
+      <c r="U275" s="2" t="n">
+        <v>19</v>
+      </c>
       <c r="V275" t="inlineStr"/>
       <c r="W275" s="2" t="n">
         <v>146.7</v>
@@ -20739,7 +21339,9 @@
       <c r="T276" s="2" t="n">
         <v>21.4</v>
       </c>
-      <c r="U276" s="2" t="inlineStr"/>
+      <c r="U276" s="2" t="n">
+        <v>16.3</v>
+      </c>
       <c r="V276" t="inlineStr"/>
       <c r="W276" s="2" t="n">
         <v>151.8</v>
@@ -20812,7 +21414,9 @@
       <c r="T277" s="6" t="n">
         <v>23.6</v>
       </c>
-      <c r="U277" s="6" t="inlineStr"/>
+      <c r="U277" s="6" t="n">
+        <v>20.3</v>
+      </c>
       <c r="V277" s="4" t="inlineStr"/>
       <c r="W277" s="6" t="n">
         <v>152.8</v>
@@ -20885,7 +21489,9 @@
       <c r="T278" s="2" t="n">
         <v>21.1</v>
       </c>
-      <c r="U278" s="2" t="inlineStr"/>
+      <c r="U278" s="2" t="n">
+        <v>17.8</v>
+      </c>
       <c r="V278" t="inlineStr"/>
       <c r="W278" s="2" t="n">
         <v>152.9</v>
@@ -20962,7 +21568,9 @@
       <c r="T279" s="2" t="n">
         <v>23.8</v>
       </c>
-      <c r="U279" s="2" t="inlineStr"/>
+      <c r="U279" s="2" t="n">
+        <v>21.9</v>
+      </c>
       <c r="V279" t="inlineStr"/>
       <c r="W279" s="2" t="n">
         <v>153.9</v>
@@ -21035,8 +21643,14 @@
       <c r="T280" s="3" t="n">
         <v>29.5</v>
       </c>
-      <c r="U280" s="2" t="inlineStr"/>
-      <c r="V280" t="inlineStr"/>
+      <c r="U280" s="3" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="V280" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W280" s="2" t="n">
         <v>151.8</v>
       </c>
@@ -21108,7 +21722,9 @@
       <c r="T281" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="U281" s="2" t="inlineStr"/>
+      <c r="U281" s="2" t="n">
+        <v>22.7</v>
+      </c>
       <c r="V281" t="inlineStr"/>
       <c r="W281" s="1" t="n">
         <v>158</v>
@@ -21181,7 +21797,9 @@
       <c r="T282" s="2" t="n">
         <v>24.9</v>
       </c>
-      <c r="U282" s="2" t="inlineStr"/>
+      <c r="U282" s="2" t="n">
+        <v>21.3</v>
+      </c>
       <c r="V282" t="inlineStr"/>
       <c r="W282" s="2" t="n">
         <v>154.5</v>
@@ -21254,7 +21872,9 @@
       <c r="T283" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U283" s="2" t="inlineStr"/>
+      <c r="U283" s="2" t="n">
+        <v>19</v>
+      </c>
       <c r="V283" t="inlineStr"/>
       <c r="W283" s="2" t="n">
         <v>152.4</v>
@@ -21325,7 +21945,9 @@
       <c r="T284" s="3" t="n">
         <v>27.3</v>
       </c>
-      <c r="U284" s="2" t="inlineStr"/>
+      <c r="U284" s="2" t="n">
+        <v>24.2</v>
+      </c>
       <c r="V284" t="inlineStr"/>
       <c r="W284" s="2" t="n">
         <v>139.9</v>
@@ -21398,8 +22020,14 @@
       <c r="T285" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="U285" s="2" t="inlineStr"/>
-      <c r="V285" t="inlineStr"/>
+      <c r="U285" s="3" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="V285" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W285" s="2" t="n">
         <v>137.8</v>
       </c>
@@ -21471,7 +22099,9 @@
       <c r="T286" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U286" s="2" t="inlineStr"/>
+      <c r="U286" s="2" t="n">
+        <v>17.4</v>
+      </c>
       <c r="V286" t="inlineStr"/>
       <c r="W286" s="2" t="n">
         <v>141.5</v>
@@ -21544,7 +22174,9 @@
       <c r="T287" s="2" t="n">
         <v>22.4</v>
       </c>
-      <c r="U287" s="2" t="inlineStr"/>
+      <c r="U287" s="2" t="n">
+        <v>17.5</v>
+      </c>
       <c r="V287" t="inlineStr"/>
       <c r="W287" s="2" t="n">
         <v>145</v>
@@ -21621,7 +22253,9 @@
       <c r="T288" s="7" t="n">
         <v>25.1</v>
       </c>
-      <c r="U288" s="6" t="inlineStr"/>
+      <c r="U288" s="6" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V288" s="4" t="inlineStr"/>
       <c r="W288" s="6" t="n">
         <v>136.5</v>
@@ -21694,7 +22328,9 @@
       <c r="T289" s="6" t="n">
         <v>24.1</v>
       </c>
-      <c r="U289" s="6" t="inlineStr"/>
+      <c r="U289" s="6" t="n">
+        <v>20.7</v>
+      </c>
       <c r="V289" s="4" t="inlineStr"/>
       <c r="W289" s="6" t="n">
         <v>138.3</v>
@@ -21767,8 +22403,14 @@
       <c r="T290" s="7" t="n">
         <v>26.8</v>
       </c>
-      <c r="U290" s="6" t="inlineStr"/>
-      <c r="V290" s="4" t="inlineStr"/>
+      <c r="U290" s="7" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="V290" s="7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W290" s="6" t="n">
         <v>139.1</v>
       </c>
@@ -21844,7 +22486,9 @@
       <c r="T291" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="U291" s="2" t="inlineStr"/>
+      <c r="U291" s="2" t="n">
+        <v>23.2</v>
+      </c>
       <c r="V291" t="inlineStr"/>
       <c r="W291" s="2" t="n">
         <v>142</v>
@@ -21917,7 +22561,9 @@
       <c r="T292" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="U292" s="2" t="inlineStr"/>
+      <c r="U292" s="2" t="n">
+        <v>20.7</v>
+      </c>
       <c r="V292" t="inlineStr"/>
       <c r="W292" s="2" t="n">
         <v>142.6</v>
@@ -21990,7 +22636,9 @@
       <c r="T293" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="U293" s="2" t="inlineStr"/>
+      <c r="U293" s="2" t="n">
+        <v>19.1</v>
+      </c>
       <c r="V293" t="inlineStr"/>
       <c r="W293" s="2" t="n">
         <v>140.9</v>
@@ -22067,7 +22715,9 @@
       <c r="T294" s="7" t="n">
         <v>27.4</v>
       </c>
-      <c r="U294" s="6" t="inlineStr"/>
+      <c r="U294" s="6" t="n">
+        <v>23.9</v>
+      </c>
       <c r="V294" s="4" t="inlineStr"/>
       <c r="W294" s="6" t="n">
         <v>144</v>
@@ -22140,8 +22790,14 @@
       <c r="T295" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="U295" s="2" t="inlineStr"/>
-      <c r="V295" t="inlineStr"/>
+      <c r="U295" s="3" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="V295" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W295" s="2" t="n">
         <v>139</v>
       </c>
@@ -22213,7 +22869,9 @@
       <c r="T296" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="U296" s="2" t="inlineStr"/>
+      <c r="U296" s="2" t="n">
+        <v>23</v>
+      </c>
       <c r="V296" t="inlineStr"/>
       <c r="W296" s="2" t="n">
         <v>142.2</v>
@@ -22286,7 +22944,9 @@
       <c r="T297" s="3" t="n">
         <v>25.2</v>
       </c>
-      <c r="U297" s="2" t="inlineStr"/>
+      <c r="U297" s="2" t="n">
+        <v>19</v>
+      </c>
       <c r="V297" t="inlineStr"/>
       <c r="W297" s="2" t="n">
         <v>145.4</v>
@@ -22359,7 +23019,9 @@
       <c r="T298" s="2" t="n">
         <v>24.5</v>
       </c>
-      <c r="U298" s="2" t="inlineStr"/>
+      <c r="U298" s="2" t="n">
+        <v>23</v>
+      </c>
       <c r="V298" t="inlineStr"/>
       <c r="W298" s="2" t="n">
         <v>143.8</v>
@@ -22432,7 +23094,9 @@
       <c r="T299" s="2" t="n">
         <v>23.9</v>
       </c>
-      <c r="U299" s="2" t="inlineStr"/>
+      <c r="U299" s="3" t="n">
+        <v>27.6</v>
+      </c>
       <c r="V299" t="inlineStr"/>
       <c r="W299" s="2" t="n">
         <v>146.9</v>
@@ -22505,7 +23169,9 @@
       <c r="T300" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U300" s="2" t="inlineStr"/>
+      <c r="U300" s="2" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V300" t="inlineStr"/>
       <c r="W300" s="2" t="n">
         <v>147.6</v>
@@ -22578,8 +23244,14 @@
       <c r="T301" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="U301" s="2" t="inlineStr"/>
-      <c r="V301" t="inlineStr"/>
+      <c r="U301" s="3" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="V301" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W301" s="2" t="n">
         <v>148.4</v>
       </c>
@@ -22651,7 +23323,9 @@
       <c r="T302" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="U302" s="2" t="inlineStr"/>
+      <c r="U302" s="2" t="n">
+        <v>16.5</v>
+      </c>
       <c r="V302" t="inlineStr"/>
       <c r="W302" s="2" t="n">
         <v>150.4</v>
@@ -22724,7 +23398,9 @@
       <c r="T303" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U303" s="2" t="inlineStr"/>
+      <c r="U303" s="2" t="n">
+        <v>14.1</v>
+      </c>
       <c r="V303" t="inlineStr"/>
       <c r="W303" s="2" t="n">
         <v>143.3</v>
@@ -22797,7 +23473,9 @@
       <c r="T304" s="2" t="n">
         <v>19.2</v>
       </c>
-      <c r="U304" s="2" t="inlineStr"/>
+      <c r="U304" s="2" t="n">
+        <v>19.1</v>
+      </c>
       <c r="V304" t="inlineStr"/>
       <c r="W304" s="2" t="n">
         <v>144.2</v>
@@ -22870,7 +23548,9 @@
       <c r="T305" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U305" s="2" t="inlineStr"/>
+      <c r="U305" s="2" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V305" t="inlineStr"/>
       <c r="W305" s="1" t="n">
         <v>156.9</v>
@@ -22943,7 +23623,9 @@
       <c r="T306" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U306" s="2" t="inlineStr"/>
+      <c r="U306" s="2" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V306" t="inlineStr"/>
       <c r="W306" s="2" t="n">
         <v>149.9</v>
@@ -23016,7 +23698,9 @@
       <c r="T307" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U307" s="2" t="inlineStr"/>
+      <c r="U307" s="2" t="n">
+        <v>12.6</v>
+      </c>
       <c r="V307" t="inlineStr"/>
       <c r="W307" s="2" t="n">
         <v>139.2</v>
@@ -23089,7 +23773,9 @@
       <c r="T308" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U308" s="2" t="inlineStr"/>
+      <c r="U308" s="2" t="n">
+        <v>12</v>
+      </c>
       <c r="V308" t="inlineStr"/>
       <c r="W308" s="2" t="n">
         <v>140.7</v>
@@ -23162,7 +23848,9 @@
       <c r="T309" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U309" s="2" t="inlineStr"/>
+      <c r="U309" s="2" t="n">
+        <v>14.2</v>
+      </c>
       <c r="V309" t="inlineStr"/>
       <c r="W309" s="2" t="n">
         <v>141.8</v>
@@ -23235,7 +23923,9 @@
       <c r="T310" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U310" s="2" t="inlineStr"/>
+      <c r="U310" s="2" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V310" t="inlineStr"/>
       <c r="W310" s="2" t="n">
         <v>141.9</v>
@@ -23312,7 +24002,9 @@
       <c r="T311" s="6" t="n">
         <v>19.5</v>
       </c>
-      <c r="U311" s="6" t="inlineStr"/>
+      <c r="U311" s="6" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V311" s="4" t="inlineStr"/>
       <c r="W311" s="6" t="n">
         <v>140.9</v>
@@ -23385,7 +24077,9 @@
       <c r="T312" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U312" s="2" t="inlineStr"/>
+      <c r="U312" s="2" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V312" t="inlineStr"/>
       <c r="W312" s="2" t="n">
         <v>140.8</v>
@@ -23462,7 +24156,9 @@
       <c r="T313" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U313" s="2" t="inlineStr"/>
+      <c r="U313" s="2" t="n">
+        <v>14.8</v>
+      </c>
       <c r="V313" t="inlineStr"/>
       <c r="W313" s="2" t="n">
         <v>139.6</v>
@@ -23535,7 +24231,9 @@
       <c r="T314" s="2" t="n">
         <v>18.7</v>
       </c>
-      <c r="U314" s="2" t="inlineStr"/>
+      <c r="U314" s="2" t="n">
+        <v>16.6</v>
+      </c>
       <c r="V314" t="inlineStr"/>
       <c r="W314" s="2" t="n">
         <v>139.1</v>
@@ -23608,7 +24306,9 @@
       <c r="T315" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U315" s="2" t="inlineStr"/>
+      <c r="U315" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V315" t="inlineStr"/>
       <c r="W315" s="2" t="n">
         <v>139.6</v>
@@ -23685,7 +24385,9 @@
       <c r="T316" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U316" s="2" t="inlineStr"/>
+      <c r="U316" s="2" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V316" t="inlineStr"/>
       <c r="W316" s="2" t="n">
         <v>138.2</v>
@@ -23758,7 +24460,9 @@
       <c r="T317" s="2" t="n">
         <v>18.8</v>
       </c>
-      <c r="U317" s="2" t="inlineStr"/>
+      <c r="U317" s="2" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V317" t="inlineStr"/>
       <c r="W317" s="2" t="n">
         <v>141.9</v>
@@ -23831,7 +24535,9 @@
       <c r="T318" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U318" s="2" t="inlineStr"/>
+      <c r="U318" s="2" t="n">
+        <v>11.6</v>
+      </c>
       <c r="V318" t="inlineStr"/>
       <c r="W318" s="2" t="n">
         <v>143.3</v>
@@ -23904,7 +24610,9 @@
       <c r="T319" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U319" s="2" t="inlineStr"/>
+      <c r="U319" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V319" t="inlineStr"/>
       <c r="W319" s="2" t="n">
         <v>141.4</v>
@@ -23977,7 +24685,9 @@
       <c r="T320" s="2" t="n">
         <v>18.3</v>
       </c>
-      <c r="U320" s="2" t="inlineStr"/>
+      <c r="U320" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V320" t="inlineStr"/>
       <c r="W320" s="2" t="n">
         <v>141.7</v>
@@ -24050,7 +24760,9 @@
       <c r="T321" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U321" s="2" t="inlineStr"/>
+      <c r="U321" s="2" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V321" t="inlineStr"/>
       <c r="W321" s="2" t="n">
         <v>138.7</v>
@@ -24123,7 +24835,9 @@
       <c r="T322" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U322" s="2" t="inlineStr"/>
+      <c r="U322" s="2" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V322" t="inlineStr"/>
       <c r="W322" s="2" t="n">
         <v>135.4</v>
@@ -24196,7 +24910,9 @@
       <c r="T323" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U323" s="2" t="inlineStr"/>
+      <c r="U323" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V323" t="inlineStr"/>
       <c r="W323" s="2" t="n">
         <v>136.1</v>
@@ -24269,7 +24985,9 @@
       <c r="T324" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U324" s="2" t="inlineStr"/>
+      <c r="U324" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V324" t="inlineStr"/>
       <c r="W324" s="2" t="n">
         <v>138.2</v>
@@ -24342,7 +25060,9 @@
       <c r="T325" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U325" s="2" t="inlineStr"/>
+      <c r="U325" s="2" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V325" t="inlineStr"/>
       <c r="W325" s="2" t="n">
         <v>140.2</v>
@@ -24415,7 +25135,9 @@
       <c r="T326" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U326" s="2" t="inlineStr"/>
+      <c r="U326" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V326" t="inlineStr"/>
       <c r="W326" s="2" t="n">
         <v>139.4</v>
@@ -24488,7 +25210,9 @@
       <c r="T327" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U327" s="2" t="inlineStr"/>
+      <c r="U327" s="2" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V327" t="inlineStr"/>
       <c r="W327" s="2" t="n">
         <v>141.5</v>
@@ -24565,7 +25289,9 @@
       <c r="T328" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U328" s="2" t="inlineStr"/>
+      <c r="U328" s="2" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V328" t="inlineStr"/>
       <c r="W328" s="2" t="n">
         <v>139.3</v>
@@ -24638,7 +25364,9 @@
       <c r="T329" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U329" s="2" t="inlineStr"/>
+      <c r="U329" s="2" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V329" t="inlineStr"/>
       <c r="W329" s="2" t="n">
         <v>145.8</v>
@@ -24711,7 +25439,9 @@
       <c r="T330" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U330" s="2" t="inlineStr"/>
+      <c r="U330" s="2" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V330" t="inlineStr"/>
       <c r="W330" s="2" t="n">
         <v>138.4</v>
@@ -24784,7 +25514,9 @@
       <c r="T331" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U331" s="2" t="inlineStr"/>
+      <c r="U331" s="2" t="n">
+        <v>13.3</v>
+      </c>
       <c r="V331" t="inlineStr"/>
       <c r="W331" s="2" t="n">
         <v>135.5</v>
@@ -24857,7 +25589,9 @@
       <c r="T332" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U332" s="2" t="inlineStr"/>
+      <c r="U332" s="2" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V332" t="inlineStr"/>
       <c r="W332" s="2" t="n">
         <v>132.3</v>
@@ -24930,7 +25664,9 @@
       <c r="T333" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U333" s="2" t="inlineStr"/>
+      <c r="U333" s="2" t="n">
+        <v>14</v>
+      </c>
       <c r="V333" t="inlineStr"/>
       <c r="W333" s="2" t="n">
         <v>137</v>
@@ -25003,7 +25739,9 @@
       <c r="T334" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U334" s="2" t="inlineStr"/>
+      <c r="U334" s="2" t="n">
+        <v>17.4</v>
+      </c>
       <c r="V334" t="inlineStr"/>
       <c r="W334" s="2" t="n">
         <v>137.4</v>
@@ -25076,7 +25814,9 @@
       <c r="T335" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U335" s="2" t="inlineStr"/>
+      <c r="U335" s="2" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V335" t="inlineStr"/>
       <c r="W335" s="2" t="n">
         <v>139</v>
@@ -25149,7 +25889,9 @@
       <c r="T336" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U336" s="2" t="inlineStr"/>
+      <c r="U336" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V336" t="inlineStr"/>
       <c r="W336" s="2" t="n">
         <v>138.6</v>
@@ -25222,7 +25964,9 @@
       <c r="T337" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U337" s="2" t="inlineStr"/>
+      <c r="U337" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V337" t="inlineStr"/>
       <c r="W337" s="2" t="n">
         <v>139.5</v>
@@ -25295,7 +26039,9 @@
       <c r="T338" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U338" s="2" t="inlineStr"/>
+      <c r="U338" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V338" t="inlineStr"/>
       <c r="W338" s="2" t="n">
         <v>144.2</v>
@@ -25368,7 +26114,9 @@
       <c r="T339" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U339" s="2" t="inlineStr"/>
+      <c r="U339" s="2" t="n">
+        <v>9.6</v>
+      </c>
       <c r="V339" t="inlineStr"/>
       <c r="W339" s="2" t="n">
         <v>142.5</v>
@@ -25441,7 +26189,9 @@
       <c r="T340" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U340" s="2" t="inlineStr"/>
+      <c r="U340" s="2" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V340" t="inlineStr"/>
       <c r="W340" s="2" t="n">
         <v>143.2</v>
@@ -25514,7 +26264,9 @@
       <c r="T341" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U341" s="2" t="inlineStr"/>
+      <c r="U341" s="2" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V341" t="inlineStr"/>
       <c r="W341" s="2" t="n">
         <v>136.9</v>
@@ -25587,7 +26339,9 @@
       <c r="T342" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U342" s="2" t="inlineStr"/>
+      <c r="U342" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V342" t="inlineStr"/>
       <c r="W342" s="2" t="n">
         <v>142.1</v>
@@ -25660,7 +26414,9 @@
       <c r="T343" s="6" t="n">
         <v>21.5</v>
       </c>
-      <c r="U343" s="6" t="inlineStr"/>
+      <c r="U343" s="7" t="n">
+        <v>28.7</v>
+      </c>
       <c r="V343" s="4" t="inlineStr"/>
       <c r="W343" s="6" t="n">
         <v>152.2</v>
@@ -25733,7 +26489,9 @@
       <c r="T344" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U344" s="2" t="inlineStr"/>
+      <c r="U344" s="2" t="n">
+        <v>16</v>
+      </c>
       <c r="V344" t="inlineStr"/>
       <c r="W344" s="2" t="n">
         <v>145</v>
@@ -25806,7 +26564,9 @@
       <c r="T345" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U345" s="2" t="inlineStr"/>
+      <c r="U345" s="2" t="n">
+        <v>20.6</v>
+      </c>
       <c r="V345" t="inlineStr"/>
       <c r="W345" s="2" t="n">
         <v>142</v>
@@ -25883,7 +26643,9 @@
       <c r="T346" s="6" t="n">
         <v>22.2</v>
       </c>
-      <c r="U346" s="6" t="inlineStr"/>
+      <c r="U346" s="6" t="n">
+        <v>23.9</v>
+      </c>
       <c r="V346" s="4" t="inlineStr"/>
       <c r="W346" s="6" t="n">
         <v>143.1</v>
@@ -25956,7 +26718,9 @@
       <c r="T347" s="2" t="n">
         <v>19.4</v>
       </c>
-      <c r="U347" s="2" t="inlineStr"/>
+      <c r="U347" s="2" t="n">
+        <v>21.1</v>
+      </c>
       <c r="V347" t="inlineStr"/>
       <c r="W347" s="2" t="n">
         <v>143</v>
@@ -26029,7 +26793,9 @@
       <c r="T348" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="U348" s="2" t="inlineStr"/>
+      <c r="U348" s="2" t="n">
+        <v>19.1</v>
+      </c>
       <c r="V348" t="inlineStr"/>
       <c r="W348" s="2" t="n">
         <v>142.6</v>
@@ -26102,7 +26868,9 @@
       <c r="T349" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U349" s="2" t="inlineStr"/>
+      <c r="U349" s="2" t="n">
+        <v>12.9</v>
+      </c>
       <c r="V349" t="inlineStr"/>
       <c r="W349" s="2" t="n">
         <v>144.3</v>
@@ -26175,7 +26943,9 @@
       <c r="T350" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U350" s="2" t="inlineStr"/>
+      <c r="U350" s="2" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V350" t="inlineStr"/>
       <c r="W350" s="2" t="n">
         <v>142.7</v>
@@ -26248,7 +27018,9 @@
       <c r="T351" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U351" s="2" t="inlineStr"/>
+      <c r="U351" s="2" t="n">
+        <v>20.7</v>
+      </c>
       <c r="V351" t="inlineStr"/>
       <c r="W351" s="2" t="n">
         <v>142.6</v>
@@ -26321,7 +27093,9 @@
       <c r="T352" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U352" s="2" t="inlineStr"/>
+      <c r="U352" s="2" t="n">
+        <v>15.7</v>
+      </c>
       <c r="V352" t="inlineStr"/>
       <c r="W352" s="2" t="n">
         <v>146.7</v>
@@ -26394,7 +27168,9 @@
       <c r="T353" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U353" s="2" t="inlineStr"/>
+      <c r="U353" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V353" t="inlineStr"/>
       <c r="W353" s="2" t="n">
         <v>141.9</v>
@@ -26467,7 +27243,9 @@
       <c r="T354" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U354" s="2" t="inlineStr"/>
+      <c r="U354" s="2" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V354" t="inlineStr"/>
       <c r="W354" s="2" t="n">
         <v>143.1</v>
@@ -26544,7 +27322,9 @@
       <c r="T355" s="6" t="n">
         <v>18.6</v>
       </c>
-      <c r="U355" s="6" t="inlineStr"/>
+      <c r="U355" s="6" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V355" s="4" t="inlineStr"/>
       <c r="W355" s="6" t="n">
         <v>145.3</v>
@@ -26621,7 +27401,9 @@
       <c r="T356" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U356" s="2" t="inlineStr"/>
+      <c r="U356" s="2" t="n">
+        <v>16</v>
+      </c>
       <c r="V356" t="inlineStr"/>
       <c r="W356" s="2" t="n">
         <v>139.9</v>
@@ -26694,7 +27476,9 @@
       <c r="T357" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U357" s="2" t="inlineStr"/>
+      <c r="U357" s="2" t="n">
+        <v>17.6</v>
+      </c>
       <c r="V357" t="inlineStr"/>
       <c r="W357" s="2" t="n">
         <v>139.4</v>
@@ -26767,7 +27551,9 @@
       <c r="T358" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U358" s="2" t="inlineStr"/>
+      <c r="U358" s="2" t="n">
+        <v>13.6</v>
+      </c>
       <c r="V358" t="inlineStr"/>
       <c r="W358" s="2" t="n">
         <v>144.5</v>
@@ -26840,7 +27626,9 @@
       <c r="T359" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U359" s="2" t="inlineStr"/>
+      <c r="U359" s="2" t="n">
+        <v>11.6</v>
+      </c>
       <c r="V359" t="inlineStr"/>
       <c r="W359" s="2" t="n">
         <v>149.6</v>
@@ -26913,7 +27701,9 @@
       <c r="T360" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U360" s="2" t="inlineStr"/>
+      <c r="U360" s="2" t="n">
+        <v>13</v>
+      </c>
       <c r="V360" t="inlineStr"/>
       <c r="W360" s="2" t="n">
         <v>154.8</v>
@@ -26986,7 +27776,9 @@
       <c r="T361" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U361" s="2" t="inlineStr"/>
+      <c r="U361" s="2" t="n">
+        <v>13.2</v>
+      </c>
       <c r="V361" t="inlineStr"/>
       <c r="W361" s="2" t="n">
         <v>150</v>
@@ -27059,7 +27851,9 @@
       <c r="T362" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U362" s="2" t="inlineStr"/>
+      <c r="U362" s="2" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="V362" t="inlineStr"/>
       <c r="W362" s="2" t="n">
         <v>145.4</v>
@@ -27136,7 +27930,9 @@
       <c r="T363" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U363" s="2" t="inlineStr"/>
+      <c r="U363" s="2" t="n">
+        <v>10.7</v>
+      </c>
       <c r="V363" t="inlineStr"/>
       <c r="W363" s="2" t="n">
         <v>145.7</v>
@@ -27209,7 +28005,9 @@
       <c r="T364" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U364" s="2" t="inlineStr"/>
+      <c r="U364" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V364" t="inlineStr"/>
       <c r="W364" s="2" t="n">
         <v>149.8</v>
@@ -27282,7 +28080,9 @@
       <c r="T365" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U365" s="2" t="inlineStr"/>
+      <c r="U365" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V365" t="inlineStr"/>
       <c r="W365" s="2" t="n">
         <v>144.7</v>
@@ -27355,7 +28155,9 @@
       <c r="T366" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U366" s="2" t="inlineStr"/>
+      <c r="U366" s="2" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V366" t="inlineStr"/>
       <c r="W366" s="2" t="n">
         <v>144.3</v>
@@ -27428,7 +28230,9 @@
       <c r="T367" s="6" t="n">
         <v>17.2</v>
       </c>
-      <c r="U367" s="6" t="inlineStr"/>
+      <c r="U367" s="6" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V367" s="4" t="inlineStr"/>
       <c r="W367" s="6" t="n">
         <v>145.7</v>
@@ -27501,7 +28305,9 @@
       <c r="T368" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U368" s="2" t="inlineStr"/>
+      <c r="U368" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V368" t="inlineStr"/>
       <c r="W368" s="2" t="n">
         <v>145.1</v>
@@ -27574,7 +28380,9 @@
       <c r="T369" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U369" s="2" t="inlineStr"/>
+      <c r="U369" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V369" t="inlineStr"/>
       <c r="W369" s="2" t="n">
         <v>148.5</v>
@@ -27647,7 +28455,9 @@
       <c r="T370" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U370" s="2" t="inlineStr"/>
+      <c r="U370" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V370" t="inlineStr"/>
       <c r="W370" s="2" t="n">
         <v>145.7</v>
@@ -27720,7 +28530,9 @@
       <c r="T371" s="2" t="n">
         <v>18.8</v>
       </c>
-      <c r="U371" s="2" t="inlineStr"/>
+      <c r="U371" s="2" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V371" t="inlineStr"/>
       <c r="W371" s="2" t="n">
         <v>147.3</v>
@@ -27793,7 +28605,9 @@
       <c r="T372" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U372" s="2" t="inlineStr"/>
+      <c r="U372" s="2" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V372" t="inlineStr"/>
       <c r="W372" s="2" t="n">
         <v>146.1</v>
@@ -27866,7 +28680,9 @@
       <c r="T373" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U373" s="2" t="inlineStr"/>
+      <c r="U373" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V373" t="inlineStr"/>
       <c r="W373" s="2" t="n">
         <v>151.7</v>
@@ -27939,7 +28755,9 @@
       <c r="T374" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U374" s="2" t="inlineStr"/>
+      <c r="U374" s="2" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V374" t="inlineStr"/>
       <c r="W374" s="2" t="n">
         <v>150.2</v>
@@ -28016,7 +28834,9 @@
       <c r="T375" s="2" t="n">
         <v>18.7</v>
       </c>
-      <c r="U375" s="2" t="inlineStr"/>
+      <c r="U375" s="2" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V375" t="inlineStr"/>
       <c r="W375" s="2" t="n">
         <v>145.9</v>
@@ -28089,7 +28909,9 @@
       <c r="T376" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U376" s="2" t="inlineStr"/>
+      <c r="U376" s="2" t="n">
+        <v>15.4</v>
+      </c>
       <c r="V376" t="inlineStr"/>
       <c r="W376" s="2" t="n">
         <v>147.3</v>
@@ -28162,7 +28984,9 @@
       <c r="T377" s="2" t="n">
         <v>18.7</v>
       </c>
-      <c r="U377" s="2" t="inlineStr"/>
+      <c r="U377" s="2" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V377" t="inlineStr"/>
       <c r="W377" s="2" t="n">
         <v>146.6</v>
@@ -28239,7 +29063,9 @@
       <c r="T378" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U378" s="2" t="inlineStr"/>
+      <c r="U378" s="2" t="n">
+        <v>15.8</v>
+      </c>
       <c r="V378" t="inlineStr"/>
       <c r="W378" s="2" t="n">
         <v>143</v>
@@ -28312,7 +29138,9 @@
       <c r="T379" s="2" t="n">
         <v>20.7</v>
       </c>
-      <c r="U379" s="2" t="inlineStr"/>
+      <c r="U379" s="2" t="n">
+        <v>19.5</v>
+      </c>
       <c r="V379" t="inlineStr"/>
       <c r="W379" s="2" t="n">
         <v>139.6</v>
@@ -28385,7 +29213,9 @@
       <c r="T380" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U380" s="2" t="inlineStr"/>
+      <c r="U380" s="2" t="n">
+        <v>14.1</v>
+      </c>
       <c r="V380" t="inlineStr"/>
       <c r="W380" s="2" t="n">
         <v>139.9</v>
@@ -28462,7 +29292,9 @@
       <c r="T381" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U381" s="2" t="inlineStr"/>
+      <c r="U381" s="2" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V381" t="inlineStr"/>
       <c r="W381" s="2" t="n">
         <v>141.2</v>
@@ -28535,7 +29367,9 @@
       <c r="T382" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U382" s="2" t="inlineStr"/>
+      <c r="U382" s="2" t="n">
+        <v>9.4</v>
+      </c>
       <c r="V382" t="inlineStr"/>
       <c r="W382" s="2" t="n">
         <v>140</v>
@@ -28608,7 +29442,9 @@
       <c r="T383" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U383" s="2" t="inlineStr"/>
+      <c r="U383" s="2" t="n">
+        <v>13.9</v>
+      </c>
       <c r="V383" t="inlineStr"/>
       <c r="W383" s="3" t="n">
         <v>126.4</v>
@@ -28681,7 +29517,9 @@
       <c r="T384" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U384" s="2" t="inlineStr"/>
+      <c r="U384" s="2" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V384" t="inlineStr"/>
       <c r="W384" s="2" t="n">
         <v>133.3</v>
@@ -28754,7 +29592,9 @@
       <c r="T385" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U385" s="2" t="inlineStr"/>
+      <c r="U385" s="2" t="n">
+        <v>12.6</v>
+      </c>
       <c r="V385" t="inlineStr"/>
       <c r="W385" s="2" t="n">
         <v>134.7</v>
@@ -28827,7 +29667,9 @@
       <c r="T386" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U386" s="2" t="inlineStr"/>
+      <c r="U386" s="2" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V386" t="inlineStr"/>
       <c r="W386" s="2" t="n">
         <v>132.6</v>
@@ -28900,7 +29742,9 @@
       <c r="T387" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="U387" s="2" t="inlineStr"/>
+      <c r="U387" s="2" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="V387" t="inlineStr"/>
       <c r="W387" s="2" t="n">
         <v>137.1</v>
@@ -28973,7 +29817,9 @@
       <c r="T388" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U388" s="2" t="inlineStr"/>
+      <c r="U388" s="2" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V388" t="inlineStr"/>
       <c r="W388" s="2" t="n">
         <v>135.6</v>
@@ -29046,7 +29892,9 @@
       <c r="T389" s="2" t="n">
         <v>14.6</v>
       </c>
-      <c r="U389" s="2" t="inlineStr"/>
+      <c r="U389" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V389" t="inlineStr"/>
       <c r="W389" s="2" t="n">
         <v>136.5</v>
@@ -29119,7 +29967,9 @@
       <c r="T390" s="2" t="n">
         <v>14.6</v>
       </c>
-      <c r="U390" s="2" t="inlineStr"/>
+      <c r="U390" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V390" t="inlineStr"/>
       <c r="W390" s="2" t="n">
         <v>134.4</v>
@@ -29192,7 +30042,9 @@
       <c r="T391" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="U391" s="2" t="inlineStr"/>
+      <c r="U391" s="2" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="V391" t="inlineStr"/>
       <c r="W391" s="2" t="n">
         <v>138.4</v>
@@ -29265,7 +30117,9 @@
       <c r="T392" s="2" t="n">
         <v>15.2</v>
       </c>
-      <c r="U392" s="2" t="inlineStr"/>
+      <c r="U392" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="V392" t="inlineStr"/>
       <c r="W392" s="2" t="n">
         <v>142.9</v>
@@ -29338,7 +30192,9 @@
       <c r="T393" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U393" s="2" t="inlineStr"/>
+      <c r="U393" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V393" t="inlineStr"/>
       <c r="W393" s="2" t="n">
         <v>143.6</v>
@@ -29411,7 +30267,9 @@
       <c r="T394" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U394" s="2" t="inlineStr"/>
+      <c r="U394" s="2" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="V394" t="inlineStr"/>
       <c r="W394" s="2" t="n">
         <v>142.9</v>
@@ -29484,7 +30342,9 @@
       <c r="T395" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U395" s="2" t="inlineStr"/>
+      <c r="U395" s="2" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V395" t="inlineStr"/>
       <c r="W395" s="2" t="n">
         <v>143.2</v>
@@ -29557,7 +30417,9 @@
       <c r="T396" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U396" s="2" t="inlineStr"/>
+      <c r="U396" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V396" t="inlineStr"/>
       <c r="W396" s="2" t="n">
         <v>143.9</v>
@@ -29630,7 +30492,9 @@
       <c r="T397" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U397" s="2" t="inlineStr"/>
+      <c r="U397" s="2" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="V397" t="inlineStr"/>
       <c r="W397" s="2" t="n">
         <v>145.6</v>
@@ -29703,7 +30567,9 @@
       <c r="T398" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U398" s="2" t="inlineStr"/>
+      <c r="U398" s="2" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V398" t="inlineStr"/>
       <c r="W398" s="2" t="n">
         <v>143.3</v>
@@ -29776,7 +30642,9 @@
       <c r="T399" s="2" t="n">
         <v>15.2</v>
       </c>
-      <c r="U399" s="2" t="inlineStr"/>
+      <c r="U399" s="2" t="n">
+        <v>12.9</v>
+      </c>
       <c r="V399" t="inlineStr"/>
       <c r="W399" s="2" t="n">
         <v>143</v>
@@ -29849,7 +30717,9 @@
       <c r="T400" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U400" s="2" t="inlineStr"/>
+      <c r="U400" s="2" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V400" t="inlineStr"/>
       <c r="W400" s="2" t="n">
         <v>144.1</v>
@@ -29922,7 +30792,9 @@
       <c r="T401" s="6" t="n">
         <v>14.4</v>
       </c>
-      <c r="U401" s="6" t="inlineStr"/>
+      <c r="U401" s="6" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V401" s="4" t="inlineStr"/>
       <c r="W401" s="6" t="n">
         <v>149.8</v>
@@ -29995,7 +30867,9 @@
       <c r="T402" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U402" s="2" t="inlineStr"/>
+      <c r="U402" s="2" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V402" t="inlineStr"/>
       <c r="W402" s="2" t="n">
         <v>148.5</v>
@@ -30072,7 +30946,9 @@
       <c r="T403" s="6" t="n">
         <v>16.3</v>
       </c>
-      <c r="U403" s="6" t="inlineStr"/>
+      <c r="U403" s="6" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V403" s="4" t="inlineStr"/>
       <c r="W403" s="6" t="n">
         <v>149.2</v>
@@ -30145,7 +31021,9 @@
       <c r="T404" s="2" t="n">
         <v>15.2</v>
       </c>
-      <c r="U404" s="2" t="inlineStr"/>
+      <c r="U404" s="2" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V404" t="inlineStr"/>
       <c r="W404" s="2" t="n">
         <v>144.1</v>
@@ -30218,7 +31096,9 @@
       <c r="T405" s="2" t="n">
         <v>14.3</v>
       </c>
-      <c r="U405" s="2" t="inlineStr"/>
+      <c r="U405" s="2" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V405" t="inlineStr"/>
       <c r="W405" s="2" t="n">
         <v>150.6</v>
@@ -30295,7 +31175,9 @@
       <c r="T406" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U406" s="2" t="inlineStr"/>
+      <c r="U406" s="2" t="n">
+        <v>12</v>
+      </c>
       <c r="V406" t="inlineStr"/>
       <c r="W406" s="2" t="n">
         <v>151.6</v>
@@ -30372,7 +31254,9 @@
       <c r="T407" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U407" s="2" t="inlineStr"/>
+      <c r="U407" s="2" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V407" t="inlineStr"/>
       <c r="W407" s="2" t="n">
         <v>148.9</v>
@@ -30445,7 +31329,9 @@
       <c r="T408" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U408" s="2" t="inlineStr"/>
+      <c r="U408" s="2" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V408" t="inlineStr"/>
       <c r="W408" s="2" t="n">
         <v>149.2</v>
@@ -30518,7 +31404,9 @@
       <c r="T409" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U409" s="2" t="inlineStr"/>
+      <c r="U409" s="2" t="n">
+        <v>17.5</v>
+      </c>
       <c r="V409" t="inlineStr"/>
       <c r="W409" s="2" t="n">
         <v>147</v>
@@ -30591,7 +31479,9 @@
       <c r="T410" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U410" s="2" t="inlineStr"/>
+      <c r="U410" s="2" t="n">
+        <v>13</v>
+      </c>
       <c r="V410" t="inlineStr"/>
       <c r="W410" s="2" t="n">
         <v>154.5</v>
@@ -30668,7 +31558,9 @@
       <c r="T411" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U411" s="2" t="inlineStr"/>
+      <c r="U411" s="2" t="n">
+        <v>12</v>
+      </c>
       <c r="V411" t="inlineStr"/>
       <c r="W411" s="2" t="n">
         <v>152.1</v>
@@ -30745,7 +31637,9 @@
       <c r="T412" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U412" s="2" t="inlineStr"/>
+      <c r="U412" s="2" t="n">
+        <v>17.1</v>
+      </c>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="2" t="n">
         <v>146.6</v>
@@ -30822,7 +31716,9 @@
       <c r="T413" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="U413" s="2" t="inlineStr"/>
+      <c r="U413" s="2" t="n">
+        <v>17</v>
+      </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="n">
         <v>145.9</v>
@@ -30895,7 +31791,9 @@
       <c r="T414" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U414" s="2" t="inlineStr"/>
+      <c r="U414" s="2" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="n">
         <v>145.7</v>
@@ -30916,37 +31814,37 @@
         <v>400.48</v>
       </c>
       <c r="D415" t="n">
-        <v>400.49</v>
+        <v>403.15</v>
       </c>
       <c r="E415" t="n">
-        <v>398.6</v>
+        <v>398.14</v>
       </c>
       <c r="F415" t="n">
-        <v>399.18</v>
+        <v>402.63</v>
       </c>
       <c r="G415" t="n">
-        <v>2016359</v>
+        <v>6792177</v>
       </c>
       <c r="H415" s="3" t="n">
-        <v>0.21</v>
+        <v>1.07</v>
       </c>
       <c r="I415" t="n">
         <v>2.5</v>
       </c>
       <c r="J415" t="n">
-        <v>406.52</v>
+        <v>406.69</v>
       </c>
       <c r="K415" t="n">
-        <v>389.8</v>
+        <v>389.85</v>
       </c>
       <c r="L415" t="n">
-        <v>403.64</v>
+        <v>403.67</v>
       </c>
       <c r="M415" t="n">
-        <v>416.21</v>
+        <v>416.23</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>42.67</v>
+        <v>45.51</v>
       </c>
       <c r="O415" t="n">
         <v>29</v>
@@ -30966,10 +31864,10 @@
         <v>5</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>7.5</v>
+        <v>10.1</v>
       </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="2" t="inlineStr"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31748,7 +31748,7 @@
         <v>398.36</v>
       </c>
       <c r="G414" t="n">
-        <v>7596700</v>
+        <v>7746100</v>
       </c>
       <c r="H414" s="3" t="n">
         <v>1.69</v>
@@ -31820,31 +31820,31 @@
         <v>398.14</v>
       </c>
       <c r="F415" t="n">
-        <v>402.63</v>
+        <v>401.17</v>
       </c>
       <c r="G415" t="n">
-        <v>6792177</v>
+        <v>9436332</v>
       </c>
       <c r="H415" s="3" t="n">
-        <v>1.07</v>
+        <v>0.71</v>
       </c>
       <c r="I415" t="n">
         <v>2.5</v>
       </c>
       <c r="J415" t="n">
-        <v>406.69</v>
+        <v>406.62</v>
       </c>
       <c r="K415" t="n">
-        <v>389.85</v>
+        <v>389.83</v>
       </c>
       <c r="L415" t="n">
-        <v>403.67</v>
+        <v>403.66</v>
       </c>
       <c r="M415" t="n">
-        <v>416.23</v>
+        <v>416.22</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>45.51</v>
+        <v>44.34</v>
       </c>
       <c r="O415" t="n">
         <v>29</v>
@@ -31864,13 +31864,15 @@
         <v>5</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>15.3</v>
+        <v>14.8</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>10.1</v>
+        <v>11.4</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="inlineStr"/>
+      <c r="W415" s="2" t="n">
+        <v>148.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2654,7 +2654,7 @@
         <v>256.05</v>
       </c>
       <c r="L29" t="n">
-        <v>250.94</v>
+        <v>250.93</v>
       </c>
       <c r="M29" t="n">
         <v>239.75</v>
@@ -3327,7 +3327,7 @@
         <v>2.5</v>
       </c>
       <c r="J38" t="n">
-        <v>271.9</v>
+        <v>271.91</v>
       </c>
       <c r="K38" t="n">
         <v>261.08</v>
@@ -8187,7 +8187,7 @@
         <v>2.5</v>
       </c>
       <c r="J102" t="n">
-        <v>308.89</v>
+        <v>308.88</v>
       </c>
       <c r="K102" t="n">
         <v>302.49</v>
@@ -11301,7 +11301,7 @@
         <v>308.13</v>
       </c>
       <c r="K143" t="n">
-        <v>308.4</v>
+        <v>308.39</v>
       </c>
       <c r="L143" t="n">
         <v>300.06</v>
@@ -12576,7 +12576,7 @@
         <v>324.76</v>
       </c>
       <c r="K160" t="n">
-        <v>313.53</v>
+        <v>313.54</v>
       </c>
       <c r="L160" t="n">
         <v>307.62</v>
@@ -21688,7 +21688,7 @@
         <v>2.5</v>
       </c>
       <c r="J281" t="n">
-        <v>470.12</v>
+        <v>470.11</v>
       </c>
       <c r="K281" t="n">
         <v>443.36</v>
@@ -31622,7 +31622,7 @@
         <v>44.34</v>
       </c>
       <c r="O412" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31648,6 +31648,79 @@
       <c r="W412" s="3" t="n">
         <v>148.1</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>400.17</v>
+      </c>
+      <c r="D413" t="n">
+        <v>400.22</v>
+      </c>
+      <c r="E413" t="n">
+        <v>396.34</v>
+      </c>
+      <c r="F413" t="n">
+        <v>398.39</v>
+      </c>
+      <c r="G413" t="n">
+        <v>3626831</v>
+      </c>
+      <c r="H413" s="2" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J413" t="n">
+        <v>405.37</v>
+      </c>
+      <c r="K413" t="n">
+        <v>390.31</v>
+      </c>
+      <c r="L413" t="n">
+        <v>403.53</v>
+      </c>
+      <c r="M413" t="n">
+        <v>416.28</v>
+      </c>
+      <c r="N413" s="3" t="n">
+        <v>42.89</v>
+      </c>
+      <c r="O413" t="n">
+        <v>34</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T413" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="U413" s="3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -2654,7 +2654,7 @@
         <v>256.05</v>
       </c>
       <c r="L29" t="n">
-        <v>250.93</v>
+        <v>250.94</v>
       </c>
       <c r="M29" t="n">
         <v>239.75</v>
@@ -11301,7 +11301,7 @@
         <v>308.13</v>
       </c>
       <c r="K143" t="n">
-        <v>308.39</v>
+        <v>308.4</v>
       </c>
       <c r="L143" t="n">
         <v>300.06</v>
@@ -12576,7 +12576,7 @@
         <v>324.76</v>
       </c>
       <c r="K160" t="n">
-        <v>313.54</v>
+        <v>313.53</v>
       </c>
       <c r="L160" t="n">
         <v>307.62</v>
@@ -13251,7 +13251,7 @@
         <v>339.24</v>
       </c>
       <c r="K169" t="n">
-        <v>319.4</v>
+        <v>319.39</v>
       </c>
       <c r="L169" t="n">
         <v>312.32</v>
@@ -31670,13 +31670,13 @@
         <v>396.34</v>
       </c>
       <c r="F413" t="n">
-        <v>398.39</v>
+        <v>398.38</v>
       </c>
       <c r="G413" t="n">
-        <v>3626831</v>
+        <v>6251437</v>
       </c>
       <c r="H413" s="2" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.7</v>
       </c>
       <c r="I413" t="n">
         <v>2.5</v>
@@ -31694,7 +31694,7 @@
         <v>416.28</v>
       </c>
       <c r="N413" s="3" t="n">
-        <v>42.89</v>
+        <v>42.88</v>
       </c>
       <c r="O413" t="n">
         <v>34</v>
@@ -31711,13 +31711,13 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>4.95</v>
+        <v>4.96</v>
       </c>
       <c r="T413" s="3" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="U413" s="3" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="3" t="inlineStr"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31673,7 +31673,7 @@
         <v>398.38</v>
       </c>
       <c r="G413" t="n">
-        <v>6251437</v>
+        <v>6278212</v>
       </c>
       <c r="H413" s="2" t="n">
         <v>-0.7</v>
@@ -31720,7 +31720,9 @@
         <v>10</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="3" t="inlineStr"/>
+      <c r="W413" s="3" t="n">
+        <v>142.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31649,6 +31649,79 @@
         <v>142.2</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>397.07</v>
+      </c>
+      <c r="D413" t="n">
+        <v>398.23</v>
+      </c>
+      <c r="E413" t="n">
+        <v>396.58</v>
+      </c>
+      <c r="F413" t="n">
+        <v>396.7</v>
+      </c>
+      <c r="G413" t="n">
+        <v>1474882</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J413" t="n">
+        <v>403.87</v>
+      </c>
+      <c r="K413" t="n">
+        <v>390.7</v>
+      </c>
+      <c r="L413" t="n">
+        <v>403.25</v>
+      </c>
+      <c r="M413" t="n">
+        <v>416.33</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>49.96</v>
+      </c>
+      <c r="O413" t="n">
+        <v>37</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31664,40 +31664,40 @@
         <v>397.07</v>
       </c>
       <c r="D413" t="n">
-        <v>398.23</v>
+        <v>399.85</v>
       </c>
       <c r="E413" t="n">
-        <v>396.58</v>
+        <v>395.59</v>
       </c>
       <c r="F413" t="n">
-        <v>396.7</v>
+        <v>399.06</v>
       </c>
       <c r="G413" t="n">
-        <v>1474882</v>
-      </c>
-      <c r="H413" s="3" t="n">
-        <v>-0.42</v>
+        <v>4024495</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>0.17</v>
       </c>
       <c r="I413" t="n">
         <v>2.5</v>
       </c>
       <c r="J413" t="n">
-        <v>403.87</v>
+        <v>403.99</v>
       </c>
       <c r="K413" t="n">
-        <v>390.7</v>
+        <v>390.73</v>
       </c>
       <c r="L413" t="n">
-        <v>403.25</v>
+        <v>403.27</v>
       </c>
       <c r="M413" t="n">
-        <v>416.33</v>
+        <v>416.34</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>49.96</v>
+        <v>51.94</v>
       </c>
       <c r="O413" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31714,10 +31714,10 @@
         <v>4.95</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>6.7</v>
+        <v>8.1</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -3252,7 +3252,7 @@
         <v>2.5</v>
       </c>
       <c r="J37" t="n">
-        <v>271.91</v>
+        <v>271.9</v>
       </c>
       <c r="K37" t="n">
         <v>261.08</v>
@@ -8112,7 +8112,7 @@
         <v>2.5</v>
       </c>
       <c r="J101" t="n">
-        <v>308.88</v>
+        <v>308.89</v>
       </c>
       <c r="K101" t="n">
         <v>302.49</v>
@@ -11226,7 +11226,7 @@
         <v>308.13</v>
       </c>
       <c r="K142" t="n">
-        <v>308.4</v>
+        <v>308.39</v>
       </c>
       <c r="L142" t="n">
         <v>300.06</v>
@@ -13176,7 +13176,7 @@
         <v>339.24</v>
       </c>
       <c r="K168" t="n">
-        <v>319.39</v>
+        <v>319.4</v>
       </c>
       <c r="L168" t="n">
         <v>312.32</v>
@@ -21613,7 +21613,7 @@
         <v>2.5</v>
       </c>
       <c r="J280" t="n">
-        <v>470.11</v>
+        <v>470.12</v>
       </c>
       <c r="K280" t="n">
         <v>443.36</v>
@@ -31598,7 +31598,7 @@
         <v>398.38</v>
       </c>
       <c r="G412" t="n">
-        <v>6292600</v>
+        <v>6411000</v>
       </c>
       <c r="H412" s="3" t="n">
         <v>-0.7</v>
@@ -31664,28 +31664,28 @@
         <v>397.07</v>
       </c>
       <c r="D413" t="n">
-        <v>399.85</v>
+        <v>400.77</v>
       </c>
       <c r="E413" t="n">
         <v>395.59</v>
       </c>
       <c r="F413" t="n">
-        <v>399.06</v>
+        <v>400.07</v>
       </c>
       <c r="G413" t="n">
-        <v>4024495</v>
+        <v>6466737</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>0.17</v>
+        <v>0.42</v>
       </c>
       <c r="I413" t="n">
         <v>2.5</v>
       </c>
       <c r="J413" t="n">
-        <v>403.99</v>
+        <v>404.04</v>
       </c>
       <c r="K413" t="n">
-        <v>390.73</v>
+        <v>390.75</v>
       </c>
       <c r="L413" t="n">
         <v>403.27</v>
@@ -31694,10 +31694,10 @@
         <v>416.34</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>51.94</v>
+        <v>52.74</v>
       </c>
       <c r="O413" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31711,16 +31711,18 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>4.95</v>
+        <v>4.97</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>8.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>144.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31619,19 +31619,11 @@
         </is>
       </c>
       <c r="R412" t="inlineStr"/>
-      <c r="S412" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="T412" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="U412" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
+      <c r="S412" t="inlineStr"/>
+      <c r="T412" s="3" t="inlineStr"/>
+      <c r="U412" s="3" t="inlineStr"/>
       <c r="V412" t="inlineStr"/>
-      <c r="W412" s="3" t="n">
-        <v>144.8</v>
-      </c>
+      <c r="W412" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31582,31 +31582,47 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>395.33</v>
+      </c>
+      <c r="D412" t="n">
+        <v>395.5</v>
+      </c>
+      <c r="E412" t="n">
+        <v>392.15</v>
+      </c>
+      <c r="F412" t="n">
+        <v>392.68</v>
+      </c>
       <c r="G412" t="n">
-        <v>6466737</v>
-      </c>
-      <c r="H412" s="3" t="n">
-        <v>0</v>
+        <v>3752738</v>
+      </c>
+      <c r="H412" s="2" t="n">
+        <v>-1.43</v>
       </c>
       <c r="I412" t="n">
         <v>2.5</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>403.67</v>
+      </c>
+      <c r="K412" t="n">
+        <v>390.63</v>
+      </c>
+      <c r="L412" t="n">
+        <v>403.21</v>
+      </c>
+      <c r="M412" t="n">
+        <v>416.31</v>
+      </c>
       <c r="N412" s="3" t="n">
-        <v>51.38</v>
+        <v>46.85</v>
       </c>
       <c r="O412" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31619,9 +31635,15 @@
         </is>
       </c>
       <c r="R412" t="inlineStr"/>
-      <c r="S412" t="inlineStr"/>
-      <c r="T412" s="3" t="inlineStr"/>
-      <c r="U412" s="3" t="inlineStr"/>
+      <c r="S412" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="T412" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="U412" s="3" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="3" t="inlineStr"/>
     </row>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2504,7 +2504,7 @@
         <v>256.05</v>
       </c>
       <c r="L27" t="n">
-        <v>250.94</v>
+        <v>250.93</v>
       </c>
       <c r="M27" t="n">
         <v>239.75</v>
@@ -3177,7 +3177,7 @@
         <v>2.5</v>
       </c>
       <c r="J36" t="n">
-        <v>271.9</v>
+        <v>271.91</v>
       </c>
       <c r="K36" t="n">
         <v>261.08</v>
@@ -8037,7 +8037,7 @@
         <v>2.5</v>
       </c>
       <c r="J100" t="n">
-        <v>308.89</v>
+        <v>308.88</v>
       </c>
       <c r="K100" t="n">
         <v>302.49</v>
@@ -12426,7 +12426,7 @@
         <v>324.76</v>
       </c>
       <c r="K158" t="n">
-        <v>313.53</v>
+        <v>313.54</v>
       </c>
       <c r="L158" t="n">
         <v>307.62</v>
@@ -21538,7 +21538,7 @@
         <v>2.5</v>
       </c>
       <c r="J279" t="n">
-        <v>470.12</v>
+        <v>470.11</v>
       </c>
       <c r="K279" t="n">
         <v>443.36</v>
@@ -31582,47 +31582,47 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C412" t="n">
-        <v>395.33</v>
+        <v>397.07</v>
       </c>
       <c r="D412" t="n">
-        <v>395.5</v>
+        <v>400.78</v>
       </c>
       <c r="E412" t="n">
-        <v>392.15</v>
+        <v>395.58</v>
       </c>
       <c r="F412" t="n">
-        <v>392.68</v>
+        <v>400.07</v>
       </c>
       <c r="G412" t="n">
-        <v>3752738</v>
-      </c>
-      <c r="H412" s="2" t="n">
-        <v>-1.43</v>
+        <v>6519900</v>
+      </c>
+      <c r="H412" s="1" t="n">
+        <v>0.42</v>
       </c>
       <c r="I412" t="n">
         <v>2.5</v>
       </c>
       <c r="J412" t="n">
-        <v>403.67</v>
+        <v>404.04</v>
       </c>
       <c r="K412" t="n">
-        <v>390.63</v>
+        <v>390.75</v>
       </c>
       <c r="L412" t="n">
-        <v>403.21</v>
+        <v>403.27</v>
       </c>
       <c r="M412" t="n">
-        <v>416.31</v>
+        <v>416.34</v>
       </c>
       <c r="N412" s="3" t="n">
-        <v>46.85</v>
+        <v>52.74</v>
       </c>
       <c r="O412" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31635,17 +31635,84 @@
         </is>
       </c>
       <c r="R412" t="inlineStr"/>
-      <c r="S412" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="T412" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="U412" s="3" t="n">
-        <v>8.4</v>
-      </c>
+      <c r="S412" t="inlineStr"/>
+      <c r="T412" s="3" t="inlineStr"/>
+      <c r="U412" s="3" t="inlineStr"/>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="3" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>395.33</v>
+      </c>
+      <c r="D413" t="n">
+        <v>395.5</v>
+      </c>
+      <c r="E413" t="n">
+        <v>391.87</v>
+      </c>
+      <c r="F413" t="n">
+        <v>392.77</v>
+      </c>
+      <c r="G413" t="n">
+        <v>6904168</v>
+      </c>
+      <c r="H413" s="2" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J413" t="n">
+        <v>402.27</v>
+      </c>
+      <c r="K413" t="n">
+        <v>391.16</v>
+      </c>
+      <c r="L413" t="n">
+        <v>402.9</v>
+      </c>
+      <c r="M413" t="n">
+        <v>416.37</v>
+      </c>
+      <c r="N413" s="3" t="n">
+        <v>41.91</v>
+      </c>
+      <c r="O413" t="n">
+        <v>35</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="T413" s="3" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="U413" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31662,19 +31662,19 @@
         <v>391.87</v>
       </c>
       <c r="F413" t="n">
-        <v>392.77</v>
+        <v>392.88</v>
       </c>
       <c r="G413" t="n">
-        <v>6904168</v>
+        <v>7353000</v>
       </c>
       <c r="H413" s="2" t="n">
-        <v>-1.82</v>
+        <v>-1.8</v>
       </c>
       <c r="I413" t="n">
         <v>2.5</v>
       </c>
       <c r="J413" t="n">
-        <v>402.27</v>
+        <v>402.28</v>
       </c>
       <c r="K413" t="n">
         <v>391.16</v>
@@ -31686,7 +31686,7 @@
         <v>416.37</v>
       </c>
       <c r="N413" s="3" t="n">
-        <v>41.91</v>
+        <v>41.98</v>
       </c>
       <c r="O413" t="n">
         <v>35</v>
@@ -31709,10 +31709,12 @@
         <v>15.2</v>
       </c>
       <c r="U413" s="3" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="3" t="inlineStr"/>
+      <c r="W413" s="3" t="n">
+        <v>146.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31652,41 +31652,25 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="C413" t="n">
-        <v>395.33</v>
-      </c>
-      <c r="D413" t="n">
-        <v>395.5</v>
-      </c>
-      <c r="E413" t="n">
-        <v>391.87</v>
-      </c>
-      <c r="F413" t="n">
-        <v>392.88</v>
-      </c>
+      <c r="C413" t="inlineStr"/>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr"/>
       <c r="G413" t="n">
         <v>7353000</v>
       </c>
-      <c r="H413" s="2" t="n">
-        <v>-1.8</v>
+      <c r="H413" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I413" t="n">
         <v>2.5</v>
       </c>
-      <c r="J413" t="n">
-        <v>402.28</v>
-      </c>
-      <c r="K413" t="n">
-        <v>391.16</v>
-      </c>
-      <c r="L413" t="n">
-        <v>402.9</v>
-      </c>
-      <c r="M413" t="n">
-        <v>416.37</v>
-      </c>
+      <c r="J413" t="inlineStr"/>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr"/>
+      <c r="M413" t="inlineStr"/>
       <c r="N413" s="3" t="n">
-        <v>41.98</v>
+        <v>47.52</v>
       </c>
       <c r="O413" t="n">
         <v>35</v>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31652,25 +31652,41 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr"/>
-      <c r="D413" t="inlineStr"/>
-      <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
+      <c r="C413" t="n">
+        <v>395.33</v>
+      </c>
+      <c r="D413" t="n">
+        <v>395.5</v>
+      </c>
+      <c r="E413" t="n">
+        <v>391.87</v>
+      </c>
+      <c r="F413" t="n">
+        <v>392.88</v>
+      </c>
       <c r="G413" t="n">
-        <v>7353000</v>
-      </c>
-      <c r="H413" s="3" t="n">
-        <v>0</v>
+        <v>7395800</v>
+      </c>
+      <c r="H413" s="2" t="n">
+        <v>-1.8</v>
       </c>
       <c r="I413" t="n">
         <v>2.5</v>
       </c>
-      <c r="J413" t="inlineStr"/>
-      <c r="K413" t="inlineStr"/>
-      <c r="L413" t="inlineStr"/>
-      <c r="M413" t="inlineStr"/>
+      <c r="J413" t="n">
+        <v>402.28</v>
+      </c>
+      <c r="K413" t="n">
+        <v>391.16</v>
+      </c>
+      <c r="L413" t="n">
+        <v>402.9</v>
+      </c>
+      <c r="M413" t="n">
+        <v>416.37</v>
+      </c>
       <c r="N413" s="3" t="n">
-        <v>47.52</v>
+        <v>41.98</v>
       </c>
       <c r="O413" t="n">
         <v>35</v>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31689,7 +31689,7 @@
         <v>41.98</v>
       </c>
       <c r="O413" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31715,6 +31715,83 @@
       <c r="W413" s="3" t="n">
         <v>146.1</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>391.96</v>
+      </c>
+      <c r="D414" t="n">
+        <v>393.07</v>
+      </c>
+      <c r="E414" t="n">
+        <v>389.05</v>
+      </c>
+      <c r="F414" t="n">
+        <v>391.27</v>
+      </c>
+      <c r="G414" t="n">
+        <v>5103102</v>
+      </c>
+      <c r="H414" s="2" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="I414" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J414" t="n">
+        <v>400.77</v>
+      </c>
+      <c r="K414" t="n">
+        <v>391.54</v>
+      </c>
+      <c r="L414" t="n">
+        <v>402.58</v>
+      </c>
+      <c r="M414" t="n">
+        <v>416.4</v>
+      </c>
+      <c r="N414" s="3" t="n">
+        <v>33.05</v>
+      </c>
+      <c r="O414" t="n">
+        <v>35</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>2nd: MA60, 50% cash, 5d</t>
+        </is>
+      </c>
+      <c r="S414" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="T414" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="U414" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31665,7 +31665,7 @@
         <v>392.88</v>
       </c>
       <c r="G413" t="n">
-        <v>7395800</v>
+        <v>7547000</v>
       </c>
       <c r="H413" s="2" t="n">
         <v>-1.8</v>
@@ -31737,34 +31737,34 @@
         <v>389.05</v>
       </c>
       <c r="F414" t="n">
-        <v>391.27</v>
+        <v>391.69</v>
       </c>
       <c r="G414" t="n">
-        <v>5103102</v>
+        <v>6667320</v>
       </c>
       <c r="H414" s="2" t="n">
-        <v>-0.41</v>
+        <v>-0.3</v>
       </c>
       <c r="I414" t="n">
         <v>2.5</v>
       </c>
       <c r="J414" t="n">
-        <v>400.77</v>
+        <v>400.8</v>
       </c>
       <c r="K414" t="n">
-        <v>391.54</v>
+        <v>391.55</v>
       </c>
       <c r="L414" t="n">
-        <v>402.58</v>
+        <v>402.59</v>
       </c>
       <c r="M414" t="n">
         <v>416.4</v>
       </c>
       <c r="N414" s="3" t="n">
-        <v>33.05</v>
+        <v>33.3</v>
       </c>
       <c r="O414" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31776,22 +31776,20 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R414" t="inlineStr">
-        <is>
-          <t>2nd: MA60, 50% cash, 5d</t>
-        </is>
-      </c>
+      <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.18</v>
+        <v>5.16</v>
       </c>
       <c r="T414" s="3" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="U414" s="3" t="n">
-        <v>11.6</v>
+        <v>12.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="3" t="inlineStr"/>
+      <c r="W414" s="3" t="n">
+        <v>146</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31727,41 +31727,25 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="C414" t="n">
-        <v>391.96</v>
-      </c>
-      <c r="D414" t="n">
-        <v>393.07</v>
-      </c>
-      <c r="E414" t="n">
-        <v>389.05</v>
-      </c>
-      <c r="F414" t="n">
-        <v>391.69</v>
-      </c>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
       <c r="G414" t="n">
         <v>6667320</v>
       </c>
-      <c r="H414" s="2" t="n">
-        <v>-0.3</v>
+      <c r="H414" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I414" t="n">
         <v>2.5</v>
       </c>
-      <c r="J414" t="n">
-        <v>400.8</v>
-      </c>
-      <c r="K414" t="n">
-        <v>391.55</v>
-      </c>
-      <c r="L414" t="n">
-        <v>402.59</v>
-      </c>
-      <c r="M414" t="n">
-        <v>416.4</v>
-      </c>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
       <c r="N414" s="3" t="n">
-        <v>33.3</v>
+        <v>34.03</v>
       </c>
       <c r="O414" t="n">
         <v>36</v>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31727,25 +31727,41 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>391.96</v>
+      </c>
+      <c r="D414" t="n">
+        <v>393.07</v>
+      </c>
+      <c r="E414" t="n">
+        <v>389.05</v>
+      </c>
+      <c r="F414" t="n">
+        <v>391.69</v>
+      </c>
       <c r="G414" t="n">
-        <v>6667320</v>
-      </c>
-      <c r="H414" s="3" t="n">
-        <v>0</v>
+        <v>6694400</v>
+      </c>
+      <c r="H414" s="2" t="n">
+        <v>-0.3</v>
       </c>
       <c r="I414" t="n">
         <v>2.5</v>
       </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>400.8</v>
+      </c>
+      <c r="K414" t="n">
+        <v>391.55</v>
+      </c>
+      <c r="L414" t="n">
+        <v>402.59</v>
+      </c>
+      <c r="M414" t="n">
+        <v>416.4</v>
+      </c>
       <c r="N414" s="3" t="n">
-        <v>34.03</v>
+        <v>33.3</v>
       </c>
       <c r="O414" t="n">
         <v>36</v>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31635,11 +31635,19 @@
         </is>
       </c>
       <c r="R412" t="inlineStr"/>
-      <c r="S412" t="inlineStr"/>
-      <c r="T412" s="3" t="inlineStr"/>
-      <c r="U412" s="3" t="inlineStr"/>
+      <c r="S412" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="T412" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="U412" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="V412" t="inlineStr"/>
-      <c r="W412" s="3" t="inlineStr"/>
+      <c r="W412" s="3" t="n">
+        <v>144.8</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31799,6 +31799,79 @@
         <v>146</v>
       </c>
     </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>392.21</v>
+      </c>
+      <c r="D415" t="n">
+        <v>394.22</v>
+      </c>
+      <c r="E415" t="n">
+        <v>390.05</v>
+      </c>
+      <c r="F415" t="n">
+        <v>393.12</v>
+      </c>
+      <c r="G415" t="n">
+        <v>4781684</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I415" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J415" t="n">
+        <v>399.32</v>
+      </c>
+      <c r="K415" t="n">
+        <v>391.92</v>
+      </c>
+      <c r="L415" t="n">
+        <v>402.3</v>
+      </c>
+      <c r="M415" t="n">
+        <v>416.44</v>
+      </c>
+      <c r="N415" s="3" t="n">
+        <v>37.23</v>
+      </c>
+      <c r="O415" t="n">
+        <v>38</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T415" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="U415" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31748,7 +31748,7 @@
         <v>391.69</v>
       </c>
       <c r="G414" t="n">
-        <v>6694400</v>
+        <v>6710200</v>
       </c>
       <c r="H414" s="2" t="n">
         <v>-0.3</v>
@@ -31820,22 +31820,22 @@
         <v>390.05</v>
       </c>
       <c r="F415" t="n">
-        <v>393.12</v>
+        <v>393.41</v>
       </c>
       <c r="G415" t="n">
-        <v>4781684</v>
+        <v>7231918</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>0.37</v>
+        <v>0.44</v>
       </c>
       <c r="I415" t="n">
         <v>2.5</v>
       </c>
       <c r="J415" t="n">
-        <v>399.32</v>
+        <v>399.34</v>
       </c>
       <c r="K415" t="n">
-        <v>391.92</v>
+        <v>391.93</v>
       </c>
       <c r="L415" t="n">
         <v>402.3</v>
@@ -31844,10 +31844,10 @@
         <v>416.44</v>
       </c>
       <c r="N415" s="3" t="n">
-        <v>37.23</v>
+        <v>37.57</v>
       </c>
       <c r="O415" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31861,16 +31861,18 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.2</v>
+        <v>5.18</v>
       </c>
       <c r="T415" s="3" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="U415" s="3" t="n">
-        <v>11.2</v>
+        <v>12.5</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="3" t="inlineStr"/>
+      <c r="W415" s="3" t="n">
+        <v>144.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31735,25 +31735,41 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>392.21</v>
+      </c>
+      <c r="D414" t="n">
+        <v>394.22</v>
+      </c>
+      <c r="E414" t="n">
+        <v>390.05</v>
+      </c>
+      <c r="F414" t="n">
+        <v>393.41</v>
+      </c>
       <c r="G414" t="n">
-        <v>7231918</v>
-      </c>
-      <c r="H414" s="3" t="n">
-        <v>0</v>
+        <v>7690100</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>0.44</v>
       </c>
       <c r="I414" t="n">
         <v>2.5</v>
       </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>399.34</v>
+      </c>
+      <c r="K414" t="n">
+        <v>391.93</v>
+      </c>
+      <c r="L414" t="n">
+        <v>402.3</v>
+      </c>
+      <c r="M414" t="n">
+        <v>416.44</v>
+      </c>
       <c r="N414" s="3" t="n">
-        <v>35.51</v>
+        <v>37.57</v>
       </c>
       <c r="O414" t="n">
         <v>37</v>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2279,7 +2279,7 @@
         <v>256.05</v>
       </c>
       <c r="L24" t="n">
-        <v>250.93</v>
+        <v>250.94</v>
       </c>
       <c r="M24" t="n">
         <v>239.75</v>
@@ -10926,7 +10926,7 @@
         <v>308.13</v>
       </c>
       <c r="K138" t="n">
-        <v>308.39</v>
+        <v>308.4</v>
       </c>
       <c r="L138" t="n">
         <v>300.06</v>
@@ -31648,6 +31648,83 @@
       <c r="W412" s="2" t="n">
         <v>144.9</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="4" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B413" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C413" s="4" t="n">
+        <v>379.76</v>
+      </c>
+      <c r="D413" s="4" t="n">
+        <v>381.52</v>
+      </c>
+      <c r="E413" s="4" t="n">
+        <v>376.88</v>
+      </c>
+      <c r="F413" s="4" t="n">
+        <v>378.04</v>
+      </c>
+      <c r="G413" s="4" t="n">
+        <v>6250516</v>
+      </c>
+      <c r="H413" s="5" t="n">
+        <v>-3.91</v>
+      </c>
+      <c r="I413" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J413" s="4" t="n">
+        <v>397.79</v>
+      </c>
+      <c r="K413" s="4" t="n">
+        <v>391.92</v>
+      </c>
+      <c r="L413" s="4" t="n">
+        <v>401.85</v>
+      </c>
+      <c r="M413" s="4" t="n">
+        <v>416.39</v>
+      </c>
+      <c r="N413" s="6" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="O413" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="P413" s="4" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" s="4" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" s="4" t="inlineStr">
+        <is>
+          <t>2nd: MA60, 50% cash, 5d</t>
+        </is>
+      </c>
+      <c r="S413" s="4" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="T413" s="6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="U413" s="6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="V413" s="4" t="inlineStr"/>
+      <c r="W413" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -2952,7 +2952,7 @@
         <v>2.5</v>
       </c>
       <c r="J33" t="n">
-        <v>271.91</v>
+        <v>271.9</v>
       </c>
       <c r="K33" t="n">
         <v>261.08</v>
@@ -3872,7 +3872,7 @@
         <v>2.5</v>
       </c>
       <c r="J45" t="n">
-        <v>280.59</v>
+        <v>280.58</v>
       </c>
       <c r="K45" t="n">
         <v>268.78</v>
@@ -12201,7 +12201,7 @@
         <v>324.76</v>
       </c>
       <c r="K155" t="n">
-        <v>313.54</v>
+        <v>313.53</v>
       </c>
       <c r="L155" t="n">
         <v>307.62</v>
@@ -21313,7 +21313,7 @@
         <v>2.5</v>
       </c>
       <c r="J276" t="n">
-        <v>470.11</v>
+        <v>470.12</v>
       </c>
       <c r="K276" t="n">
         <v>443.36</v>
@@ -31670,13 +31670,13 @@
         <v>376.88</v>
       </c>
       <c r="F413" s="4" t="n">
-        <v>378.04</v>
+        <v>377.91</v>
       </c>
       <c r="G413" s="4" t="n">
-        <v>6250516</v>
+        <v>14038684</v>
       </c>
       <c r="H413" s="5" t="n">
-        <v>-3.91</v>
+        <v>-3.94</v>
       </c>
       <c r="I413" s="4" t="n">
         <v>2.5</v>
@@ -31694,7 +31694,7 @@
         <v>416.39</v>
       </c>
       <c r="N413" s="6" t="n">
-        <v>32.53</v>
+        <v>32.47</v>
       </c>
       <c r="O413" s="4" t="n">
         <v>34</v>
@@ -31715,16 +31715,18 @@
         </is>
       </c>
       <c r="S413" s="4" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="T413" s="6" t="n">
-        <v>16.5</v>
+        <v>16.1</v>
       </c>
       <c r="U413" s="6" t="n">
-        <v>9.5</v>
+        <v>11.3</v>
       </c>
       <c r="V413" s="4" t="inlineStr"/>
-      <c r="W413" s="6" t="inlineStr"/>
+      <c r="W413" s="6" t="n">
+        <v>146.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31653,6 +31653,79 @@
         <v>146.2</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>380.94</v>
+      </c>
+      <c r="D413" t="n">
+        <v>382.76</v>
+      </c>
+      <c r="E413" t="n">
+        <v>380.32</v>
+      </c>
+      <c r="F413" t="n">
+        <v>380.34</v>
+      </c>
+      <c r="G413" t="n">
+        <v>3685433</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J413" t="n">
+        <v>396.38</v>
+      </c>
+      <c r="K413" t="n">
+        <v>391.89</v>
+      </c>
+      <c r="L413" t="n">
+        <v>401.4</v>
+      </c>
+      <c r="M413" t="n">
+        <v>416.35</v>
+      </c>
+      <c r="N413" s="3" t="n">
+        <v>31.14</v>
+      </c>
+      <c r="O413" t="n">
+        <v>33</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="T413" s="3" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="U413" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -2877,7 +2877,7 @@
         <v>2.5</v>
       </c>
       <c r="J32" t="n">
-        <v>271.9</v>
+        <v>271.91</v>
       </c>
       <c r="K32" t="n">
         <v>261.08</v>
@@ -3797,7 +3797,7 @@
         <v>2.5</v>
       </c>
       <c r="J44" t="n">
-        <v>280.58</v>
+        <v>280.59</v>
       </c>
       <c r="K44" t="n">
         <v>268.78</v>
@@ -12126,7 +12126,7 @@
         <v>324.76</v>
       </c>
       <c r="K154" t="n">
-        <v>313.53</v>
+        <v>313.54</v>
       </c>
       <c r="L154" t="n">
         <v>307.62</v>
@@ -21238,7 +21238,7 @@
         <v>2.5</v>
       </c>
       <c r="J275" t="n">
-        <v>470.12</v>
+        <v>470.11</v>
       </c>
       <c r="K275" t="n">
         <v>443.36</v>
@@ -31598,7 +31598,7 @@
         <v>377.91</v>
       </c>
       <c r="G412" s="4" t="n">
-        <v>14750400</v>
+        <v>14843400</v>
       </c>
       <c r="H412" s="5" t="n">
         <v>-3.94</v>
@@ -31668,40 +31668,40 @@
         <v>380.94</v>
       </c>
       <c r="D413" t="n">
-        <v>382.76</v>
+        <v>383</v>
       </c>
       <c r="E413" t="n">
-        <v>380.32</v>
+        <v>379.71</v>
       </c>
       <c r="F413" t="n">
-        <v>380.34</v>
+        <v>382.89</v>
       </c>
       <c r="G413" t="n">
-        <v>3685433</v>
+        <v>7718834</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>0.64</v>
+        <v>1.32</v>
       </c>
       <c r="I413" t="n">
         <v>2.5</v>
       </c>
       <c r="J413" t="n">
-        <v>396.38</v>
+        <v>396.51</v>
       </c>
       <c r="K413" t="n">
-        <v>391.89</v>
+        <v>391.93</v>
       </c>
       <c r="L413" t="n">
-        <v>401.4</v>
+        <v>401.42</v>
       </c>
       <c r="M413" t="n">
-        <v>416.35</v>
+        <v>416.36</v>
       </c>
       <c r="N413" s="3" t="n">
-        <v>31.14</v>
+        <v>33.9</v>
       </c>
       <c r="O413" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31715,13 +31715,13 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.27</v>
+        <v>5.26</v>
       </c>
       <c r="T413" s="3" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="U413" s="3" t="n">
-        <v>10</v>
+        <v>11.7</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="3" t="inlineStr"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31589,25 +31589,41 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="C412" t="n">
+        <v>380.94</v>
+      </c>
+      <c r="D412" t="n">
+        <v>383</v>
+      </c>
+      <c r="E412" t="n">
+        <v>379.72</v>
+      </c>
+      <c r="F412" t="n">
+        <v>382.89</v>
+      </c>
       <c r="G412" t="n">
-        <v>7901795</v>
-      </c>
-      <c r="H412" s="3" t="n">
-        <v>0</v>
+        <v>8100800</v>
+      </c>
+      <c r="H412" s="1" t="n">
+        <v>1.32</v>
       </c>
       <c r="I412" t="n">
         <v>2.5</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
-      <c r="N412" s="1" t="n">
-        <v>28.28</v>
+      <c r="J412" t="n">
+        <v>396.51</v>
+      </c>
+      <c r="K412" t="n">
+        <v>391.93</v>
+      </c>
+      <c r="L412" t="n">
+        <v>401.42</v>
+      </c>
+      <c r="M412" t="n">
+        <v>416.36</v>
+      </c>
+      <c r="N412" s="3" t="n">
+        <v>33.9</v>
       </c>
       <c r="O412" t="n">
         <v>32</v>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31626,7 +31626,7 @@
         <v>33.9</v>
       </c>
       <c r="O412" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31653,6 +31653,79 @@
         <v>144.6</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>384.39</v>
+      </c>
+      <c r="D413" t="n">
+        <v>384.59</v>
+      </c>
+      <c r="E413" t="n">
+        <v>380.18</v>
+      </c>
+      <c r="F413" t="n">
+        <v>380.52</v>
+      </c>
+      <c r="G413" t="n">
+        <v>4975503</v>
+      </c>
+      <c r="H413" s="2" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J413" t="n">
+        <v>395.7</v>
+      </c>
+      <c r="K413" t="n">
+        <v>391.98</v>
+      </c>
+      <c r="L413" t="n">
+        <v>400.94</v>
+      </c>
+      <c r="M413" t="n">
+        <v>416.3</v>
+      </c>
+      <c r="N413" s="3" t="n">
+        <v>36.56</v>
+      </c>
+      <c r="O413" t="n">
+        <v>33</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T413" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="U413" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -12051,7 +12051,7 @@
         <v>324.76</v>
       </c>
       <c r="K153" t="n">
-        <v>313.54</v>
+        <v>313.53</v>
       </c>
       <c r="L153" t="n">
         <v>307.62</v>
@@ -12726,7 +12726,7 @@
         <v>339.24</v>
       </c>
       <c r="K162" t="n">
-        <v>319.4</v>
+        <v>319.39</v>
       </c>
       <c r="L162" t="n">
         <v>312.32</v>
@@ -31602,7 +31602,7 @@
         <v>382.89</v>
       </c>
       <c r="G412" t="n">
-        <v>8100800</v>
+        <v>8122800</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>1.32</v>
@@ -31674,34 +31674,34 @@
         <v>380.18</v>
       </c>
       <c r="F413" t="n">
-        <v>380.52</v>
+        <v>380.84</v>
       </c>
       <c r="G413" t="n">
-        <v>4975503</v>
+        <v>6924147</v>
       </c>
       <c r="H413" s="2" t="n">
-        <v>-0.62</v>
+        <v>-0.54</v>
       </c>
       <c r="I413" t="n">
         <v>2.5</v>
       </c>
       <c r="J413" t="n">
-        <v>395.7</v>
+        <v>395.72</v>
       </c>
       <c r="K413" t="n">
-        <v>391.98</v>
+        <v>391.99</v>
       </c>
       <c r="L413" t="n">
-        <v>400.94</v>
+        <v>400.95</v>
       </c>
       <c r="M413" t="n">
         <v>416.3</v>
       </c>
       <c r="N413" s="3" t="n">
-        <v>36.56</v>
+        <v>36.76</v>
       </c>
       <c r="O413" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31715,16 +31715,18 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.3</v>
+        <v>5.29</v>
       </c>
       <c r="T413" s="3" t="n">
-        <v>15.9</v>
+        <v>16.3</v>
       </c>
       <c r="U413" s="3" t="n">
-        <v>11.4</v>
+        <v>12.2</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="3" t="inlineStr"/>
+      <c r="W413" s="3" t="n">
+        <v>141.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31677,7 +31677,7 @@
         <v>380.84</v>
       </c>
       <c r="G413" t="n">
-        <v>6924147</v>
+        <v>6934700</v>
       </c>
       <c r="H413" s="2" t="n">
         <v>-0.54</v>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31701,7 +31701,7 @@
         <v>36.76</v>
       </c>
       <c r="O413" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31728,6 +31728,79 @@
         <v>141.9</v>
       </c>
     </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>381.91</v>
+      </c>
+      <c r="D414" t="n">
+        <v>382.81</v>
+      </c>
+      <c r="E414" t="n">
+        <v>380.36</v>
+      </c>
+      <c r="F414" t="n">
+        <v>382.66</v>
+      </c>
+      <c r="G414" t="n">
+        <v>2652692</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I414" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J414" t="n">
+        <v>394.71</v>
+      </c>
+      <c r="K414" t="n">
+        <v>392.13</v>
+      </c>
+      <c r="L414" t="n">
+        <v>400.49</v>
+      </c>
+      <c r="M414" t="n">
+        <v>416.23</v>
+      </c>
+      <c r="N414" s="3" t="n">
+        <v>36.11</v>
+      </c>
+      <c r="O414" t="n">
+        <v>27</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="T414" s="3" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="U414" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31677,7 +31677,7 @@
         <v>380.84</v>
       </c>
       <c r="G413" t="n">
-        <v>6934700</v>
+        <v>7016200</v>
       </c>
       <c r="H413" s="2" t="n">
         <v>-0.54</v>
@@ -31743,19 +31743,19 @@
         <v>381.91</v>
       </c>
       <c r="D414" t="n">
-        <v>382.81</v>
+        <v>383.69</v>
       </c>
       <c r="E414" t="n">
         <v>380.36</v>
       </c>
       <c r="F414" t="n">
-        <v>382.66</v>
+        <v>382.76</v>
       </c>
       <c r="G414" t="n">
-        <v>2652692</v>
+        <v>5811518</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="I414" t="n">
         <v>2.5</v>
@@ -31773,10 +31773,10 @@
         <v>416.23</v>
       </c>
       <c r="N414" s="3" t="n">
-        <v>36.11</v>
+        <v>36.22</v>
       </c>
       <c r="O414" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31790,16 +31790,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="T414" s="3" t="n">
-        <v>17.3</v>
+        <v>16.4</v>
       </c>
       <c r="U414" s="3" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="3" t="inlineStr"/>
+      <c r="W414" s="3" t="n">
+        <v>142.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31739,41 +31739,25 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C414" t="n">
-        <v>381.91</v>
-      </c>
-      <c r="D414" t="n">
-        <v>383.69</v>
-      </c>
-      <c r="E414" t="n">
-        <v>380.36</v>
-      </c>
-      <c r="F414" t="n">
-        <v>382.76</v>
-      </c>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
       <c r="G414" t="n">
         <v>5811518</v>
       </c>
-      <c r="H414" s="1" t="n">
-        <v>0.5</v>
+      <c r="H414" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I414" t="n">
         <v>2.5</v>
       </c>
-      <c r="J414" t="n">
-        <v>394.71</v>
-      </c>
-      <c r="K414" t="n">
-        <v>392.13</v>
-      </c>
-      <c r="L414" t="n">
-        <v>400.49</v>
-      </c>
-      <c r="M414" t="n">
-        <v>416.23</v>
-      </c>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
       <c r="N414" s="3" t="n">
-        <v>36.22</v>
+        <v>34.05</v>
       </c>
       <c r="O414" t="n">
         <v>28</v>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31739,28 +31739,44 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>381.91</v>
+      </c>
+      <c r="D414" t="n">
+        <v>383.7</v>
+      </c>
+      <c r="E414" t="n">
+        <v>380.36</v>
+      </c>
+      <c r="F414" t="n">
+        <v>382.76</v>
+      </c>
       <c r="G414" t="n">
-        <v>5811518</v>
-      </c>
-      <c r="H414" s="3" t="n">
-        <v>0</v>
+        <v>5844800</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>0.5</v>
       </c>
       <c r="I414" t="n">
         <v>2.5</v>
       </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>394.71</v>
+      </c>
+      <c r="K414" t="n">
+        <v>392.13</v>
+      </c>
+      <c r="L414" t="n">
+        <v>400.49</v>
+      </c>
+      <c r="M414" t="n">
+        <v>416.23</v>
+      </c>
       <c r="N414" s="3" t="n">
-        <v>34.05</v>
+        <v>36.22</v>
       </c>
       <c r="O414" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31776,7 +31776,7 @@
         <v>36.22</v>
       </c>
       <c r="O414" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31802,6 +31802,79 @@
       <c r="W414" s="3" t="n">
         <v>142.8</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>384.45</v>
+      </c>
+      <c r="D415" t="n">
+        <v>385.22</v>
+      </c>
+      <c r="E415" t="n">
+        <v>378.87</v>
+      </c>
+      <c r="F415" t="n">
+        <v>379.66</v>
+      </c>
+      <c r="G415" t="n">
+        <v>4913113</v>
+      </c>
+      <c r="H415" s="2" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="I415" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J415" t="n">
+        <v>393.19</v>
+      </c>
+      <c r="K415" t="n">
+        <v>392.15</v>
+      </c>
+      <c r="L415" t="n">
+        <v>400.03</v>
+      </c>
+      <c r="M415" t="n">
+        <v>416.15</v>
+      </c>
+      <c r="N415" s="3" t="n">
+        <v>38.08</v>
+      </c>
+      <c r="O415" t="n">
+        <v>31</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T415" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="U415" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31752,7 +31752,7 @@
         <v>382.76</v>
       </c>
       <c r="G414" t="n">
-        <v>5844800</v>
+        <v>6095900</v>
       </c>
       <c r="H414" s="1" t="n">
         <v>0.5</v>
@@ -31821,34 +31821,34 @@
         <v>385.22</v>
       </c>
       <c r="E415" t="n">
-        <v>378.87</v>
+        <v>378.12</v>
       </c>
       <c r="F415" t="n">
-        <v>379.66</v>
+        <v>380.14</v>
       </c>
       <c r="G415" t="n">
-        <v>4913113</v>
+        <v>8892962</v>
       </c>
       <c r="H415" s="2" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.68</v>
       </c>
       <c r="I415" t="n">
         <v>2.5</v>
       </c>
       <c r="J415" t="n">
-        <v>393.19</v>
+        <v>393.21</v>
       </c>
       <c r="K415" t="n">
-        <v>392.15</v>
+        <v>392.16</v>
       </c>
       <c r="L415" t="n">
         <v>400.03</v>
       </c>
       <c r="M415" t="n">
-        <v>416.15</v>
+        <v>416.16</v>
       </c>
       <c r="N415" s="3" t="n">
-        <v>38.08</v>
+        <v>38.41</v>
       </c>
       <c r="O415" t="n">
         <v>31</v>
@@ -31865,13 +31865,13 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.25</v>
+        <v>5.28</v>
       </c>
       <c r="T415" s="3" t="n">
-        <v>15.8</v>
+        <v>15.3</v>
       </c>
       <c r="U415" s="3" t="n">
-        <v>10.4</v>
+        <v>11</v>
       </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="3" t="inlineStr"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31739,25 +31739,41 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>384.45</v>
+      </c>
+      <c r="D414" t="n">
+        <v>385.22</v>
+      </c>
+      <c r="E414" t="n">
+        <v>378.11</v>
+      </c>
+      <c r="F414" t="n">
+        <v>380.14</v>
+      </c>
       <c r="G414" t="n">
-        <v>9032801</v>
-      </c>
-      <c r="H414" s="2" t="n">
-        <v>0</v>
+        <v>9154900</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-0.68</v>
       </c>
       <c r="I414" t="n">
         <v>2.5</v>
       </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>393.21</v>
+      </c>
+      <c r="K414" t="n">
+        <v>392.16</v>
+      </c>
+      <c r="L414" t="n">
+        <v>400.03</v>
+      </c>
+      <c r="M414" t="n">
+        <v>416.16</v>
+      </c>
       <c r="N414" s="2" t="n">
-        <v>40.34</v>
+        <v>38.41</v>
       </c>
       <c r="O414" t="n">
         <v>31</v>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31626,7 +31626,7 @@
         <v>38.41</v>
       </c>
       <c r="O412" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2577,7 +2577,7 @@
         <v>2.5</v>
       </c>
       <c r="J28" t="n">
-        <v>271.91</v>
+        <v>271.9</v>
       </c>
       <c r="K28" t="n">
         <v>261.08</v>
@@ -3497,7 +3497,7 @@
         <v>2.5</v>
       </c>
       <c r="J40" t="n">
-        <v>280.59</v>
+        <v>280.58</v>
       </c>
       <c r="K40" t="n">
         <v>268.78</v>
@@ -10551,7 +10551,7 @@
         <v>308.13</v>
       </c>
       <c r="K133" t="n">
-        <v>308.4</v>
+        <v>308.39</v>
       </c>
       <c r="L133" t="n">
         <v>300.06</v>
@@ -11826,7 +11826,7 @@
         <v>324.76</v>
       </c>
       <c r="K150" t="n">
-        <v>313.53</v>
+        <v>313.54</v>
       </c>
       <c r="L150" t="n">
         <v>307.62</v>
@@ -12501,7 +12501,7 @@
         <v>339.24</v>
       </c>
       <c r="K159" t="n">
-        <v>319.39</v>
+        <v>319.4</v>
       </c>
       <c r="L159" t="n">
         <v>312.32</v>
@@ -20938,7 +20938,7 @@
         <v>2.5</v>
       </c>
       <c r="J271" t="n">
-        <v>470.11</v>
+        <v>470.12</v>
       </c>
       <c r="K271" t="n">
         <v>443.36</v>
@@ -31626,7 +31626,7 @@
         <v>38.41</v>
       </c>
       <c r="O412" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31652,6 +31652,79 @@
       <c r="W412" s="3" t="n">
         <v>144.9</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>380.7</v>
+      </c>
+      <c r="D413" t="n">
+        <v>380.78</v>
+      </c>
+      <c r="E413" t="n">
+        <v>377.98</v>
+      </c>
+      <c r="F413" t="n">
+        <v>379.59</v>
+      </c>
+      <c r="G413" t="n">
+        <v>3028317</v>
+      </c>
+      <c r="H413" s="2" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J413" t="n">
+        <v>391.85</v>
+      </c>
+      <c r="K413" t="n">
+        <v>392.2</v>
+      </c>
+      <c r="L413" t="n">
+        <v>399.49</v>
+      </c>
+      <c r="M413" t="n">
+        <v>416.07</v>
+      </c>
+      <c r="N413" s="3" t="n">
+        <v>36.53</v>
+      </c>
+      <c r="O413" t="n">
+        <v>44</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="T413" s="3" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="U413" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31527,7 +31527,7 @@
         <v>380.14</v>
       </c>
       <c r="G411" t="n">
-        <v>9154900</v>
+        <v>9322100</v>
       </c>
       <c r="H411" s="1" t="n">
         <v>-0.68</v>
@@ -31589,25 +31589,41 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="C412" t="n">
+        <v>380.7</v>
+      </c>
+      <c r="D412" t="n">
+        <v>380.78</v>
+      </c>
+      <c r="E412" t="n">
+        <v>377.98</v>
+      </c>
+      <c r="F412" t="n">
+        <v>379.55</v>
+      </c>
       <c r="G412" t="n">
-        <v>4216295</v>
-      </c>
-      <c r="H412" s="2" t="n">
-        <v>0</v>
+        <v>4244900</v>
+      </c>
+      <c r="H412" s="1" t="n">
+        <v>-0.16</v>
       </c>
       <c r="I412" t="n">
         <v>2.5</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>391.85</v>
+      </c>
+      <c r="K412" t="n">
+        <v>392.2</v>
+      </c>
+      <c r="L412" t="n">
+        <v>399.49</v>
+      </c>
+      <c r="M412" t="n">
+        <v>416.07</v>
+      </c>
       <c r="N412" s="2" t="n">
-        <v>36.9</v>
+        <v>36.5</v>
       </c>
       <c r="O412" t="n">
         <v>43</v>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31626,7 +31626,7 @@
         <v>36.5</v>
       </c>
       <c r="O412" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31652,6 +31652,79 @@
       <c r="W412" s="2" t="n">
         <v>143</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>381.46</v>
+      </c>
+      <c r="D413" t="n">
+        <v>381.79</v>
+      </c>
+      <c r="E413" t="n">
+        <v>379.82</v>
+      </c>
+      <c r="F413" t="n">
+        <v>380.85</v>
+      </c>
+      <c r="G413" t="n">
+        <v>1589478</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J413" t="n">
+        <v>390.91</v>
+      </c>
+      <c r="K413" t="n">
+        <v>392.43</v>
+      </c>
+      <c r="L413" t="n">
+        <v>398.99</v>
+      </c>
+      <c r="M413" t="n">
+        <v>415.98</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>39.72</v>
+      </c>
+      <c r="O413" t="n">
+        <v>48</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -1829,7 +1829,7 @@
         <v>256.05</v>
       </c>
       <c r="L18" t="n">
-        <v>250.93</v>
+        <v>250.94</v>
       </c>
       <c r="M18" t="n">
         <v>239.75</v>
@@ -3422,7 +3422,7 @@
         <v>2.5</v>
       </c>
       <c r="J39" t="n">
-        <v>280.58</v>
+        <v>280.59</v>
       </c>
       <c r="K39" t="n">
         <v>268.78</v>
@@ -7362,7 +7362,7 @@
         <v>2.5</v>
       </c>
       <c r="J91" t="n">
-        <v>308.88</v>
+        <v>308.89</v>
       </c>
       <c r="K91" t="n">
         <v>302.49</v>
@@ -10476,7 +10476,7 @@
         <v>308.13</v>
       </c>
       <c r="K132" t="n">
-        <v>308.39</v>
+        <v>308.4</v>
       </c>
       <c r="L132" t="n">
         <v>300.06</v>
@@ -11751,7 +11751,7 @@
         <v>324.76</v>
       </c>
       <c r="K149" t="n">
-        <v>313.53</v>
+        <v>313.54</v>
       </c>
       <c r="L149" t="n">
         <v>307.62</v>
@@ -31602,7 +31602,7 @@
         <v>379.55</v>
       </c>
       <c r="G412" t="n">
-        <v>4244900</v>
+        <v>4289400</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>-0.16</v>
@@ -31668,37 +31668,37 @@
         <v>381.46</v>
       </c>
       <c r="D413" t="n">
-        <v>381.79</v>
+        <v>383.55</v>
       </c>
       <c r="E413" t="n">
         <v>379.82</v>
       </c>
       <c r="F413" t="n">
-        <v>380.85</v>
+        <v>382.22</v>
       </c>
       <c r="G413" t="n">
-        <v>1589478</v>
+        <v>7301750</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>0.34</v>
+        <v>0.7</v>
       </c>
       <c r="I413" t="n">
         <v>2.5</v>
       </c>
       <c r="J413" t="n">
-        <v>390.91</v>
+        <v>390.97</v>
       </c>
       <c r="K413" t="n">
-        <v>392.43</v>
+        <v>392.46</v>
       </c>
       <c r="L413" t="n">
-        <v>398.99</v>
+        <v>399</v>
       </c>
       <c r="M413" t="n">
-        <v>415.98</v>
+        <v>415.99</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>39.72</v>
+        <v>41.24</v>
       </c>
       <c r="O413" t="n">
         <v>48</v>
@@ -31715,13 +31715,13 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.28</v>
+        <v>5.27</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>15.4</v>
+        <v>15.1</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31589,25 +31589,41 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="C412" t="n">
+        <v>381.47</v>
+      </c>
+      <c r="D412" t="n">
+        <v>383.57</v>
+      </c>
+      <c r="E412" t="n">
+        <v>379.79</v>
+      </c>
+      <c r="F412" t="n">
+        <v>382.27</v>
+      </c>
       <c r="G412" t="n">
-        <v>7506542</v>
-      </c>
-      <c r="H412" s="3" t="n">
-        <v>0</v>
+        <v>7506100</v>
+      </c>
+      <c r="H412" s="1" t="n">
+        <v>0.72</v>
       </c>
       <c r="I412" t="n">
         <v>2.5</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>390.98</v>
+      </c>
+      <c r="K412" t="n">
+        <v>392.46</v>
+      </c>
+      <c r="L412" t="n">
+        <v>399</v>
+      </c>
+      <c r="M412" t="n">
+        <v>415.99</v>
+      </c>
       <c r="N412" s="3" t="n">
-        <v>38.2</v>
+        <v>41.29</v>
       </c>
       <c r="O412" t="n">
         <v>47</v>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31653,6 +31653,83 @@
         <v>141.2</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>374.97</v>
+      </c>
+      <c r="D413" t="n">
+        <v>376.15</v>
+      </c>
+      <c r="E413" t="n">
+        <v>374.24</v>
+      </c>
+      <c r="F413" t="n">
+        <v>375.65</v>
+      </c>
+      <c r="G413" t="n">
+        <v>2337921</v>
+      </c>
+      <c r="H413" s="2" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J413" t="n">
+        <v>389.59</v>
+      </c>
+      <c r="K413" t="n">
+        <v>392.51</v>
+      </c>
+      <c r="L413" t="n">
+        <v>398.46</v>
+      </c>
+      <c r="M413" t="n">
+        <v>415.87</v>
+      </c>
+      <c r="N413" s="1" t="n">
+        <v>29.12</v>
+      </c>
+      <c r="O413" t="n">
+        <v>42</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S413" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="T413" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="U413" s="3" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -2427,7 +2427,7 @@
         <v>2.5</v>
       </c>
       <c r="J26" t="n">
-        <v>271.9</v>
+        <v>271.91</v>
       </c>
       <c r="K26" t="n">
         <v>261.08</v>
@@ -10401,7 +10401,7 @@
         <v>308.13</v>
       </c>
       <c r="K131" t="n">
-        <v>308.4</v>
+        <v>308.39</v>
       </c>
       <c r="L131" t="n">
         <v>300.06</v>
@@ -11676,7 +11676,7 @@
         <v>324.76</v>
       </c>
       <c r="K148" t="n">
-        <v>313.54</v>
+        <v>313.53</v>
       </c>
       <c r="L148" t="n">
         <v>307.62</v>
@@ -20788,7 +20788,7 @@
         <v>2.5</v>
       </c>
       <c r="J269" t="n">
-        <v>470.12</v>
+        <v>470.11</v>
       </c>
       <c r="K269" t="n">
         <v>443.36</v>
@@ -31668,40 +31668,40 @@
         <v>374.97</v>
       </c>
       <c r="D413" t="n">
-        <v>376.15</v>
+        <v>378.25</v>
       </c>
       <c r="E413" t="n">
         <v>374.24</v>
       </c>
       <c r="F413" t="n">
-        <v>375.65</v>
+        <v>375.88</v>
       </c>
       <c r="G413" t="n">
-        <v>2337921</v>
+        <v>6967670</v>
       </c>
       <c r="H413" s="2" t="n">
-        <v>-1.73</v>
+        <v>-1.67</v>
       </c>
       <c r="I413" t="n">
         <v>2.5</v>
       </c>
       <c r="J413" t="n">
-        <v>389.59</v>
+        <v>389.6</v>
       </c>
       <c r="K413" t="n">
-        <v>392.51</v>
+        <v>392.52</v>
       </c>
       <c r="L413" t="n">
-        <v>398.46</v>
+        <v>398.47</v>
       </c>
       <c r="M413" t="n">
-        <v>415.87</v>
+        <v>415.88</v>
       </c>
       <c r="N413" s="1" t="n">
-        <v>29.12</v>
+        <v>29.25</v>
       </c>
       <c r="O413" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31719,13 +31719,13 @@
         </is>
       </c>
       <c r="S413" t="n">
-        <v>5.32</v>
+        <v>5.28</v>
       </c>
       <c r="T413" s="3" t="n">
-        <v>15.8</v>
+        <v>15.1</v>
       </c>
       <c r="U413" s="3" t="n">
-        <v>7.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="3" t="inlineStr"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31664,41 +31664,25 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="C413" t="n">
-        <v>374.97</v>
-      </c>
-      <c r="D413" t="n">
-        <v>378.25</v>
-      </c>
-      <c r="E413" t="n">
-        <v>374.24</v>
-      </c>
-      <c r="F413" t="n">
-        <v>375.88</v>
-      </c>
+      <c r="C413" t="inlineStr"/>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr"/>
       <c r="G413" t="n">
-        <v>6967670</v>
-      </c>
-      <c r="H413" s="2" t="n">
-        <v>-1.67</v>
+        <v>7008541</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I413" t="n">
         <v>2.5</v>
       </c>
-      <c r="J413" t="n">
-        <v>389.6</v>
-      </c>
-      <c r="K413" t="n">
-        <v>392.52</v>
-      </c>
-      <c r="L413" t="n">
-        <v>398.47</v>
-      </c>
-      <c r="M413" t="n">
-        <v>415.88</v>
-      </c>
-      <c r="N413" s="1" t="n">
-        <v>29.25</v>
+      <c r="J413" t="inlineStr"/>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr"/>
+      <c r="M413" t="inlineStr"/>
+      <c r="N413" s="3" t="n">
+        <v>33.16</v>
       </c>
       <c r="O413" t="n">
         <v>45</v>
@@ -31713,11 +31697,7 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R413" t="inlineStr">
-        <is>
-          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
-        </is>
-      </c>
+      <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
         <v>5.28</v>
       </c>
@@ -31728,7 +31708,9 @@
         <v>9.300000000000001</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="3" t="inlineStr"/>
+      <c r="W413" s="3" t="n">
+        <v>141.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31664,25 +31664,41 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr"/>
-      <c r="D413" t="inlineStr"/>
-      <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
+      <c r="C413" t="n">
+        <v>374.97</v>
+      </c>
+      <c r="D413" t="n">
+        <v>378.25</v>
+      </c>
+      <c r="E413" t="n">
+        <v>374.23</v>
+      </c>
+      <c r="F413" t="n">
+        <v>375.88</v>
+      </c>
       <c r="G413" t="n">
-        <v>7008541</v>
-      </c>
-      <c r="H413" s="3" t="n">
-        <v>0</v>
+        <v>7197200</v>
+      </c>
+      <c r="H413" s="2" t="n">
+        <v>-1.67</v>
       </c>
       <c r="I413" t="n">
         <v>2.5</v>
       </c>
-      <c r="J413" t="inlineStr"/>
-      <c r="K413" t="inlineStr"/>
-      <c r="L413" t="inlineStr"/>
-      <c r="M413" t="inlineStr"/>
-      <c r="N413" s="3" t="n">
-        <v>33.16</v>
+      <c r="J413" t="n">
+        <v>389.6</v>
+      </c>
+      <c r="K413" t="n">
+        <v>392.52</v>
+      </c>
+      <c r="L413" t="n">
+        <v>398.47</v>
+      </c>
+      <c r="M413" t="n">
+        <v>415.88</v>
+      </c>
+      <c r="N413" s="1" t="n">
+        <v>29.25</v>
       </c>
       <c r="O413" t="n">
         <v>45</v>
@@ -31697,7 +31713,11 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R413" t="inlineStr"/>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
       <c r="S413" t="n">
         <v>5.28</v>
       </c>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31701,7 +31701,7 @@
         <v>29.25</v>
       </c>
       <c r="O413" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31731,6 +31731,83 @@
       <c r="W413" s="3" t="n">
         <v>141.8</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>377.85</v>
+      </c>
+      <c r="D414" t="n">
+        <v>379.34</v>
+      </c>
+      <c r="E414" t="n">
+        <v>376.85</v>
+      </c>
+      <c r="F414" t="n">
+        <v>377.07</v>
+      </c>
+      <c r="G414" t="n">
+        <v>3587130</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I414" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J414" t="n">
+        <v>388.64</v>
+      </c>
+      <c r="K414" t="n">
+        <v>392.6</v>
+      </c>
+      <c r="L414" t="n">
+        <v>397.89</v>
+      </c>
+      <c r="M414" t="n">
+        <v>415.77</v>
+      </c>
+      <c r="N414" s="1" t="n">
+        <v>27.07</v>
+      </c>
+      <c r="O414" t="n">
+        <v>41</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S414" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T414" s="3" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="U414" s="3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31677,7 +31677,7 @@
         <v>375.88</v>
       </c>
       <c r="G413" t="n">
-        <v>7197200</v>
+        <v>7216600</v>
       </c>
       <c r="H413" s="2" t="n">
         <v>-1.67</v>
@@ -31747,40 +31747,40 @@
         <v>377.85</v>
       </c>
       <c r="D414" t="n">
-        <v>379.34</v>
+        <v>379.88</v>
       </c>
       <c r="E414" t="n">
-        <v>376.85</v>
+        <v>376.13</v>
       </c>
       <c r="F414" t="n">
-        <v>377.07</v>
+        <v>378.62</v>
       </c>
       <c r="G414" t="n">
-        <v>3587130</v>
+        <v>9544773</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>0.32</v>
+        <v>0.73</v>
       </c>
       <c r="I414" t="n">
         <v>2.5</v>
       </c>
       <c r="J414" t="n">
-        <v>388.64</v>
+        <v>388.72</v>
       </c>
       <c r="K414" t="n">
-        <v>392.6</v>
+        <v>392.62</v>
       </c>
       <c r="L414" t="n">
-        <v>397.89</v>
+        <v>397.9</v>
       </c>
       <c r="M414" t="n">
         <v>415.77</v>
       </c>
       <c r="N414" s="1" t="n">
-        <v>27.07</v>
+        <v>29.16</v>
       </c>
       <c r="O414" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31798,13 +31798,13 @@
         </is>
       </c>
       <c r="S414" t="n">
-        <v>5.3</v>
+        <v>5.23</v>
       </c>
       <c r="T414" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="U414" s="3" t="n">
-        <v>7.6</v>
+        <v>10.2</v>
       </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="3" t="inlineStr"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31756,7 +31756,7 @@
         <v>378.62</v>
       </c>
       <c r="G414" t="n">
-        <v>9544773</v>
+        <v>9669200</v>
       </c>
       <c r="H414" s="1" t="n">
         <v>0.73</v>
@@ -31807,7 +31807,9 @@
         <v>10.2</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="3" t="inlineStr"/>
+      <c r="W414" s="3" t="n">
+        <v>149.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31780,7 +31780,7 @@
         <v>29.16</v>
       </c>
       <c r="O414" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31810,6 +31810,79 @@
       <c r="W414" s="3" t="n">
         <v>149.2</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>383.98</v>
+      </c>
+      <c r="D415" t="n">
+        <v>384.69</v>
+      </c>
+      <c r="E415" t="n">
+        <v>383.26</v>
+      </c>
+      <c r="F415" t="n">
+        <v>384.29</v>
+      </c>
+      <c r="G415" t="n">
+        <v>3885150</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I415" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J415" t="n">
+        <v>387.99</v>
+      </c>
+      <c r="K415" t="n">
+        <v>392.94</v>
+      </c>
+      <c r="L415" t="n">
+        <v>397.42</v>
+      </c>
+      <c r="M415" t="n">
+        <v>415.65</v>
+      </c>
+      <c r="N415" s="3" t="n">
+        <v>37.63</v>
+      </c>
+      <c r="O415" t="n">
+        <v>44</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="T415" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="U415" s="3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31756,7 +31756,7 @@
         <v>378.62</v>
       </c>
       <c r="G414" t="n">
-        <v>9669200</v>
+        <v>9706600</v>
       </c>
       <c r="H414" s="1" t="n">
         <v>0.73</v>
@@ -31826,40 +31826,40 @@
         <v>383.98</v>
       </c>
       <c r="D415" t="n">
-        <v>384.69</v>
+        <v>385.17</v>
       </c>
       <c r="E415" t="n">
         <v>383.26</v>
       </c>
       <c r="F415" t="n">
-        <v>384.29</v>
+        <v>384.58</v>
       </c>
       <c r="G415" t="n">
-        <v>3885150</v>
+        <v>7205346</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="I415" t="n">
         <v>2.5</v>
       </c>
       <c r="J415" t="n">
-        <v>387.99</v>
+        <v>388.01</v>
       </c>
       <c r="K415" t="n">
-        <v>392.94</v>
+        <v>392.95</v>
       </c>
       <c r="L415" t="n">
-        <v>397.42</v>
+        <v>397.43</v>
       </c>
       <c r="M415" t="n">
         <v>415.65</v>
       </c>
       <c r="N415" s="3" t="n">
-        <v>37.63</v>
+        <v>37.95</v>
       </c>
       <c r="O415" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31873,13 +31873,13 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="T415" s="3" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="U415" s="3" t="n">
-        <v>7.3</v>
+        <v>9.1</v>
       </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="3" t="inlineStr"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31822,41 +31822,25 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="C415" t="n">
-        <v>383.98</v>
-      </c>
-      <c r="D415" t="n">
-        <v>385.17</v>
-      </c>
-      <c r="E415" t="n">
-        <v>383.26</v>
-      </c>
-      <c r="F415" t="n">
-        <v>384.58</v>
-      </c>
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr"/>
       <c r="G415" t="n">
-        <v>7205346</v>
-      </c>
-      <c r="H415" s="1" t="n">
-        <v>1.57</v>
+        <v>7274435</v>
+      </c>
+      <c r="H415" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I415" t="n">
         <v>2.5</v>
       </c>
-      <c r="J415" t="n">
-        <v>388.01</v>
-      </c>
-      <c r="K415" t="n">
-        <v>392.95</v>
-      </c>
-      <c r="L415" t="n">
-        <v>397.43</v>
-      </c>
-      <c r="M415" t="n">
-        <v>415.65</v>
-      </c>
+      <c r="J415" t="inlineStr"/>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr"/>
       <c r="N415" s="3" t="n">
-        <v>37.95</v>
+        <v>30.74</v>
       </c>
       <c r="O415" t="n">
         <v>45</v>
@@ -31882,7 +31866,9 @@
         <v>9.1</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="3" t="inlineStr"/>
+      <c r="W415" s="3" t="n">
+        <v>154.3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31822,25 +31822,41 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
+      <c r="C415" t="n">
+        <v>383.98</v>
+      </c>
+      <c r="D415" t="n">
+        <v>385.17</v>
+      </c>
+      <c r="E415" t="n">
+        <v>383.26</v>
+      </c>
+      <c r="F415" t="n">
+        <v>384.58</v>
+      </c>
       <c r="G415" t="n">
-        <v>7274435</v>
-      </c>
-      <c r="H415" s="3" t="n">
-        <v>0</v>
+        <v>7467200</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>1.57</v>
       </c>
       <c r="I415" t="n">
         <v>2.5</v>
       </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
+      <c r="J415" t="n">
+        <v>388.01</v>
+      </c>
+      <c r="K415" t="n">
+        <v>392.95</v>
+      </c>
+      <c r="L415" t="n">
+        <v>397.43</v>
+      </c>
+      <c r="M415" t="n">
+        <v>415.65</v>
+      </c>
       <c r="N415" s="3" t="n">
-        <v>30.74</v>
+        <v>37.95</v>
       </c>
       <c r="O415" t="n">
         <v>45</v>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7137,7 +7137,7 @@
         <v>2.5</v>
       </c>
       <c r="J88" t="n">
-        <v>308.89</v>
+        <v>308.88</v>
       </c>
       <c r="K88" t="n">
         <v>302.49</v>
@@ -10251,7 +10251,7 @@
         <v>308.13</v>
       </c>
       <c r="K129" t="n">
-        <v>308.39</v>
+        <v>308.4</v>
       </c>
       <c r="L129" t="n">
         <v>300.06</v>
@@ -12201,7 +12201,7 @@
         <v>339.24</v>
       </c>
       <c r="K155" t="n">
-        <v>319.4</v>
+        <v>319.39</v>
       </c>
       <c r="L155" t="n">
         <v>312.32</v>
@@ -31709,11 +31709,11 @@
         <v>37.95</v>
       </c>
       <c r="O413" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="Q413" t="inlineStr">
@@ -31734,6 +31734,81 @@
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="3" t="n">
         <v>154.3</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>382.61</v>
+      </c>
+      <c r="D414" t="n">
+        <v>382.74</v>
+      </c>
+      <c r="E414" t="n">
+        <v>381.16</v>
+      </c>
+      <c r="F414" t="n">
+        <v>382.15</v>
+      </c>
+      <c r="G414" t="n">
+        <v>4659220</v>
+      </c>
+      <c r="H414" s="2" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="I414" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J414" t="n">
+        <v>387.47</v>
+      </c>
+      <c r="K414" t="n">
+        <v>393.18</v>
+      </c>
+      <c r="L414" t="n">
+        <v>397.03</v>
+      </c>
+      <c r="M414" t="n">
+        <v>415.5</v>
+      </c>
+      <c r="N414" s="3" t="n">
+        <v>34.55</v>
+      </c>
+      <c r="O414" t="n">
+        <v>46</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="T414" s="3" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="U414" s="3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>155.1</v>
       </c>
     </row>
   </sheetData>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31736,6 +31736,79 @@
         <v>155.1</v>
       </c>
     </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>383.93</v>
+      </c>
+      <c r="D414" t="n">
+        <v>384</v>
+      </c>
+      <c r="E414" t="n">
+        <v>380.09</v>
+      </c>
+      <c r="F414" t="n">
+        <v>380.33</v>
+      </c>
+      <c r="G414" t="n">
+        <v>4032570</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="I414" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J414" t="n">
+        <v>386.78</v>
+      </c>
+      <c r="K414" t="n">
+        <v>393.39</v>
+      </c>
+      <c r="L414" t="n">
+        <v>396.57</v>
+      </c>
+      <c r="M414" t="n">
+        <v>415.34</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>38.08</v>
+      </c>
+      <c r="O414" t="n">
+        <v>44</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -2202,7 +2202,7 @@
         <v>2.5</v>
       </c>
       <c r="J23" t="n">
-        <v>271.91</v>
+        <v>271.9</v>
       </c>
       <c r="K23" t="n">
         <v>261.08</v>
@@ -7062,7 +7062,7 @@
         <v>2.5</v>
       </c>
       <c r="J87" t="n">
-        <v>308.88</v>
+        <v>308.89</v>
       </c>
       <c r="K87" t="n">
         <v>302.49</v>
@@ -11451,7 +11451,7 @@
         <v>324.76</v>
       </c>
       <c r="K145" t="n">
-        <v>313.53</v>
+        <v>313.54</v>
       </c>
       <c r="L145" t="n">
         <v>307.62</v>
@@ -12126,7 +12126,7 @@
         <v>339.24</v>
       </c>
       <c r="K154" t="n">
-        <v>319.39</v>
+        <v>319.4</v>
       </c>
       <c r="L154" t="n">
         <v>312.32</v>
@@ -31685,7 +31685,7 @@
         <v>382.15</v>
       </c>
       <c r="G413" t="n">
-        <v>4854300</v>
+        <v>4874400</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>-0.63</v>
@@ -31757,34 +31757,34 @@
         <v>380.09</v>
       </c>
       <c r="F414" t="n">
-        <v>380.33</v>
+        <v>381.67</v>
       </c>
       <c r="G414" t="n">
-        <v>4032570</v>
+        <v>5706764</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>-0.48</v>
+        <v>-0.13</v>
       </c>
       <c r="I414" t="n">
         <v>2.5</v>
       </c>
       <c r="J414" t="n">
-        <v>386.78</v>
+        <v>386.85</v>
       </c>
       <c r="K414" t="n">
-        <v>393.39</v>
+        <v>393.41</v>
       </c>
       <c r="L414" t="n">
-        <v>396.57</v>
+        <v>396.58</v>
       </c>
       <c r="M414" t="n">
-        <v>415.34</v>
+        <v>415.35</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>38.08</v>
+        <v>39.07</v>
       </c>
       <c r="O414" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31800,12 +31800,8 @@
       <c r="S414" t="n">
         <v>5.22</v>
       </c>
-      <c r="T414" s="2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="U414" s="2" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="T414" s="2" t="inlineStr"/>
+      <c r="U414" s="2" t="inlineStr"/>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>
     </row>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31713,7 +31713,7 @@
       </c>
       <c r="P413" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="Q413" t="inlineStr">

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31709,11 +31709,11 @@
         <v>39.07</v>
       </c>
       <c r="O413" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>fear</t>
         </is>
       </c>
       <c r="Q413" t="inlineStr">
@@ -31735,6 +31735,79 @@
       <c r="W413" s="3" t="n">
         <v>154.7</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>374.91</v>
+      </c>
+      <c r="D414" t="n">
+        <v>376.48</v>
+      </c>
+      <c r="E414" t="n">
+        <v>374.51</v>
+      </c>
+      <c r="F414" t="n">
+        <v>375.1</v>
+      </c>
+      <c r="G414" t="n">
+        <v>3716703</v>
+      </c>
+      <c r="H414" s="2" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="I414" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J414" t="n">
+        <v>386.02</v>
+      </c>
+      <c r="K414" t="n">
+        <v>393.42</v>
+      </c>
+      <c r="L414" t="n">
+        <v>396.12</v>
+      </c>
+      <c r="M414" t="n">
+        <v>415.14</v>
+      </c>
+      <c r="N414" s="3" t="n">
+        <v>35.36</v>
+      </c>
+      <c r="O414" t="n">
+        <v>37</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T414" s="3" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="U414" s="3" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31754,37 +31754,37 @@
         <v>376.48</v>
       </c>
       <c r="E414" t="n">
-        <v>374.51</v>
+        <v>373.38</v>
       </c>
       <c r="F414" t="n">
-        <v>375.1</v>
+        <v>376.09</v>
       </c>
       <c r="G414" t="n">
-        <v>3716703</v>
+        <v>7324014</v>
       </c>
       <c r="H414" s="2" t="n">
-        <v>-1.72</v>
+        <v>-1.46</v>
       </c>
       <c r="I414" t="n">
         <v>2.5</v>
       </c>
       <c r="J414" t="n">
-        <v>386.02</v>
+        <v>386.07</v>
       </c>
       <c r="K414" t="n">
-        <v>393.42</v>
+        <v>393.43</v>
       </c>
       <c r="L414" t="n">
-        <v>396.12</v>
+        <v>396.13</v>
       </c>
       <c r="M414" t="n">
         <v>415.14</v>
       </c>
       <c r="N414" s="3" t="n">
-        <v>35.36</v>
+        <v>35.99</v>
       </c>
       <c r="O414" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31798,13 +31798,13 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="T414" s="3" t="n">
-        <v>15.7</v>
+        <v>17.2</v>
       </c>
       <c r="U414" s="3" t="n">
-        <v>8.1</v>
+        <v>14</v>
       </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="3" t="inlineStr"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -2127,7 +2127,7 @@
         <v>2.5</v>
       </c>
       <c r="J22" t="n">
-        <v>271.9</v>
+        <v>271.91</v>
       </c>
       <c r="K22" t="n">
         <v>261.08</v>
@@ -31757,19 +31757,19 @@
         <v>373.38</v>
       </c>
       <c r="F414" t="n">
-        <v>376.09</v>
+        <v>375.99</v>
       </c>
       <c r="G414" t="n">
-        <v>7324014</v>
+        <v>10283502</v>
       </c>
       <c r="H414" s="2" t="n">
-        <v>-1.46</v>
+        <v>-1.49</v>
       </c>
       <c r="I414" t="n">
         <v>2.5</v>
       </c>
       <c r="J414" t="n">
-        <v>386.07</v>
+        <v>386.06</v>
       </c>
       <c r="K414" t="n">
         <v>393.43</v>
@@ -31781,10 +31781,10 @@
         <v>415.14</v>
       </c>
       <c r="N414" s="3" t="n">
-        <v>35.99</v>
+        <v>35.93</v>
       </c>
       <c r="O414" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31801,13 +31801,15 @@
         <v>5.19</v>
       </c>
       <c r="T414" s="3" t="n">
-        <v>17.2</v>
+        <v>16.9</v>
       </c>
       <c r="U414" s="3" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="3" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>157.3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31754,13 +31754,13 @@
         <v>376.48</v>
       </c>
       <c r="E414" t="n">
-        <v>373.38</v>
+        <v>373.36</v>
       </c>
       <c r="F414" t="n">
         <v>375.99</v>
       </c>
       <c r="G414" t="n">
-        <v>10283502</v>
+        <v>10283300</v>
       </c>
       <c r="H414" s="2" t="n">
         <v>-1.49</v>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31784,7 +31784,7 @@
         <v>35.93</v>
       </c>
       <c r="O414" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31784,7 +31784,7 @@
         <v>35.93</v>
       </c>
       <c r="O414" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31810,6 +31810,79 @@
       <c r="W414" s="2" t="n">
         <v>157.3</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>380.92</v>
+      </c>
+      <c r="D415" t="n">
+        <v>381.49</v>
+      </c>
+      <c r="E415" t="n">
+        <v>380.33</v>
+      </c>
+      <c r="F415" t="n">
+        <v>380.34</v>
+      </c>
+      <c r="G415" t="n">
+        <v>1469718</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="I415" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J415" t="n">
+        <v>385.16</v>
+      </c>
+      <c r="K415" t="n">
+        <v>393.45</v>
+      </c>
+      <c r="L415" t="n">
+        <v>395.68</v>
+      </c>
+      <c r="M415" t="n">
+        <v>415.05</v>
+      </c>
+      <c r="N415" s="3" t="n">
+        <v>38.81</v>
+      </c>
+      <c r="O415" t="n">
+        <v>24</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>extreme fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>3x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="T415" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="U415" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31826,60 +31826,60 @@
         <v>380.92</v>
       </c>
       <c r="D415" t="n">
-        <v>381.49</v>
+        <v>381.65</v>
       </c>
       <c r="E415" t="n">
-        <v>380.33</v>
+        <v>379.74</v>
       </c>
       <c r="F415" t="n">
-        <v>380.34</v>
+        <v>381.12</v>
       </c>
       <c r="G415" t="n">
-        <v>1469718</v>
+        <v>4932999</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="I415" t="n">
         <v>2.5</v>
       </c>
       <c r="J415" t="n">
-        <v>385.16</v>
+        <v>385.2</v>
       </c>
       <c r="K415" t="n">
-        <v>393.45</v>
+        <v>393.47</v>
       </c>
       <c r="L415" t="n">
-        <v>395.68</v>
+        <v>395.69</v>
       </c>
       <c r="M415" t="n">
         <v>415.05</v>
       </c>
       <c r="N415" s="3" t="n">
-        <v>38.81</v>
+        <v>39.62</v>
       </c>
       <c r="O415" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
-          <t>extreme fear</t>
+          <t>fear</t>
         </is>
       </c>
       <c r="Q415" t="inlineStr">
         <is>
-          <t>3x BUY</t>
+          <t>2x BUY</t>
         </is>
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.05</v>
+        <v>5.08</v>
       </c>
       <c r="T415" s="3" t="n">
-        <v>17.6</v>
+        <v>16.8</v>
       </c>
       <c r="U415" s="3" t="n">
-        <v>10.7</v>
+        <v>12.5</v>
       </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="3" t="inlineStr"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31760,7 +31760,7 @@
         <v>375.99</v>
       </c>
       <c r="G414" t="n">
-        <v>10283300</v>
+        <v>10311100</v>
       </c>
       <c r="H414" s="2" t="n">
         <v>-1.49</v>
@@ -31826,40 +31826,40 @@
         <v>380.92</v>
       </c>
       <c r="D415" t="n">
-        <v>381.65</v>
+        <v>382.93</v>
       </c>
       <c r="E415" t="n">
         <v>379.74</v>
       </c>
       <c r="F415" t="n">
-        <v>381.12</v>
+        <v>382.71</v>
       </c>
       <c r="G415" t="n">
-        <v>4932999</v>
+        <v>8522745</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>1.36</v>
+        <v>1.79</v>
       </c>
       <c r="I415" t="n">
         <v>2.5</v>
       </c>
       <c r="J415" t="n">
-        <v>385.2</v>
+        <v>385.28</v>
       </c>
       <c r="K415" t="n">
-        <v>393.47</v>
+        <v>393.49</v>
       </c>
       <c r="L415" t="n">
-        <v>395.69</v>
+        <v>395.7</v>
       </c>
       <c r="M415" t="n">
-        <v>415.05</v>
+        <v>415.06</v>
       </c>
       <c r="N415" s="3" t="n">
-        <v>39.62</v>
+        <v>41.2</v>
       </c>
       <c r="O415" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31873,16 +31873,18 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.08</v>
+        <v>5.09</v>
       </c>
       <c r="T415" s="3" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="U415" s="3" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="3" t="inlineStr"/>
+      <c r="W415" s="2" t="n">
+        <v>160.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31822,41 +31822,25 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="C415" t="n">
-        <v>380.92</v>
-      </c>
-      <c r="D415" t="n">
-        <v>382.93</v>
-      </c>
-      <c r="E415" t="n">
-        <v>379.74</v>
-      </c>
-      <c r="F415" t="n">
-        <v>382.71</v>
-      </c>
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr"/>
       <c r="G415" t="n">
         <v>8522745</v>
       </c>
-      <c r="H415" s="1" t="n">
-        <v>1.79</v>
+      <c r="H415" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I415" t="n">
         <v>2.5</v>
       </c>
-      <c r="J415" t="n">
-        <v>385.28</v>
-      </c>
-      <c r="K415" t="n">
-        <v>393.49</v>
-      </c>
-      <c r="L415" t="n">
-        <v>395.7</v>
-      </c>
-      <c r="M415" t="n">
-        <v>415.06</v>
-      </c>
+      <c r="J415" t="inlineStr"/>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr"/>
       <c r="N415" s="3" t="n">
-        <v>41.2</v>
+        <v>33.89</v>
       </c>
       <c r="O415" t="n">
         <v>32</v>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31822,28 +31822,44 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
+      <c r="C415" t="n">
+        <v>380.92</v>
+      </c>
+      <c r="D415" t="n">
+        <v>382.94</v>
+      </c>
+      <c r="E415" t="n">
+        <v>379.72</v>
+      </c>
+      <c r="F415" t="n">
+        <v>382.71</v>
+      </c>
       <c r="G415" t="n">
-        <v>8522745</v>
-      </c>
-      <c r="H415" s="3" t="n">
-        <v>0</v>
+        <v>8548000</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>1.79</v>
       </c>
       <c r="I415" t="n">
         <v>2.5</v>
       </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
+      <c r="J415" t="n">
+        <v>385.28</v>
+      </c>
+      <c r="K415" t="n">
+        <v>393.49</v>
+      </c>
+      <c r="L415" t="n">
+        <v>395.7</v>
+      </c>
+      <c r="M415" t="n">
+        <v>415.06</v>
+      </c>
       <c r="N415" s="3" t="n">
-        <v>33.89</v>
+        <v>41.2</v>
       </c>
       <c r="O415" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31859,7 +31859,7 @@
         <v>41.2</v>
       </c>
       <c r="O415" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W415"/>
+  <dimension ref="A1:W416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31859,7 +31859,7 @@
         <v>41.2</v>
       </c>
       <c r="O415" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31885,6 +31885,79 @@
       <c r="W415" s="2" t="n">
         <v>160.4</v>
       </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>381.34</v>
+      </c>
+      <c r="D416" t="n">
+        <v>384.88</v>
+      </c>
+      <c r="E416" t="n">
+        <v>381.07</v>
+      </c>
+      <c r="F416" t="n">
+        <v>382.97</v>
+      </c>
+      <c r="G416" t="n">
+        <v>3524962</v>
+      </c>
+      <c r="H416" s="1" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I416" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J416" t="n">
+        <v>384.37</v>
+      </c>
+      <c r="K416" t="n">
+        <v>393.68</v>
+      </c>
+      <c r="L416" t="n">
+        <v>395.31</v>
+      </c>
+      <c r="M416" t="n">
+        <v>414.98</v>
+      </c>
+      <c r="N416" s="3" t="n">
+        <v>55.56</v>
+      </c>
+      <c r="O416" t="n">
+        <v>30</v>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr"/>
+      <c r="S416" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="T416" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="U416" s="3" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="V416" t="inlineStr"/>
+      <c r="W416" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31904,57 +31904,57 @@
         <v>384.88</v>
       </c>
       <c r="E416" t="n">
-        <v>381.07</v>
+        <v>380.9</v>
       </c>
       <c r="F416" t="n">
-        <v>382.97</v>
+        <v>381.75</v>
       </c>
       <c r="G416" t="n">
-        <v>3524962</v>
-      </c>
-      <c r="H416" s="1" t="n">
-        <v>0.07000000000000001</v>
+        <v>6785989</v>
+      </c>
+      <c r="H416" s="2" t="n">
+        <v>-0.25</v>
       </c>
       <c r="I416" t="n">
         <v>2.5</v>
       </c>
       <c r="J416" t="n">
-        <v>384.37</v>
+        <v>384.31</v>
       </c>
       <c r="K416" t="n">
-        <v>393.68</v>
+        <v>393.66</v>
       </c>
       <c r="L416" t="n">
-        <v>395.31</v>
+        <v>395.3</v>
       </c>
       <c r="M416" t="n">
         <v>414.98</v>
       </c>
       <c r="N416" s="3" t="n">
-        <v>55.56</v>
+        <v>54.15</v>
       </c>
       <c r="O416" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="P416" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>extreme fear</t>
         </is>
       </c>
       <c r="Q416" t="inlineStr">
         <is>
-          <t>2x BUY</t>
+          <t>3x BUY</t>
         </is>
       </c>
       <c r="R416" t="inlineStr"/>
       <c r="S416" t="n">
-        <v>5.09</v>
+        <v>5.1</v>
       </c>
       <c r="T416" s="3" t="n">
-        <v>15.9</v>
+        <v>21.3</v>
       </c>
       <c r="U416" s="3" t="n">
-        <v>8.1</v>
+        <v>22</v>
       </c>
       <c r="V416" t="inlineStr"/>
       <c r="W416" s="3" t="inlineStr"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31835,7 +31835,7 @@
         <v>382.71</v>
       </c>
       <c r="G415" t="n">
-        <v>8548000</v>
+        <v>8773500</v>
       </c>
       <c r="H415" s="1" t="n">
         <v>1.79</v>
@@ -31907,31 +31907,31 @@
         <v>380.9</v>
       </c>
       <c r="F416" t="n">
-        <v>381.75</v>
+        <v>382.01</v>
       </c>
       <c r="G416" t="n">
-        <v>6785989</v>
+        <v>9045826</v>
       </c>
       <c r="H416" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.18</v>
       </c>
       <c r="I416" t="n">
         <v>2.5</v>
       </c>
       <c r="J416" t="n">
-        <v>384.31</v>
+        <v>384.32</v>
       </c>
       <c r="K416" t="n">
-        <v>393.66</v>
+        <v>393.67</v>
       </c>
       <c r="L416" t="n">
-        <v>395.3</v>
+        <v>395.31</v>
       </c>
       <c r="M416" t="n">
         <v>414.98</v>
       </c>
       <c r="N416" s="3" t="n">
-        <v>54.15</v>
+        <v>54.46</v>
       </c>
       <c r="O416" t="n">
         <v>18</v>
@@ -31951,13 +31951,15 @@
         <v>5.1</v>
       </c>
       <c r="T416" s="3" t="n">
-        <v>21.3</v>
+        <v>20</v>
       </c>
       <c r="U416" s="3" t="n">
-        <v>22</v>
+        <v>23.3</v>
       </c>
       <c r="V416" t="inlineStr"/>
-      <c r="W416" s="3" t="inlineStr"/>
+      <c r="W416" s="2" t="n">
+        <v>168.6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31822,25 +31822,41 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
+      <c r="C415" t="n">
+        <v>381.34</v>
+      </c>
+      <c r="D415" t="n">
+        <v>384.88</v>
+      </c>
+      <c r="E415" t="n">
+        <v>380.89</v>
+      </c>
+      <c r="F415" t="n">
+        <v>382.01</v>
+      </c>
       <c r="G415" t="n">
-        <v>9045826</v>
-      </c>
-      <c r="H415" s="2" t="n">
-        <v>0</v>
+        <v>9063100</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>-0.18</v>
       </c>
       <c r="I415" t="n">
         <v>2.5</v>
       </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
+      <c r="J415" t="n">
+        <v>384.32</v>
+      </c>
+      <c r="K415" t="n">
+        <v>393.67</v>
+      </c>
+      <c r="L415" t="n">
+        <v>395.31</v>
+      </c>
+      <c r="M415" t="n">
+        <v>414.98</v>
+      </c>
       <c r="N415" s="2" t="n">
-        <v>55.3</v>
+        <v>54.46</v>
       </c>
       <c r="O415" t="n">
         <v>18</v>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31709,7 +31709,7 @@
         <v>54.46</v>
       </c>
       <c r="O413" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6762,7 +6762,7 @@
         <v>2.5</v>
       </c>
       <c r="J83" t="n">
-        <v>308.89</v>
+        <v>308.88</v>
       </c>
       <c r="K83" t="n">
         <v>302.49</v>
@@ -31709,7 +31709,7 @@
         <v>54.46</v>
       </c>
       <c r="O413" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31735,6 +31735,79 @@
       <c r="W413" s="1" t="n">
         <v>168.6</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>381.42</v>
+      </c>
+      <c r="D414" t="n">
+        <v>381.92</v>
+      </c>
+      <c r="E414" t="n">
+        <v>379.12</v>
+      </c>
+      <c r="F414" t="n">
+        <v>379.81</v>
+      </c>
+      <c r="G414" t="n">
+        <v>3894634</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="I414" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J414" t="n">
+        <v>383.39</v>
+      </c>
+      <c r="K414" t="n">
+        <v>393.8</v>
+      </c>
+      <c r="L414" t="n">
+        <v>394.95</v>
+      </c>
+      <c r="M414" t="n">
+        <v>414.9</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>46.44</v>
+      </c>
+      <c r="O414" t="n">
+        <v>24</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>extreme fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>3x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -11151,7 +11151,7 @@
         <v>324.76</v>
       </c>
       <c r="K141" t="n">
-        <v>313.54</v>
+        <v>313.53</v>
       </c>
       <c r="L141" t="n">
         <v>307.62</v>
@@ -11826,7 +11826,7 @@
         <v>339.24</v>
       </c>
       <c r="K150" t="n">
-        <v>319.4</v>
+        <v>319.39</v>
       </c>
       <c r="L150" t="n">
         <v>312.32</v>
@@ -31757,13 +31757,13 @@
         <v>379.12</v>
       </c>
       <c r="F414" t="n">
-        <v>379.81</v>
+        <v>379.69</v>
       </c>
       <c r="G414" t="n">
-        <v>3894634</v>
+        <v>5054504</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>-0.58</v>
+        <v>-0.61</v>
       </c>
       <c r="I414" t="n">
         <v>2.5</v>
@@ -31781,10 +31781,10 @@
         <v>414.9</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>46.44</v>
+        <v>46.31</v>
       </c>
       <c r="O414" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31798,16 +31798,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.13</v>
+        <v>5.14</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>11.4</v>
+        <v>11.9</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="1" t="n">
+        <v>161.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31705,7 +31705,7 @@
         <v>46.31</v>
       </c>
       <c r="O413" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31731,6 +31731,79 @@
       <c r="W413" s="1" t="n">
         <v>161.9</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>377.91</v>
+      </c>
+      <c r="D414" t="n">
+        <v>380.88</v>
+      </c>
+      <c r="E414" t="n">
+        <v>377.26</v>
+      </c>
+      <c r="F414" t="n">
+        <v>379.89</v>
+      </c>
+      <c r="G414" t="n">
+        <v>2391898</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I414" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J414" t="n">
+        <v>382.38</v>
+      </c>
+      <c r="K414" t="n">
+        <v>393.89</v>
+      </c>
+      <c r="L414" t="n">
+        <v>394.64</v>
+      </c>
+      <c r="M414" t="n">
+        <v>414.8</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>48.85</v>
+      </c>
+      <c r="O414" t="n">
+        <v>28</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31753,34 +31753,34 @@
         <v>377.26</v>
       </c>
       <c r="F414" t="n">
-        <v>379.89</v>
+        <v>378.07</v>
       </c>
       <c r="G414" t="n">
-        <v>2391898</v>
-      </c>
-      <c r="H414" s="3" t="n">
-        <v>0.05</v>
+        <v>4763283</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-0.43</v>
       </c>
       <c r="I414" t="n">
         <v>2.5</v>
       </c>
       <c r="J414" t="n">
-        <v>382.38</v>
+        <v>382.29</v>
       </c>
       <c r="K414" t="n">
-        <v>393.89</v>
+        <v>393.85</v>
       </c>
       <c r="L414" t="n">
-        <v>394.64</v>
+        <v>394.63</v>
       </c>
       <c r="M414" t="n">
-        <v>414.8</v>
+        <v>414.79</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>48.85</v>
+        <v>46.77</v>
       </c>
       <c r="O414" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31794,13 +31794,13 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.08</v>
+        <v>5.12</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>9.9</v>
+        <v>11.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -1150,7 +1150,7 @@
         <v>256.05</v>
       </c>
       <c r="L9" t="n">
-        <v>250.94</v>
+        <v>250.93</v>
       </c>
       <c r="M9" t="n">
         <v>239.75</v>
@@ -1823,7 +1823,7 @@
         <v>2.5</v>
       </c>
       <c r="J18" t="n">
-        <v>271.91</v>
+        <v>271.9</v>
       </c>
       <c r="K18" t="n">
         <v>261.08</v>
@@ -6683,7 +6683,7 @@
         <v>2.5</v>
       </c>
       <c r="J82" t="n">
-        <v>308.88</v>
+        <v>308.89</v>
       </c>
       <c r="K82" t="n">
         <v>302.49</v>
@@ -9797,7 +9797,7 @@
         <v>308.13</v>
       </c>
       <c r="K123" t="n">
-        <v>308.4</v>
+        <v>308.39</v>
       </c>
       <c r="L123" t="n">
         <v>300.06</v>
@@ -11747,7 +11747,7 @@
         <v>339.24</v>
       </c>
       <c r="K149" t="n">
-        <v>319.39</v>
+        <v>319.4</v>
       </c>
       <c r="L149" t="n">
         <v>312.32</v>
@@ -31681,7 +31681,7 @@
         <v>379.69</v>
       </c>
       <c r="G413" t="n">
-        <v>5144700</v>
+        <v>5164300</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>-0.61</v>
@@ -31753,31 +31753,31 @@
         <v>377.26</v>
       </c>
       <c r="F414" t="n">
-        <v>378.07</v>
+        <v>377.65</v>
       </c>
       <c r="G414" t="n">
-        <v>4763283</v>
+        <v>5917199</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>-0.43</v>
+        <v>-0.54</v>
       </c>
       <c r="I414" t="n">
         <v>2.5</v>
       </c>
       <c r="J414" t="n">
-        <v>382.29</v>
+        <v>382.26</v>
       </c>
       <c r="K414" t="n">
         <v>393.85</v>
       </c>
       <c r="L414" t="n">
-        <v>394.63</v>
+        <v>394.62</v>
       </c>
       <c r="M414" t="n">
         <v>414.79</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>46.77</v>
+        <v>46.32</v>
       </c>
       <c r="O414" t="n">
         <v>27</v>
@@ -31797,13 +31797,15 @@
         <v>5.12</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="1" t="n">
+        <v>160.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31705,7 +31705,7 @@
         <v>46.32</v>
       </c>
       <c r="O413" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31705,7 +31705,7 @@
         <v>46.32</v>
       </c>
       <c r="O413" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31731,6 +31731,77 @@
       <c r="W413" s="3" t="n">
         <v>160.4</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>377.91</v>
+      </c>
+      <c r="D414" t="n">
+        <v>379.32</v>
+      </c>
+      <c r="E414" t="n">
+        <v>378.79</v>
+      </c>
+      <c r="F414" t="n">
+        <v>378.93</v>
+      </c>
+      <c r="G414" t="n">
+        <v>348378</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I414" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J414" t="n">
+        <v>381.57</v>
+      </c>
+      <c r="K414" t="n">
+        <v>394.01</v>
+      </c>
+      <c r="L414" t="n">
+        <v>394.25</v>
+      </c>
+      <c r="M414" t="n">
+        <v>414.64</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>45.51</v>
+      </c>
+      <c r="O414" t="n">
+        <v>29</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="U414" s="2" t="inlineStr"/>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31705,7 +31705,7 @@
         <v>46.32</v>
       </c>
       <c r="O413" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31744,43 +31744,43 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>377.91</v>
+        <v>379.17</v>
       </c>
       <c r="D414" t="n">
-        <v>379.32</v>
+        <v>379.52</v>
       </c>
       <c r="E414" t="n">
-        <v>378.79</v>
+        <v>377.74</v>
       </c>
       <c r="F414" t="n">
-        <v>378.93</v>
+        <v>379.41</v>
       </c>
       <c r="G414" t="n">
-        <v>348378</v>
+        <v>3859901</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>0.34</v>
+        <v>0.47</v>
       </c>
       <c r="I414" t="n">
         <v>2.5</v>
       </c>
       <c r="J414" t="n">
-        <v>381.57</v>
+        <v>381.59</v>
       </c>
       <c r="K414" t="n">
-        <v>394.01</v>
+        <v>394.02</v>
       </c>
       <c r="L414" t="n">
         <v>394.25</v>
       </c>
       <c r="M414" t="n">
-        <v>414.64</v>
+        <v>414.65</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>45.51</v>
+        <v>46.12</v>
       </c>
       <c r="O414" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31794,12 +31794,14 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.1</v>
+        <v>5.11</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="U414" s="2" t="inlineStr"/>
+        <v>16.6</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>
     </row>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -1075,7 +1075,7 @@
         <v>256.05</v>
       </c>
       <c r="L8" t="n">
-        <v>250.93</v>
+        <v>250.94</v>
       </c>
       <c r="M8" t="n">
         <v>239.75</v>
@@ -1748,7 +1748,7 @@
         <v>2.5</v>
       </c>
       <c r="J17" t="n">
-        <v>271.9</v>
+        <v>271.91</v>
       </c>
       <c r="K17" t="n">
         <v>261.08</v>
@@ -9722,7 +9722,7 @@
         <v>308.13</v>
       </c>
       <c r="K122" t="n">
-        <v>308.39</v>
+        <v>308.4</v>
       </c>
       <c r="L122" t="n">
         <v>300.06</v>
@@ -31681,7 +31681,7 @@
         <v>377.65</v>
       </c>
       <c r="G413" t="n">
-        <v>6010700</v>
+        <v>6038300</v>
       </c>
       <c r="H413" s="3" t="n">
         <v>-0.54</v>
@@ -31747,40 +31747,40 @@
         <v>379.17</v>
       </c>
       <c r="D414" t="n">
-        <v>379.52</v>
+        <v>379.55</v>
       </c>
       <c r="E414" t="n">
-        <v>377.74</v>
+        <v>376.2</v>
       </c>
       <c r="F414" t="n">
-        <v>379.41</v>
+        <v>378.95</v>
       </c>
       <c r="G414" t="n">
-        <v>3859901</v>
+        <v>6836525</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>0.47</v>
+        <v>0.34</v>
       </c>
       <c r="I414" t="n">
         <v>2.5</v>
       </c>
       <c r="J414" t="n">
-        <v>381.59</v>
+        <v>381.57</v>
       </c>
       <c r="K414" t="n">
-        <v>394.02</v>
+        <v>394.01</v>
       </c>
       <c r="L414" t="n">
         <v>394.25</v>
       </c>
       <c r="M414" t="n">
-        <v>414.65</v>
+        <v>414.64</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>46.12</v>
+        <v>45.54</v>
       </c>
       <c r="O414" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31794,16 +31794,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.11</v>
+        <v>5.15</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>10</v>
+        <v>11.4</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>150.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31743,41 +31743,25 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="C414" t="n">
-        <v>379.17</v>
-      </c>
-      <c r="D414" t="n">
-        <v>379.55</v>
-      </c>
-      <c r="E414" t="n">
-        <v>376.2</v>
-      </c>
-      <c r="F414" t="n">
-        <v>378.95</v>
-      </c>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
       <c r="G414" t="n">
         <v>6836525</v>
       </c>
-      <c r="H414" s="1" t="n">
-        <v>0.34</v>
+      <c r="H414" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I414" t="n">
         <v>2.5</v>
       </c>
-      <c r="J414" t="n">
-        <v>381.57</v>
-      </c>
-      <c r="K414" t="n">
-        <v>394.01</v>
-      </c>
-      <c r="L414" t="n">
-        <v>394.25</v>
-      </c>
-      <c r="M414" t="n">
-        <v>414.64</v>
-      </c>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
       <c r="N414" s="2" t="n">
-        <v>45.54</v>
+        <v>43.83</v>
       </c>
       <c r="O414" t="n">
         <v>31</v>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31743,28 +31743,44 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>379.17</v>
+      </c>
+      <c r="D414" t="n">
+        <v>379.55</v>
+      </c>
+      <c r="E414" t="n">
+        <v>376.2</v>
+      </c>
+      <c r="F414" t="n">
+        <v>378.95</v>
+      </c>
       <c r="G414" t="n">
-        <v>6836525</v>
-      </c>
-      <c r="H414" s="2" t="n">
-        <v>0</v>
+        <v>6857700</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>0.34</v>
       </c>
       <c r="I414" t="n">
         <v>2.5</v>
       </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>381.57</v>
+      </c>
+      <c r="K414" t="n">
+        <v>394.01</v>
+      </c>
+      <c r="L414" t="n">
+        <v>394.25</v>
+      </c>
+      <c r="M414" t="n">
+        <v>414.64</v>
+      </c>
       <c r="N414" s="2" t="n">
-        <v>43.83</v>
+        <v>45.54</v>
       </c>
       <c r="O414" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31780,7 +31780,7 @@
         <v>45.54</v>
       </c>
       <c r="O414" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31806,6 +31806,77 @@
       <c r="W414" s="2" t="n">
         <v>150.4</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>379.17</v>
+      </c>
+      <c r="D415" t="n">
+        <v>373.87</v>
+      </c>
+      <c r="E415" t="n">
+        <v>372.37</v>
+      </c>
+      <c r="F415" t="n">
+        <v>372.37</v>
+      </c>
+      <c r="G415" t="n">
+        <v>870190</v>
+      </c>
+      <c r="H415" s="3" t="n">
+        <v>-1.74</v>
+      </c>
+      <c r="I415" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J415" t="n">
+        <v>380.6</v>
+      </c>
+      <c r="K415" t="n">
+        <v>394.03</v>
+      </c>
+      <c r="L415" t="n">
+        <v>393.83</v>
+      </c>
+      <c r="M415" t="n">
+        <v>414.44</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="O415" t="n">
+        <v>28</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="U415" s="2" t="inlineStr"/>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31780,7 +31780,7 @@
         <v>45.54</v>
       </c>
       <c r="O414" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31819,62 +31819,64 @@
         </is>
       </c>
       <c r="C415" t="n">
-        <v>379.17</v>
+        <v>373.54</v>
       </c>
       <c r="D415" t="n">
         <v>373.87</v>
       </c>
       <c r="E415" t="n">
-        <v>372.37</v>
+        <v>369.57</v>
       </c>
       <c r="F415" t="n">
-        <v>372.37</v>
+        <v>369.94</v>
       </c>
       <c r="G415" t="n">
-        <v>870190</v>
+        <v>10284688</v>
       </c>
       <c r="H415" s="3" t="n">
-        <v>-1.74</v>
+        <v>-2.38</v>
       </c>
       <c r="I415" t="n">
         <v>2.5</v>
       </c>
       <c r="J415" t="n">
-        <v>380.6</v>
+        <v>380.48</v>
       </c>
       <c r="K415" t="n">
-        <v>394.03</v>
+        <v>393.99</v>
       </c>
       <c r="L415" t="n">
-        <v>393.83</v>
+        <v>393.81</v>
       </c>
       <c r="M415" t="n">
-        <v>414.44</v>
+        <v>414.43</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>41.67</v>
+        <v>39.61</v>
       </c>
       <c r="O415" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>extreme fear</t>
         </is>
       </c>
       <c r="Q415" t="inlineStr">
         <is>
-          <t>2x BUY</t>
+          <t>3x BUY</t>
         </is>
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.04</v>
+        <v>4.95</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="U415" s="2" t="inlineStr"/>
+        <v>19.5</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="2" t="inlineStr"/>
     </row>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31756,7 +31756,7 @@
         <v>378.95</v>
       </c>
       <c r="G414" t="n">
-        <v>6857700</v>
+        <v>6880800</v>
       </c>
       <c r="H414" s="1" t="n">
         <v>0.34</v>
@@ -31808,77 +31808,79 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
+      <c r="A415" s="4" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B415" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="C415" t="n">
+      <c r="C415" s="4" t="n">
         <v>373.54</v>
       </c>
-      <c r="D415" t="n">
+      <c r="D415" s="4" t="n">
         <v>373.87</v>
       </c>
-      <c r="E415" t="n">
-        <v>369.57</v>
-      </c>
-      <c r="F415" t="n">
-        <v>369.94</v>
-      </c>
-      <c r="G415" t="n">
-        <v>10284688</v>
-      </c>
-      <c r="H415" s="3" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="I415" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J415" t="n">
-        <v>380.48</v>
-      </c>
-      <c r="K415" t="n">
-        <v>393.99</v>
-      </c>
-      <c r="L415" t="n">
-        <v>393.81</v>
-      </c>
-      <c r="M415" t="n">
-        <v>414.43</v>
-      </c>
-      <c r="N415" s="2" t="n">
-        <v>39.61</v>
-      </c>
-      <c r="O415" t="n">
+      <c r="E415" s="4" t="n">
+        <v>368.35</v>
+      </c>
+      <c r="F415" s="4" t="n">
+        <v>369</v>
+      </c>
+      <c r="G415" s="4" t="n">
+        <v>17000345</v>
+      </c>
+      <c r="H415" s="5" t="n">
+        <v>-2.63</v>
+      </c>
+      <c r="I415" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J415" s="4" t="n">
+        <v>380.43</v>
+      </c>
+      <c r="K415" s="4" t="n">
+        <v>393.97</v>
+      </c>
+      <c r="L415" s="4" t="n">
+        <v>393.8</v>
+      </c>
+      <c r="M415" s="4" t="n">
+        <v>414.42</v>
+      </c>
+      <c r="N415" s="6" t="n">
+        <v>38.86</v>
+      </c>
+      <c r="O415" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="P415" s="4" t="inlineStr">
+        <is>
+          <t>extreme fear</t>
+        </is>
+      </c>
+      <c r="Q415" s="4" t="inlineStr">
+        <is>
+          <t>3x BUY</t>
+        </is>
+      </c>
+      <c r="R415" s="4" t="inlineStr"/>
+      <c r="S415" s="4" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T415" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="P415" t="inlineStr">
-        <is>
-          <t>extreme fear</t>
-        </is>
-      </c>
-      <c r="Q415" t="inlineStr">
-        <is>
-          <t>3x BUY</t>
-        </is>
-      </c>
-      <c r="R415" t="inlineStr"/>
-      <c r="S415" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="T415" s="2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="U415" s="2" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="inlineStr"/>
+      <c r="U415" s="6" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="V415" s="4" t="inlineStr"/>
+      <c r="W415" s="6" t="n">
+        <v>152.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31808,77 +31808,61 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="4" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="B415" s="4" t="inlineStr">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="C415" s="4" t="n">
-        <v>373.54</v>
-      </c>
-      <c r="D415" s="4" t="n">
-        <v>373.87</v>
-      </c>
-      <c r="E415" s="4" t="n">
-        <v>368.35</v>
-      </c>
-      <c r="F415" s="4" t="n">
-        <v>369</v>
-      </c>
-      <c r="G415" s="4" t="n">
-        <v>17000345</v>
-      </c>
-      <c r="H415" s="5" t="n">
-        <v>-2.63</v>
-      </c>
-      <c r="I415" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J415" s="4" t="n">
-        <v>380.43</v>
-      </c>
-      <c r="K415" s="4" t="n">
-        <v>393.97</v>
-      </c>
-      <c r="L415" s="4" t="n">
-        <v>393.8</v>
-      </c>
-      <c r="M415" s="4" t="n">
-        <v>414.42</v>
-      </c>
-      <c r="N415" s="6" t="n">
-        <v>38.86</v>
-      </c>
-      <c r="O415" s="4" t="n">
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="n">
+        <v>17009944</v>
+      </c>
+      <c r="H415" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I415" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J415" t="inlineStr"/>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr"/>
+      <c r="N415" s="2" t="n">
+        <v>48.52</v>
+      </c>
+      <c r="O415" t="n">
         <v>20</v>
       </c>
-      <c r="P415" s="4" t="inlineStr">
+      <c r="P415" t="inlineStr">
         <is>
           <t>extreme fear</t>
         </is>
       </c>
-      <c r="Q415" s="4" t="inlineStr">
+      <c r="Q415" t="inlineStr">
         <is>
           <t>3x BUY</t>
         </is>
       </c>
-      <c r="R415" s="4" t="inlineStr"/>
-      <c r="S415" s="4" t="n">
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
         <v>4.95</v>
       </c>
-      <c r="T415" s="6" t="n">
+      <c r="T415" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U415" s="6" t="n">
+      <c r="U415" s="2" t="n">
         <v>15.2</v>
       </c>
-      <c r="V415" s="4" t="inlineStr"/>
-      <c r="W415" s="6" t="n">
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="n">
         <v>152.4</v>
       </c>
     </row>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31808,61 +31808,77 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
+      <c r="A415" s="4" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B415" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
-      <c r="G415" t="n">
-        <v>17009944</v>
-      </c>
-      <c r="H415" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I415" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
-      <c r="N415" s="2" t="n">
-        <v>48.52</v>
-      </c>
-      <c r="O415" t="n">
+      <c r="C415" s="4" t="n">
+        <v>373.54</v>
+      </c>
+      <c r="D415" s="4" t="n">
+        <v>373.87</v>
+      </c>
+      <c r="E415" s="4" t="n">
+        <v>368.35</v>
+      </c>
+      <c r="F415" s="4" t="n">
+        <v>369</v>
+      </c>
+      <c r="G415" s="4" t="n">
+        <v>17010400</v>
+      </c>
+      <c r="H415" s="5" t="n">
+        <v>-2.63</v>
+      </c>
+      <c r="I415" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J415" s="4" t="n">
+        <v>380.43</v>
+      </c>
+      <c r="K415" s="4" t="n">
+        <v>393.97</v>
+      </c>
+      <c r="L415" s="4" t="n">
+        <v>393.8</v>
+      </c>
+      <c r="M415" s="4" t="n">
+        <v>414.42</v>
+      </c>
+      <c r="N415" s="6" t="n">
+        <v>38.86</v>
+      </c>
+      <c r="O415" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="P415" t="inlineStr">
+      <c r="P415" s="4" t="inlineStr">
         <is>
           <t>extreme fear</t>
         </is>
       </c>
-      <c r="Q415" t="inlineStr">
+      <c r="Q415" s="4" t="inlineStr">
         <is>
           <t>3x BUY</t>
         </is>
       </c>
-      <c r="R415" t="inlineStr"/>
-      <c r="S415" t="n">
+      <c r="R415" s="4" t="inlineStr"/>
+      <c r="S415" s="4" t="n">
         <v>4.95</v>
       </c>
-      <c r="T415" s="2" t="n">
+      <c r="T415" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="U415" s="2" t="n">
+      <c r="U415" s="6" t="n">
         <v>15.2</v>
       </c>
-      <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="n">
+      <c r="V415" s="4" t="inlineStr"/>
+      <c r="W415" s="6" t="n">
         <v>152.4</v>
       </c>
     </row>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31855,7 +31855,7 @@
         <v>38.86</v>
       </c>
       <c r="O415" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W415"/>
+  <dimension ref="A1:W416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31855,7 +31855,7 @@
         <v>38.86</v>
       </c>
       <c r="O415" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
@@ -31881,6 +31881,79 @@
       <c r="W415" s="6" t="n">
         <v>152.4</v>
       </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>368.95</v>
+      </c>
+      <c r="D416" t="n">
+        <v>369.25</v>
+      </c>
+      <c r="E416" t="n">
+        <v>364.33</v>
+      </c>
+      <c r="F416" t="n">
+        <v>366.38</v>
+      </c>
+      <c r="G416" t="n">
+        <v>7659080</v>
+      </c>
+      <c r="H416" s="3" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="I416" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J416" t="n">
+        <v>379.08</v>
+      </c>
+      <c r="K416" t="n">
+        <v>393.79</v>
+      </c>
+      <c r="L416" t="n">
+        <v>393.4</v>
+      </c>
+      <c r="M416" t="n">
+        <v>414.21</v>
+      </c>
+      <c r="N416" s="2" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="O416" t="n">
+        <v>20</v>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>extreme fear</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>3x BUY</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr"/>
+      <c r="S416" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="T416" s="2" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="U416" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="V416" t="inlineStr"/>
+      <c r="W416" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31831,7 +31831,7 @@
         <v>369</v>
       </c>
       <c r="G415" s="4" t="n">
-        <v>17010400</v>
+        <v>17543700</v>
       </c>
       <c r="H415" s="5" t="n">
         <v>-2.63</v>
@@ -31903,22 +31903,22 @@
         <v>364.33</v>
       </c>
       <c r="F416" t="n">
-        <v>366.38</v>
+        <v>366.61</v>
       </c>
       <c r="G416" t="n">
-        <v>7659080</v>
+        <v>9911036</v>
       </c>
       <c r="H416" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.65</v>
       </c>
       <c r="I416" t="n">
         <v>2.5</v>
       </c>
       <c r="J416" t="n">
-        <v>379.08</v>
+        <v>379.09</v>
       </c>
       <c r="K416" t="n">
-        <v>393.79</v>
+        <v>393.8</v>
       </c>
       <c r="L416" t="n">
         <v>393.4</v>
@@ -31927,10 +31927,10 @@
         <v>414.21</v>
       </c>
       <c r="N416" s="2" t="n">
-        <v>37.35</v>
+        <v>37.51</v>
       </c>
       <c r="O416" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P416" t="inlineStr">
         <is>
@@ -31944,16 +31944,18 @@
       </c>
       <c r="R416" t="inlineStr"/>
       <c r="S416" t="n">
-        <v>4.98</v>
+        <v>4.99</v>
       </c>
       <c r="T416" s="2" t="n">
-        <v>20.1</v>
+        <v>19.5</v>
       </c>
       <c r="U416" s="2" t="n">
-        <v>15.5</v>
+        <v>16.8</v>
       </c>
       <c r="V416" t="inlineStr"/>
-      <c r="W416" s="2" t="inlineStr"/>
+      <c r="W416" s="2" t="n">
+        <v>151.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31818,25 +31818,41 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
+      <c r="C415" t="n">
+        <v>368.95</v>
+      </c>
+      <c r="D415" t="n">
+        <v>369.25</v>
+      </c>
+      <c r="E415" t="n">
+        <v>364.33</v>
+      </c>
+      <c r="F415" t="n">
+        <v>366.61</v>
+      </c>
       <c r="G415" t="n">
-        <v>9911036</v>
-      </c>
-      <c r="H415" s="2" t="n">
-        <v>0</v>
+        <v>10097500</v>
+      </c>
+      <c r="H415" s="3" t="n">
+        <v>-0.65</v>
       </c>
       <c r="I415" t="n">
         <v>2.5</v>
       </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
+      <c r="J415" t="n">
+        <v>379.09</v>
+      </c>
+      <c r="K415" t="n">
+        <v>393.8</v>
+      </c>
+      <c r="L415" t="n">
+        <v>393.4</v>
+      </c>
+      <c r="M415" t="n">
+        <v>414.21</v>
+      </c>
       <c r="N415" s="2" t="n">
-        <v>39.33</v>
+        <v>37.51</v>
       </c>
       <c r="O415" t="n">
         <v>21</v>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6383,7 +6383,7 @@
         <v>2.5</v>
       </c>
       <c r="J78" t="n">
-        <v>308.89</v>
+        <v>308.88</v>
       </c>
       <c r="K78" t="n">
         <v>302.49</v>
@@ -11447,7 +11447,7 @@
         <v>339.24</v>
       </c>
       <c r="K145" t="n">
-        <v>319.4</v>
+        <v>319.39</v>
       </c>
       <c r="L145" t="n">
         <v>312.32</v>
@@ -31705,7 +31705,7 @@
         <v>37.51</v>
       </c>
       <c r="O413" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31731,6 +31731,79 @@
       <c r="W413" s="2" t="n">
         <v>151.8</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>367.3</v>
+      </c>
+      <c r="D414" t="n">
+        <v>369</v>
+      </c>
+      <c r="E414" t="n">
+        <v>365.54</v>
+      </c>
+      <c r="F414" t="n">
+        <v>368.3</v>
+      </c>
+      <c r="G414" t="n">
+        <v>3590853</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I414" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J414" t="n">
+        <v>378.61</v>
+      </c>
+      <c r="K414" t="n">
+        <v>393.74</v>
+      </c>
+      <c r="L414" t="n">
+        <v>392.98</v>
+      </c>
+      <c r="M414" t="n">
+        <v>413.99</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>36.25</v>
+      </c>
+      <c r="O414" t="n">
+        <v>27</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -10772,7 +10772,7 @@
         <v>324.76</v>
       </c>
       <c r="K136" t="n">
-        <v>313.53</v>
+        <v>313.54</v>
       </c>
       <c r="L136" t="n">
         <v>307.62</v>
@@ -11447,7 +11447,7 @@
         <v>339.24</v>
       </c>
       <c r="K145" t="n">
-        <v>319.39</v>
+        <v>319.4</v>
       </c>
       <c r="L145" t="n">
         <v>312.32</v>
@@ -31747,25 +31747,25 @@
         <v>367.3</v>
       </c>
       <c r="D414" t="n">
-        <v>369</v>
+        <v>369.3</v>
       </c>
       <c r="E414" t="n">
         <v>365.54</v>
       </c>
       <c r="F414" t="n">
-        <v>368.3</v>
+        <v>367.82</v>
       </c>
       <c r="G414" t="n">
-        <v>3590853</v>
+        <v>6420927</v>
       </c>
       <c r="H414" s="3" t="n">
-        <v>0.46</v>
+        <v>0.33</v>
       </c>
       <c r="I414" t="n">
         <v>2.5</v>
       </c>
       <c r="J414" t="n">
-        <v>378.61</v>
+        <v>378.59</v>
       </c>
       <c r="K414" t="n">
         <v>393.74</v>
@@ -31777,7 +31777,7 @@
         <v>413.99</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>36.25</v>
+        <v>35.64</v>
       </c>
       <c r="O414" t="n">
         <v>27</v>
@@ -31794,16 +31794,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>4.97</v>
+        <v>4.99</v>
       </c>
       <c r="T414" s="2" t="n">
         <v>18.4</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>9.1</v>
+        <v>10.5</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>151</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31606,7 +31606,7 @@
         <v>366.61</v>
       </c>
       <c r="G412" t="n">
-        <v>10097500</v>
+        <v>10120200</v>
       </c>
       <c r="H412" s="3" t="n">
         <v>-0.65</v>
@@ -31668,28 +31668,44 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr"/>
-      <c r="D413" t="inlineStr"/>
-      <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
+      <c r="C413" t="n">
+        <v>367.3</v>
+      </c>
+      <c r="D413" t="n">
+        <v>369.31</v>
+      </c>
+      <c r="E413" t="n">
+        <v>365.54</v>
+      </c>
+      <c r="F413" t="n">
+        <v>367.82</v>
+      </c>
       <c r="G413" t="n">
-        <v>6420927</v>
-      </c>
-      <c r="H413" s="2" t="n">
-        <v>0</v>
+        <v>6429100</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>0.33</v>
       </c>
       <c r="I413" t="n">
         <v>2.5</v>
       </c>
-      <c r="J413" t="inlineStr"/>
-      <c r="K413" t="inlineStr"/>
-      <c r="L413" t="inlineStr"/>
-      <c r="M413" t="inlineStr"/>
+      <c r="J413" t="n">
+        <v>378.59</v>
+      </c>
+      <c r="K413" t="n">
+        <v>393.74</v>
+      </c>
+      <c r="L413" t="n">
+        <v>392.98</v>
+      </c>
+      <c r="M413" t="n">
+        <v>413.99</v>
+      </c>
       <c r="N413" s="2" t="n">
-        <v>34.05</v>
+        <v>35.64</v>
       </c>
       <c r="O413" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31705,7 +31705,7 @@
         <v>35.64</v>
       </c>
       <c r="O413" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31731,6 +31731,79 @@
       <c r="W413" s="2" t="n">
         <v>151</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>368.45</v>
+      </c>
+      <c r="D414" t="n">
+        <v>370.38</v>
+      </c>
+      <c r="E414" t="n">
+        <v>368.45</v>
+      </c>
+      <c r="F414" t="n">
+        <v>370.2</v>
+      </c>
+      <c r="G414" t="n">
+        <v>910324</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I414" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J414" t="n">
+        <v>377.95</v>
+      </c>
+      <c r="K414" t="n">
+        <v>393.71</v>
+      </c>
+      <c r="L414" t="n">
+        <v>392.47</v>
+      </c>
+      <c r="M414" t="n">
+        <v>413.77</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>43.87</v>
+      </c>
+      <c r="O414" t="n">
+        <v>32</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31681,7 +31681,7 @@
         <v>367.82</v>
       </c>
       <c r="G413" t="n">
-        <v>6429100</v>
+        <v>6548100</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>0.33</v>
@@ -31747,40 +31747,40 @@
         <v>368.45</v>
       </c>
       <c r="D414" t="n">
-        <v>370.38</v>
+        <v>372.59</v>
       </c>
       <c r="E414" t="n">
         <v>368.45</v>
       </c>
       <c r="F414" t="n">
-        <v>370.2</v>
+        <v>372.18</v>
       </c>
       <c r="G414" t="n">
-        <v>910324</v>
+        <v>4706433</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>0.65</v>
+        <v>1.19</v>
       </c>
       <c r="I414" t="n">
         <v>2.5</v>
       </c>
       <c r="J414" t="n">
-        <v>377.95</v>
+        <v>378.05</v>
       </c>
       <c r="K414" t="n">
-        <v>393.71</v>
+        <v>393.74</v>
       </c>
       <c r="L414" t="n">
-        <v>392.47</v>
+        <v>392.49</v>
       </c>
       <c r="M414" t="n">
-        <v>413.77</v>
+        <v>413.78</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>43.87</v>
+        <v>46.17</v>
       </c>
       <c r="O414" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31794,13 +31794,13 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -1448,7 +1448,7 @@
         <v>2.5</v>
       </c>
       <c r="J13" t="n">
-        <v>271.91</v>
+        <v>271.9</v>
       </c>
       <c r="K13" t="n">
         <v>261.08</v>
@@ -6308,7 +6308,7 @@
         <v>2.5</v>
       </c>
       <c r="J77" t="n">
-        <v>308.88</v>
+        <v>308.89</v>
       </c>
       <c r="K77" t="n">
         <v>302.49</v>
@@ -9422,7 +9422,7 @@
         <v>308.13</v>
       </c>
       <c r="K118" t="n">
-        <v>308.4</v>
+        <v>308.39</v>
       </c>
       <c r="L118" t="n">
         <v>300.06</v>
@@ -19809,7 +19809,7 @@
         <v>2.5</v>
       </c>
       <c r="J256" t="n">
-        <v>470.11</v>
+        <v>470.12</v>
       </c>
       <c r="K256" t="n">
         <v>443.36</v>
@@ -29431,7 +29431,7 @@
         <v>28.35</v>
       </c>
       <c r="O383" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P383" t="inlineStr">
         <is>
@@ -29510,7 +29510,7 @@
         <v>28.29</v>
       </c>
       <c r="O384" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P384" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>34.68</v>
       </c>
       <c r="O386" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P386" t="inlineStr">
         <is>
@@ -29743,7 +29743,7 @@
         <v>44.34</v>
       </c>
       <c r="O387" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P387" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>41.98</v>
       </c>
       <c r="O390" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P390" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>33.3</v>
       </c>
       <c r="O391" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P391" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>32.47</v>
       </c>
       <c r="O393" s="4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>33.9</v>
       </c>
       <c r="O394" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P394" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>38.41</v>
       </c>
       <c r="O397" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P397" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>36.5</v>
       </c>
       <c r="O398" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P398" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>29.25</v>
       </c>
       <c r="O400" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P400" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>29.16</v>
       </c>
       <c r="O401" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P401" t="inlineStr">
         <is>
@@ -30880,11 +30880,11 @@
         <v>37.95</v>
       </c>
       <c r="O402" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P402" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>fear</t>
         </is>
       </c>
       <c r="Q402" t="inlineStr">
@@ -30955,7 +30955,7 @@
         <v>34.55</v>
       </c>
       <c r="O403" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P403" t="inlineStr">
         <is>
@@ -31030,11 +31030,11 @@
         <v>39.07</v>
       </c>
       <c r="O404" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P404" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="Q404" t="inlineStr">
@@ -31105,7 +31105,7 @@
         <v>35.93</v>
       </c>
       <c r="O405" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P405" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>41.2</v>
       </c>
       <c r="O406" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P406" t="inlineStr">
         <is>
@@ -31255,7 +31255,7 @@
         <v>54.46</v>
       </c>
       <c r="O407" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="P407" t="inlineStr">
         <is>
@@ -31330,7 +31330,7 @@
         <v>46.31</v>
       </c>
       <c r="O408" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P408" t="inlineStr">
         <is>
@@ -31405,7 +31405,7 @@
         <v>46.32</v>
       </c>
       <c r="O409" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P409" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>45.54</v>
       </c>
       <c r="O410" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="P410" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>38.86</v>
       </c>
       <c r="O411" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>37.51</v>
       </c>
       <c r="O412" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31693,7 +31693,7 @@
         <v>378.59</v>
       </c>
       <c r="K413" t="n">
-        <v>393.74</v>
+        <v>393.73</v>
       </c>
       <c r="L413" t="n">
         <v>392.98</v>
@@ -31705,7 +31705,7 @@
         <v>35.64</v>
       </c>
       <c r="O413" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31753,19 +31753,19 @@
         <v>368.45</v>
       </c>
       <c r="F414" t="n">
-        <v>372.18</v>
+        <v>372.28</v>
       </c>
       <c r="G414" t="n">
-        <v>4706433</v>
+        <v>5151791</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="I414" t="n">
         <v>2.5</v>
       </c>
       <c r="J414" t="n">
-        <v>378.05</v>
+        <v>378.06</v>
       </c>
       <c r="K414" t="n">
         <v>393.74</v>
@@ -31777,10 +31777,10 @@
         <v>413.78</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>46.17</v>
+        <v>46.28</v>
       </c>
       <c r="O414" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31803,7 +31803,9 @@
         <v>12.5</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>149.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31705,7 +31705,7 @@
         <v>46.28</v>
       </c>
       <c r="O413" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31731,6 +31731,79 @@
       <c r="W413" s="2" t="n">
         <v>149.2</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>371.29</v>
+      </c>
+      <c r="D414" t="n">
+        <v>371.4</v>
+      </c>
+      <c r="E414" t="n">
+        <v>369.87</v>
+      </c>
+      <c r="F414" t="n">
+        <v>370.43</v>
+      </c>
+      <c r="G414" t="n">
+        <v>3479141</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="I414" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J414" t="n">
+        <v>377.54</v>
+      </c>
+      <c r="K414" t="n">
+        <v>393.68</v>
+      </c>
+      <c r="L414" t="n">
+        <v>391.98</v>
+      </c>
+      <c r="M414" t="n">
+        <v>413.52</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>41.38</v>
+      </c>
+      <c r="O414" t="n">
+        <v>35</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -700,7 +700,7 @@
         <v>256.05</v>
       </c>
       <c r="L3" t="n">
-        <v>250.94</v>
+        <v>250.93</v>
       </c>
       <c r="M3" t="n">
         <v>239.75</v>
@@ -2293,7 +2293,7 @@
         <v>2.5</v>
       </c>
       <c r="J24" t="n">
-        <v>280.59</v>
+        <v>280.58</v>
       </c>
       <c r="K24" t="n">
         <v>268.78</v>
@@ -6233,7 +6233,7 @@
         <v>2.5</v>
       </c>
       <c r="J76" t="n">
-        <v>308.89</v>
+        <v>308.88</v>
       </c>
       <c r="K76" t="n">
         <v>302.49</v>
@@ -31681,7 +31681,7 @@
         <v>372.28</v>
       </c>
       <c r="G413" t="n">
-        <v>5319900</v>
+        <v>5335900</v>
       </c>
       <c r="H413" s="3" t="n">
         <v>1.21</v>
@@ -31747,40 +31747,40 @@
         <v>371.29</v>
       </c>
       <c r="D414" t="n">
-        <v>371.4</v>
+        <v>373.6</v>
       </c>
       <c r="E414" t="n">
-        <v>369.87</v>
+        <v>368.88</v>
       </c>
       <c r="F414" t="n">
-        <v>370.43</v>
+        <v>373.51</v>
       </c>
       <c r="G414" t="n">
-        <v>3479141</v>
-      </c>
-      <c r="H414" s="1" t="n">
-        <v>-0.5</v>
+        <v>9001436</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>0.33</v>
       </c>
       <c r="I414" t="n">
         <v>2.5</v>
       </c>
       <c r="J414" t="n">
-        <v>377.54</v>
+        <v>377.69</v>
       </c>
       <c r="K414" t="n">
-        <v>393.68</v>
+        <v>393.73</v>
       </c>
       <c r="L414" t="n">
-        <v>391.98</v>
+        <v>392</v>
       </c>
       <c r="M414" t="n">
-        <v>413.52</v>
+        <v>413.54</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>41.38</v>
+        <v>44.55</v>
       </c>
       <c r="O414" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31794,16 +31794,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.02</v>
+        <v>5.05</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17.3</v>
+        <v>16.9</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>14.4</v>
+        <v>13.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>148.7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31756,7 +31756,7 @@
         <v>373.51</v>
       </c>
       <c r="G414" t="n">
-        <v>9001436</v>
+        <v>8922700</v>
       </c>
       <c r="H414" s="3" t="n">
         <v>0.33</v>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31780,7 +31780,7 @@
         <v>44.55</v>
       </c>
       <c r="O414" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31806,6 +31806,79 @@
       <c r="W414" s="2" t="n">
         <v>148.7</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>368.8</v>
+      </c>
+      <c r="D415" t="n">
+        <v>369.94</v>
+      </c>
+      <c r="E415" t="n">
+        <v>367.42</v>
+      </c>
+      <c r="F415" t="n">
+        <v>368.03</v>
+      </c>
+      <c r="G415" t="n">
+        <v>3990509</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="I415" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J415" t="n">
+        <v>376.96</v>
+      </c>
+      <c r="K415" t="n">
+        <v>393.37</v>
+      </c>
+      <c r="L415" t="n">
+        <v>391.46</v>
+      </c>
+      <c r="M415" t="n">
+        <v>413.27</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>32.16</v>
+      </c>
+      <c r="O415" t="n">
+        <v>35</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31756,7 +31756,7 @@
         <v>373.51</v>
       </c>
       <c r="G414" t="n">
-        <v>8922700</v>
+        <v>9013100</v>
       </c>
       <c r="H414" s="3" t="n">
         <v>0.33</v>
@@ -31825,25 +31825,25 @@
         <v>369.94</v>
       </c>
       <c r="E415" t="n">
-        <v>367.42</v>
+        <v>366.97</v>
       </c>
       <c r="F415" t="n">
-        <v>368.03</v>
+        <v>368.57</v>
       </c>
       <c r="G415" t="n">
-        <v>3990509</v>
+        <v>8983381</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>-1.47</v>
+        <v>-1.32</v>
       </c>
       <c r="I415" t="n">
         <v>2.5</v>
       </c>
       <c r="J415" t="n">
-        <v>376.96</v>
+        <v>376.98</v>
       </c>
       <c r="K415" t="n">
-        <v>393.37</v>
+        <v>393.38</v>
       </c>
       <c r="L415" t="n">
         <v>391.46</v>
@@ -31852,7 +31852,7 @@
         <v>413.27</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>32.16</v>
+        <v>32.54</v>
       </c>
       <c r="O415" t="n">
         <v>35</v>
@@ -31869,16 +31869,18 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>16.3</v>
+        <v>17.2</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>10.2</v>
+        <v>13.6</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="inlineStr"/>
+      <c r="W415" s="2" t="n">
+        <v>151</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31831,7 +31831,7 @@
         <v>368.57</v>
       </c>
       <c r="G415" t="n">
-        <v>8983381</v>
+        <v>9110500</v>
       </c>
       <c r="H415" s="1" t="n">
         <v>-1.32</v>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31855,7 +31855,7 @@
         <v>32.54</v>
       </c>
       <c r="O415" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W415"/>
+  <dimension ref="A1:W416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31855,7 +31855,7 @@
         <v>32.54</v>
       </c>
       <c r="O415" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31881,6 +31881,83 @@
       <c r="W415" s="2" t="n">
         <v>151</v>
       </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="4" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B416" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C416" s="4" t="n">
+        <v>361.45</v>
+      </c>
+      <c r="D416" s="4" t="n">
+        <v>361.68</v>
+      </c>
+      <c r="E416" s="4" t="n">
+        <v>356.64</v>
+      </c>
+      <c r="F416" s="4" t="n">
+        <v>357.45</v>
+      </c>
+      <c r="G416" s="4" t="n">
+        <v>7329419</v>
+      </c>
+      <c r="H416" s="5" t="n">
+        <v>-3.02</v>
+      </c>
+      <c r="I416" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J416" s="4" t="n">
+        <v>375.85</v>
+      </c>
+      <c r="K416" s="4" t="n">
+        <v>392.85</v>
+      </c>
+      <c r="L416" s="4" t="n">
+        <v>390.82</v>
+      </c>
+      <c r="M416" s="4" t="n">
+        <v>412.93</v>
+      </c>
+      <c r="N416" s="7" t="n">
+        <v>27.36</v>
+      </c>
+      <c r="O416" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="P416" s="4" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q416" s="4" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R416" s="4" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S416" s="4" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T416" s="6" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="U416" s="6" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="V416" s="4" t="inlineStr"/>
+      <c r="W416" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31831,7 +31831,7 @@
         <v>368.57</v>
       </c>
       <c r="G415" t="n">
-        <v>9110500</v>
+        <v>9132600</v>
       </c>
       <c r="H415" s="1" t="n">
         <v>-1.32</v>
@@ -31900,37 +31900,37 @@
         <v>361.68</v>
       </c>
       <c r="E416" s="4" t="n">
-        <v>356.64</v>
+        <v>354.67</v>
       </c>
       <c r="F416" s="4" t="n">
-        <v>357.45</v>
+        <v>355.78</v>
       </c>
       <c r="G416" s="4" t="n">
-        <v>7329419</v>
+        <v>16051216</v>
       </c>
       <c r="H416" s="5" t="n">
-        <v>-3.02</v>
+        <v>-3.47</v>
       </c>
       <c r="I416" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="J416" s="4" t="n">
-        <v>375.85</v>
+        <v>375.76</v>
       </c>
       <c r="K416" s="4" t="n">
-        <v>392.85</v>
+        <v>392.82</v>
       </c>
       <c r="L416" s="4" t="n">
-        <v>390.82</v>
+        <v>390.8</v>
       </c>
       <c r="M416" s="4" t="n">
-        <v>412.93</v>
+        <v>412.92</v>
       </c>
       <c r="N416" s="7" t="n">
-        <v>27.36</v>
+        <v>26.54</v>
       </c>
       <c r="O416" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
@@ -31948,13 +31948,13 @@
         </is>
       </c>
       <c r="S416" s="4" t="n">
-        <v>4.95</v>
+        <v>4.93</v>
       </c>
       <c r="T416" s="6" t="n">
         <v>19.4</v>
       </c>
       <c r="U416" s="6" t="n">
-        <v>12.7</v>
+        <v>19.3</v>
       </c>
       <c r="V416" s="4" t="inlineStr"/>
       <c r="W416" s="6" t="inlineStr"/>

--- a/US_stock/GOLD_table.xlsx
+++ b/US_stock/GOLD_table.xlsx
@@ -31800,61 +31800,81 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
+      <c r="A415" s="4" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B415" s="4" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
-      <c r="G415" t="n">
-        <v>16200319</v>
-      </c>
-      <c r="H415" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I415" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
-      <c r="N415" s="2" t="n">
-        <v>34.36</v>
-      </c>
-      <c r="O415" t="n">
+      <c r="C415" s="4" t="n">
+        <v>361.45</v>
+      </c>
+      <c r="D415" s="4" t="n">
+        <v>361.68</v>
+      </c>
+      <c r="E415" s="4" t="n">
+        <v>354.67</v>
+      </c>
+      <c r="F415" s="4" t="n">
+        <v>355.78</v>
+      </c>
+      <c r="G415" s="4" t="n">
+        <v>16231700</v>
+      </c>
+      <c r="H415" s="5" t="n">
+        <v>-3.47</v>
+      </c>
+      <c r="I415" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J415" s="4" t="n">
+        <v>375.76</v>
+      </c>
+      <c r="K415" s="4" t="n">
+        <v>392.82</v>
+      </c>
+      <c r="L415" s="4" t="n">
+        <v>390.8</v>
+      </c>
+      <c r="M415" s="4" t="n">
+        <v>412.92</v>
+      </c>
+      <c r="N415" s="7" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="O415" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="P415" t="inlineStr">
+      <c r="P415" s="4" t="inlineStr">
         <is>
           <t>fear</t>
         </is>
       </c>
-      <c r="Q415" t="inlineStr">
+      <c r="Q415" s="4" t="inlineStr">
         <is>
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R415" t="inlineStr"/>
-      <c r="S415" t="n">
+      <c r="R415" s="4" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S415" s="4" t="n">
         <v>4.93</v>
       </c>
-      <c r="T415" s="2" t="n">
+      <c r="T415" s="6" t="n">
         <v>19.4</v>
       </c>
-      <c r="U415" s="2" t="n">
+      <c r="U415" s="6" t="n">
         <v>19.3</v>
       </c>
-      <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="n">
+      <c r="V415" s="4" t="inlineStr"/>
+      <c r="W415" s="6" t="n">
         <v>149.8</v>
       </c>
     </row>
